--- a/odoo/addons/base/static/xls/contacts_import_template.xlsx
+++ b/odoo/addons/base/static/xls/contacts_import_template.xlsx
@@ -109,7 +109,7 @@
     <t>BE</t>
   </si>
   <si>
-    <t>www.modulo-interiors.com</t>
+    <t/>
   </si>
   <si>
     <t>Vendor</t>
@@ -162,7 +162,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,12 +186,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -240,11 +234,11 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -578,7 +572,7 @@
     <col min="16" max="16" style="10" width="28.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,7 +662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -695,7 +689,7 @@
         <v>30</v>
       </c>
       <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -704,9 +698,9 @@
       <c r="O3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+      <c r="P3" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -739,10 +733,10 @@
       <c r="N4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+      <c r="O4" s="5"/>
+      <c r="P4" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -780,9 +774,9 @@
         <v>46</v>
       </c>
       <c r="O5" s="3"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+      <c r="P5" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -797,10 +791,10 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+      <c r="O6" s="5"/>
+      <c r="P6" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -816,9 +810,9 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+      <c r="P7" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -834,9 +828,9 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+      <c r="P8" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -852,9 +846,9 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+      <c r="P9" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -870,9 +864,9 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+      <c r="P10" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -888,9 +882,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+      <c r="P11" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -906,9 +900,9 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+      <c r="P12" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -924,9 +918,9 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+      <c r="P13" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -942,9 +936,9 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+      <c r="P14" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -960,9 +954,9 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+      <c r="P15" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -978,9 +972,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+      <c r="P16" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -996,9 +990,9 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+      <c r="P17" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1014,9 +1008,9 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+      <c r="P18" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1032,9 +1026,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+      <c r="P19" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1050,9 +1044,9 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+      <c r="P20" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1068,9 +1062,9 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+      <c r="P21" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1086,9 +1080,9 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+      <c r="P22" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1104,9 +1098,9 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+      <c r="P23" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1122,9 +1116,9 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+      <c r="P24" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1140,9 +1134,9 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+      <c r="P25" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1158,9 +1152,9 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+      <c r="P26" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1176,9 +1170,9 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+      <c r="P27" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1194,9 +1188,9 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+      <c r="P28" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1212,9 +1206,9 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+      <c r="P29" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1230,7 +1224,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="6"/>
+      <c r="P30" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
       <c r="A31" s="3"/>
@@ -1248,7 +1242,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="6"/>
+      <c r="P31" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
       <c r="A32" s="3"/>
@@ -1266,7 +1260,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
-      <c r="P32" s="6"/>
+      <c r="P32" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
       <c r="A33" s="3"/>
@@ -1284,7 +1278,7 @@
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="6"/>
+      <c r="P33" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
       <c r="A34" s="3"/>
@@ -1302,7 +1296,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="6"/>
+      <c r="P34" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="3"/>
@@ -1320,7 +1314,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
-      <c r="P35" s="6"/>
+      <c r="P35" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3"/>
@@ -1338,7 +1332,7 @@
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="6"/>
+      <c r="P36" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3"/>
@@ -1356,7 +1350,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="6"/>
+      <c r="P37" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3"/>
@@ -1374,7 +1368,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="6"/>
+      <c r="P38" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3"/>
@@ -1392,7 +1386,7 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="6"/>
+      <c r="P39" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3"/>
@@ -1410,7 +1404,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="6"/>
+      <c r="P40" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3"/>
@@ -1428,7 +1422,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="6"/>
+      <c r="P41" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="3"/>
@@ -1446,7 +1440,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="6"/>
+      <c r="P42" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3"/>
@@ -1464,7 +1458,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="6"/>
+      <c r="P43" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3"/>
@@ -1482,7 +1476,7 @@
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="6"/>
+      <c r="P44" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3"/>
@@ -1500,7 +1494,7 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="6"/>
+      <c r="P45" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3"/>
@@ -1518,7 +1512,7 @@
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="6"/>
+      <c r="P46" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3"/>
@@ -1536,7 +1530,7 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="6"/>
+      <c r="P47" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3"/>
@@ -1554,7 +1548,7 @@
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="6"/>
+      <c r="P48" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3"/>
@@ -1572,7 +1566,7 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="6"/>
+      <c r="P49" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="3"/>
@@ -1590,7 +1584,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="6"/>
+      <c r="P50" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3"/>
@@ -1608,7 +1602,7 @@
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="6"/>
+      <c r="P51" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3"/>
@@ -1626,7 +1620,7 @@
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="6"/>
+      <c r="P52" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3"/>
@@ -1644,7 +1638,7 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
-      <c r="P53" s="6"/>
+      <c r="P53" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3"/>
@@ -1662,7 +1656,7 @@
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="6"/>
+      <c r="P54" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3"/>
@@ -1680,7 +1674,7 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-      <c r="P55" s="6"/>
+      <c r="P55" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="3"/>
@@ -1698,7 +1692,7 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-      <c r="P56" s="6"/>
+      <c r="P56" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3"/>
@@ -1716,7 +1710,7 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
-      <c r="P57" s="6"/>
+      <c r="P57" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3"/>
@@ -1734,7 +1728,7 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="6"/>
+      <c r="P58" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3"/>
@@ -1752,7 +1746,7 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
-      <c r="P59" s="6"/>
+      <c r="P59" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3"/>
@@ -1770,7 +1764,7 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="6"/>
+      <c r="P60" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
       <c r="A61" s="3"/>
@@ -1788,7 +1782,7 @@
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="6"/>
+      <c r="P61" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
       <c r="A62" s="3"/>
@@ -1806,7 +1800,7 @@
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="6"/>
+      <c r="P62" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="3"/>
@@ -1824,7 +1818,7 @@
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
-      <c r="P63" s="6"/>
+      <c r="P63" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="3"/>
@@ -1842,7 +1836,7 @@
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
-      <c r="P64" s="6"/>
+      <c r="P64" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
       <c r="A65" s="3"/>
@@ -1860,7 +1854,7 @@
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
-      <c r="P65" s="6"/>
+      <c r="P65" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
       <c r="A66" s="3"/>
@@ -1878,7 +1872,7 @@
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
-      <c r="P66" s="6"/>
+      <c r="P66" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
       <c r="A67" s="3"/>
@@ -1896,7 +1890,7 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-      <c r="P67" s="6"/>
+      <c r="P67" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
       <c r="A68" s="3"/>
@@ -1914,7 +1908,7 @@
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="6"/>
+      <c r="P68" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
       <c r="A69" s="3"/>
@@ -1932,7 +1926,7 @@
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
-      <c r="P69" s="6"/>
+      <c r="P69" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
       <c r="A70" s="3"/>
@@ -1950,7 +1944,7 @@
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
-      <c r="P70" s="6"/>
+      <c r="P70" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
       <c r="A71" s="3"/>
@@ -1968,7 +1962,7 @@
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
-      <c r="P71" s="6"/>
+      <c r="P71" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
       <c r="A72" s="3"/>
@@ -1986,7 +1980,7 @@
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
-      <c r="P72" s="6"/>
+      <c r="P72" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
       <c r="A73" s="3"/>
@@ -2004,7 +1998,7 @@
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
       <c r="O73" s="3"/>
-      <c r="P73" s="6"/>
+      <c r="P73" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
       <c r="A74" s="3"/>
@@ -2022,7 +2016,7 @@
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
-      <c r="P74" s="6"/>
+      <c r="P74" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
       <c r="A75" s="3"/>
@@ -2040,7 +2034,7 @@
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
-      <c r="P75" s="6"/>
+      <c r="P75" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
       <c r="A76" s="3"/>
@@ -2058,7 +2052,7 @@
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
-      <c r="P76" s="6"/>
+      <c r="P76" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
       <c r="A77" s="3"/>
@@ -2076,7 +2070,7 @@
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
-      <c r="P77" s="6"/>
+      <c r="P77" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
       <c r="A78" s="3"/>
@@ -2094,7 +2088,7 @@
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
-      <c r="P78" s="6"/>
+      <c r="P78" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
       <c r="A79" s="3"/>
@@ -2112,7 +2106,7 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
-      <c r="P79" s="6"/>
+      <c r="P79" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
       <c r="A80" s="3"/>
@@ -2130,7 +2124,7 @@
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
-      <c r="P80" s="6"/>
+      <c r="P80" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
       <c r="A81" s="3"/>
@@ -2148,7 +2142,7 @@
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
-      <c r="P81" s="6"/>
+      <c r="P81" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
       <c r="A82" s="3"/>
@@ -2166,7 +2160,7 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-      <c r="P82" s="6"/>
+      <c r="P82" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
       <c r="A83" s="3"/>
@@ -2184,7 +2178,7 @@
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
-      <c r="P83" s="6"/>
+      <c r="P83" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
       <c r="A84" s="3"/>
@@ -2202,7 +2196,7 @@
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
-      <c r="P84" s="6"/>
+      <c r="P84" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
       <c r="A85" s="3"/>
@@ -2220,7 +2214,7 @@
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
-      <c r="P85" s="6"/>
+      <c r="P85" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
       <c r="A86" s="3"/>
@@ -2238,7 +2232,7 @@
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
-      <c r="P86" s="6"/>
+      <c r="P86" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
       <c r="A87" s="3"/>
@@ -2256,7 +2250,7 @@
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
-      <c r="P87" s="6"/>
+      <c r="P87" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
       <c r="A88" s="3"/>
@@ -2274,7 +2268,7 @@
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
-      <c r="P88" s="6"/>
+      <c r="P88" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
       <c r="A89" s="3"/>
@@ -2292,7 +2286,7 @@
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
-      <c r="P89" s="6"/>
+      <c r="P89" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
       <c r="A90" s="3"/>
@@ -2310,7 +2304,7 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-      <c r="P90" s="6"/>
+      <c r="P90" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
       <c r="A91" s="3"/>
@@ -2328,7 +2322,7 @@
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
-      <c r="P91" s="6"/>
+      <c r="P91" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
       <c r="A92" s="3"/>
@@ -2346,7 +2340,7 @@
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
-      <c r="P92" s="6"/>
+      <c r="P92" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
       <c r="A93" s="3"/>
@@ -2364,7 +2358,7 @@
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
-      <c r="P93" s="6"/>
+      <c r="P93" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
       <c r="A94" s="3"/>
@@ -2382,7 +2376,7 @@
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
-      <c r="P94" s="6"/>
+      <c r="P94" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
       <c r="A95" s="3"/>
@@ -2400,7 +2394,7 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-      <c r="P95" s="6"/>
+      <c r="P95" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
       <c r="A96" s="3"/>
@@ -2418,7 +2412,7 @@
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
-      <c r="P96" s="6"/>
+      <c r="P96" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
       <c r="A97" s="3"/>
@@ -2436,7 +2430,7 @@
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
-      <c r="P97" s="6"/>
+      <c r="P97" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
       <c r="A98" s="3"/>
@@ -2454,7 +2448,7 @@
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
-      <c r="P98" s="6"/>
+      <c r="P98" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
       <c r="A99" s="3"/>
@@ -2472,7 +2466,7 @@
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
-      <c r="P99" s="6"/>
+      <c r="P99" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
       <c r="A100" s="3"/>
@@ -2490,7 +2484,7 @@
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
-      <c r="P100" s="6"/>
+      <c r="P100" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
       <c r="A101" s="3"/>
@@ -2508,7 +2502,7 @@
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
-      <c r="P101" s="6"/>
+      <c r="P101" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
       <c r="A102" s="3"/>
@@ -2526,7 +2520,7 @@
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
-      <c r="P102" s="6"/>
+      <c r="P102" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
       <c r="A103" s="3"/>
@@ -2544,7 +2538,7 @@
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
-      <c r="P103" s="6"/>
+      <c r="P103" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
       <c r="A104" s="3"/>
@@ -2562,7 +2556,7 @@
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
-      <c r="P104" s="6"/>
+      <c r="P104" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
       <c r="A105" s="3"/>
@@ -2580,7 +2574,7 @@
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
-      <c r="P105" s="6"/>
+      <c r="P105" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
       <c r="A106" s="3"/>
@@ -2598,7 +2592,7 @@
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
-      <c r="P106" s="6"/>
+      <c r="P106" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
       <c r="A107" s="3"/>
@@ -2616,7 +2610,7 @@
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
-      <c r="P107" s="6"/>
+      <c r="P107" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
       <c r="A108" s="3"/>
@@ -2634,7 +2628,7 @@
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
-      <c r="P108" s="6"/>
+      <c r="P108" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
       <c r="A109" s="3"/>
@@ -2652,7 +2646,7 @@
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
       <c r="O109" s="3"/>
-      <c r="P109" s="6"/>
+      <c r="P109" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
       <c r="A110" s="3"/>
@@ -2670,7 +2664,7 @@
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
       <c r="O110" s="3"/>
-      <c r="P110" s="6"/>
+      <c r="P110" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
       <c r="A111" s="3"/>
@@ -2688,7 +2682,7 @@
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
       <c r="O111" s="3"/>
-      <c r="P111" s="6"/>
+      <c r="P111" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
       <c r="A112" s="3"/>
@@ -2706,7 +2700,7 @@
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
       <c r="O112" s="3"/>
-      <c r="P112" s="6"/>
+      <c r="P112" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
       <c r="A113" s="3"/>
@@ -2724,7 +2718,7 @@
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
       <c r="O113" s="3"/>
-      <c r="P113" s="6"/>
+      <c r="P113" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
       <c r="A114" s="3"/>
@@ -2742,7 +2736,7 @@
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
       <c r="O114" s="3"/>
-      <c r="P114" s="6"/>
+      <c r="P114" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
       <c r="A115" s="3"/>
@@ -2760,7 +2754,7 @@
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
-      <c r="P115" s="6"/>
+      <c r="P115" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
       <c r="A116" s="3"/>
@@ -2778,7 +2772,7 @@
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
       <c r="O116" s="3"/>
-      <c r="P116" s="6"/>
+      <c r="P116" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
       <c r="A117" s="3"/>
@@ -2796,7 +2790,7 @@
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
       <c r="O117" s="3"/>
-      <c r="P117" s="6"/>
+      <c r="P117" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
       <c r="A118" s="3"/>
@@ -2814,7 +2808,7 @@
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
       <c r="O118" s="3"/>
-      <c r="P118" s="6"/>
+      <c r="P118" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
       <c r="A119" s="3"/>
@@ -2832,7 +2826,7 @@
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
       <c r="O119" s="3"/>
-      <c r="P119" s="6"/>
+      <c r="P119" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
       <c r="A120" s="3"/>
@@ -2850,7 +2844,7 @@
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
-      <c r="P120" s="6"/>
+      <c r="P120" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
       <c r="A121" s="3"/>
@@ -2868,7 +2862,7 @@
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
       <c r="O121" s="3"/>
-      <c r="P121" s="6"/>
+      <c r="P121" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
       <c r="A122" s="3"/>
@@ -2886,7 +2880,7 @@
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
       <c r="O122" s="3"/>
-      <c r="P122" s="6"/>
+      <c r="P122" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
       <c r="A123" s="3"/>
@@ -2904,7 +2898,7 @@
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
-      <c r="P123" s="6"/>
+      <c r="P123" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
       <c r="A124" s="3"/>
@@ -2922,7 +2916,7 @@
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
       <c r="O124" s="3"/>
-      <c r="P124" s="6"/>
+      <c r="P124" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
       <c r="A125" s="3"/>
@@ -2940,7 +2934,7 @@
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
       <c r="O125" s="3"/>
-      <c r="P125" s="6"/>
+      <c r="P125" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
       <c r="A126" s="3"/>
@@ -2958,7 +2952,7 @@
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
       <c r="O126" s="3"/>
-      <c r="P126" s="6"/>
+      <c r="P126" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
       <c r="A127" s="3"/>
@@ -2976,7 +2970,7 @@
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
       <c r="O127" s="3"/>
-      <c r="P127" s="6"/>
+      <c r="P127" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
       <c r="A128" s="3"/>
@@ -2994,7 +2988,7 @@
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
-      <c r="P128" s="6"/>
+      <c r="P128" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
       <c r="A129" s="3"/>
@@ -3012,7 +3006,7 @@
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
-      <c r="P129" s="6"/>
+      <c r="P129" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
       <c r="A130" s="3"/>
@@ -3030,7 +3024,7 @@
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
-      <c r="P130" s="6"/>
+      <c r="P130" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
       <c r="A131" s="3"/>
@@ -3048,7 +3042,7 @@
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
-      <c r="P131" s="6"/>
+      <c r="P131" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
       <c r="A132" s="3"/>
@@ -3066,7 +3060,7 @@
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
-      <c r="P132" s="6"/>
+      <c r="P132" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
       <c r="A133" s="3"/>
@@ -3084,7 +3078,7 @@
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
-      <c r="P133" s="6"/>
+      <c r="P133" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
       <c r="A134" s="3"/>
@@ -3102,7 +3096,7 @@
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
-      <c r="P134" s="6"/>
+      <c r="P134" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
       <c r="A135" s="3"/>
@@ -3120,7 +3114,7 @@
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
-      <c r="P135" s="6"/>
+      <c r="P135" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
       <c r="A136" s="3"/>
@@ -3138,7 +3132,7 @@
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
-      <c r="P136" s="6"/>
+      <c r="P136" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
       <c r="A137" s="3"/>
@@ -3156,7 +3150,7 @@
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
-      <c r="P137" s="6"/>
+      <c r="P137" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
       <c r="A138" s="3"/>
@@ -3174,7 +3168,7 @@
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
-      <c r="P138" s="6"/>
+      <c r="P138" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
       <c r="A139" s="3"/>
@@ -3192,7 +3186,7 @@
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
-      <c r="P139" s="6"/>
+      <c r="P139" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
       <c r="A140" s="3"/>
@@ -3210,7 +3204,7 @@
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
-      <c r="P140" s="6"/>
+      <c r="P140" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
       <c r="A141" s="3"/>
@@ -3228,7 +3222,7 @@
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
-      <c r="P141" s="6"/>
+      <c r="P141" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
       <c r="A142" s="3"/>
@@ -3246,7 +3240,7 @@
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
-      <c r="P142" s="6"/>
+      <c r="P142" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
       <c r="A143" s="3"/>
@@ -3264,7 +3258,7 @@
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
-      <c r="P143" s="6"/>
+      <c r="P143" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
       <c r="A144" s="3"/>
@@ -3282,7 +3276,7 @@
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
-      <c r="P144" s="6"/>
+      <c r="P144" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
       <c r="A145" s="3"/>
@@ -3300,7 +3294,7 @@
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
-      <c r="P145" s="6"/>
+      <c r="P145" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
       <c r="A146" s="3"/>
@@ -3318,7 +3312,7 @@
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
       <c r="O146" s="3"/>
-      <c r="P146" s="6"/>
+      <c r="P146" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
       <c r="A147" s="3"/>
@@ -3336,7 +3330,7 @@
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
-      <c r="P147" s="6"/>
+      <c r="P147" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
       <c r="A148" s="3"/>
@@ -3354,7 +3348,7 @@
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
-      <c r="P148" s="6"/>
+      <c r="P148" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
       <c r="A149" s="3"/>
@@ -3372,7 +3366,7 @@
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
-      <c r="P149" s="6"/>
+      <c r="P149" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
       <c r="A150" s="3"/>
@@ -3390,7 +3384,7 @@
       <c r="M150" s="3"/>
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
-      <c r="P150" s="6"/>
+      <c r="P150" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
       <c r="A151" s="3"/>
@@ -3408,7 +3402,7 @@
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
       <c r="O151" s="3"/>
-      <c r="P151" s="6"/>
+      <c r="P151" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
       <c r="A152" s="3"/>
@@ -3426,7 +3420,7 @@
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
       <c r="O152" s="3"/>
-      <c r="P152" s="6"/>
+      <c r="P152" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
       <c r="A153" s="3"/>
@@ -3444,7 +3438,7 @@
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
-      <c r="P153" s="6"/>
+      <c r="P153" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
       <c r="A154" s="3"/>
@@ -3462,7 +3456,7 @@
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
-      <c r="P154" s="6"/>
+      <c r="P154" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
       <c r="A155" s="3"/>
@@ -3480,7 +3474,7 @@
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
-      <c r="P155" s="6"/>
+      <c r="P155" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
       <c r="A156" s="3"/>
@@ -3498,7 +3492,7 @@
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
       <c r="O156" s="3"/>
-      <c r="P156" s="6"/>
+      <c r="P156" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
       <c r="A157" s="3"/>
@@ -3516,7 +3510,7 @@
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
-      <c r="P157" s="6"/>
+      <c r="P157" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
       <c r="A158" s="3"/>
@@ -3534,7 +3528,7 @@
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
-      <c r="P158" s="6"/>
+      <c r="P158" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
       <c r="A159" s="3"/>
@@ -3552,7 +3546,7 @@
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
-      <c r="P159" s="6"/>
+      <c r="P159" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
       <c r="A160" s="3"/>
@@ -3570,7 +3564,7 @@
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
       <c r="O160" s="3"/>
-      <c r="P160" s="6"/>
+      <c r="P160" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
       <c r="A161" s="3"/>
@@ -3588,7 +3582,7 @@
       <c r="M161" s="3"/>
       <c r="N161" s="3"/>
       <c r="O161" s="3"/>
-      <c r="P161" s="6"/>
+      <c r="P161" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
       <c r="A162" s="3"/>
@@ -3606,7 +3600,7 @@
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
       <c r="O162" s="3"/>
-      <c r="P162" s="6"/>
+      <c r="P162" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
       <c r="A163" s="3"/>
@@ -3624,7 +3618,7 @@
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
       <c r="O163" s="3"/>
-      <c r="P163" s="6"/>
+      <c r="P163" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
       <c r="A164" s="3"/>
@@ -3642,7 +3636,7 @@
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
-      <c r="P164" s="6"/>
+      <c r="P164" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
       <c r="A165" s="3"/>
@@ -3660,7 +3654,7 @@
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
       <c r="O165" s="3"/>
-      <c r="P165" s="6"/>
+      <c r="P165" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
       <c r="A166" s="3"/>
@@ -3678,7 +3672,7 @@
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
-      <c r="P166" s="6"/>
+      <c r="P166" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
       <c r="A167" s="3"/>
@@ -3696,7 +3690,7 @@
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
       <c r="O167" s="3"/>
-      <c r="P167" s="6"/>
+      <c r="P167" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
       <c r="A168" s="3"/>
@@ -3714,7 +3708,7 @@
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
       <c r="O168" s="3"/>
-      <c r="P168" s="6"/>
+      <c r="P168" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
       <c r="A169" s="3"/>
@@ -3732,7 +3726,7 @@
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
       <c r="O169" s="3"/>
-      <c r="P169" s="6"/>
+      <c r="P169" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
       <c r="A170" s="3"/>
@@ -3750,7 +3744,7 @@
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
       <c r="O170" s="3"/>
-      <c r="P170" s="6"/>
+      <c r="P170" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
       <c r="A171" s="3"/>
@@ -3768,7 +3762,7 @@
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
       <c r="O171" s="3"/>
-      <c r="P171" s="6"/>
+      <c r="P171" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
       <c r="A172" s="3"/>
@@ -3786,7 +3780,7 @@
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
       <c r="O172" s="3"/>
-      <c r="P172" s="6"/>
+      <c r="P172" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
       <c r="A173" s="3"/>
@@ -3804,7 +3798,7 @@
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
       <c r="O173" s="3"/>
-      <c r="P173" s="6"/>
+      <c r="P173" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
       <c r="A174" s="3"/>
@@ -3822,7 +3816,7 @@
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
       <c r="O174" s="3"/>
-      <c r="P174" s="6"/>
+      <c r="P174" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
       <c r="A175" s="3"/>
@@ -3840,7 +3834,7 @@
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
       <c r="O175" s="3"/>
-      <c r="P175" s="6"/>
+      <c r="P175" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25">
       <c r="A176" s="3"/>
@@ -3858,7 +3852,7 @@
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
       <c r="O176" s="3"/>
-      <c r="P176" s="6"/>
+      <c r="P176" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25">
       <c r="A177" s="3"/>
@@ -3876,7 +3870,7 @@
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
       <c r="O177" s="3"/>
-      <c r="P177" s="6"/>
+      <c r="P177" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25">
       <c r="A178" s="3"/>
@@ -3894,7 +3888,7 @@
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
       <c r="O178" s="3"/>
-      <c r="P178" s="6"/>
+      <c r="P178" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25">
       <c r="A179" s="3"/>
@@ -3912,7 +3906,7 @@
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
       <c r="O179" s="3"/>
-      <c r="P179" s="6"/>
+      <c r="P179" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
       <c r="A180" s="3"/>
@@ -3930,7 +3924,7 @@
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
       <c r="O180" s="3"/>
-      <c r="P180" s="6"/>
+      <c r="P180" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
       <c r="A181" s="3"/>
@@ -3948,7 +3942,7 @@
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
       <c r="O181" s="3"/>
-      <c r="P181" s="6"/>
+      <c r="P181" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25">
       <c r="A182" s="3"/>
@@ -3966,7 +3960,7 @@
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
       <c r="O182" s="3"/>
-      <c r="P182" s="6"/>
+      <c r="P182" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
       <c r="A183" s="3"/>
@@ -3984,7 +3978,7 @@
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
       <c r="O183" s="3"/>
-      <c r="P183" s="6"/>
+      <c r="P183" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25">
       <c r="A184" s="3"/>
@@ -4002,7 +3996,7 @@
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
       <c r="O184" s="3"/>
-      <c r="P184" s="6"/>
+      <c r="P184" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25">
       <c r="A185" s="3"/>
@@ -4020,7 +4014,7 @@
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
       <c r="O185" s="3"/>
-      <c r="P185" s="6"/>
+      <c r="P185" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25">
       <c r="A186" s="3"/>
@@ -4038,7 +4032,7 @@
       <c r="M186" s="3"/>
       <c r="N186" s="3"/>
       <c r="O186" s="3"/>
-      <c r="P186" s="6"/>
+      <c r="P186" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25">
       <c r="A187" s="3"/>
@@ -4056,7 +4050,7 @@
       <c r="M187" s="3"/>
       <c r="N187" s="3"/>
       <c r="O187" s="3"/>
-      <c r="P187" s="6"/>
+      <c r="P187" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
       <c r="A188" s="3"/>
@@ -4074,7 +4068,7 @@
       <c r="M188" s="3"/>
       <c r="N188" s="3"/>
       <c r="O188" s="3"/>
-      <c r="P188" s="6"/>
+      <c r="P188" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25">
       <c r="A189" s="3"/>
@@ -4092,7 +4086,7 @@
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
       <c r="O189" s="3"/>
-      <c r="P189" s="6"/>
+      <c r="P189" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25">
       <c r="A190" s="3"/>
@@ -4110,7 +4104,7 @@
       <c r="M190" s="3"/>
       <c r="N190" s="3"/>
       <c r="O190" s="3"/>
-      <c r="P190" s="6"/>
+      <c r="P190" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25">
       <c r="A191" s="3"/>
@@ -4128,7 +4122,7 @@
       <c r="M191" s="3"/>
       <c r="N191" s="3"/>
       <c r="O191" s="3"/>
-      <c r="P191" s="6"/>
+      <c r="P191" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25">
       <c r="A192" s="3"/>
@@ -4146,7 +4140,7 @@
       <c r="M192" s="3"/>
       <c r="N192" s="3"/>
       <c r="O192" s="3"/>
-      <c r="P192" s="6"/>
+      <c r="P192" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25">
       <c r="A193" s="3"/>
@@ -4164,7 +4158,7 @@
       <c r="M193" s="3"/>
       <c r="N193" s="3"/>
       <c r="O193" s="3"/>
-      <c r="P193" s="6"/>
+      <c r="P193" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
       <c r="A194" s="3"/>
@@ -4182,7 +4176,7 @@
       <c r="M194" s="3"/>
       <c r="N194" s="3"/>
       <c r="O194" s="3"/>
-      <c r="P194" s="6"/>
+      <c r="P194" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25">
       <c r="A195" s="3"/>
@@ -4200,7 +4194,7 @@
       <c r="M195" s="3"/>
       <c r="N195" s="3"/>
       <c r="O195" s="3"/>
-      <c r="P195" s="6"/>
+      <c r="P195" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
       <c r="A196" s="3"/>
@@ -4218,7 +4212,7 @@
       <c r="M196" s="3"/>
       <c r="N196" s="3"/>
       <c r="O196" s="3"/>
-      <c r="P196" s="6"/>
+      <c r="P196" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25">
       <c r="A197" s="3"/>
@@ -4236,7 +4230,7 @@
       <c r="M197" s="3"/>
       <c r="N197" s="3"/>
       <c r="O197" s="3"/>
-      <c r="P197" s="6"/>
+      <c r="P197" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25">
       <c r="A198" s="3"/>
@@ -4254,7 +4248,7 @@
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
-      <c r="P198" s="6"/>
+      <c r="P198" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
       <c r="A199" s="3"/>
@@ -4272,7 +4266,7 @@
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
-      <c r="P199" s="6"/>
+      <c r="P199" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
       <c r="A200" s="3"/>
@@ -4290,7 +4284,7 @@
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
-      <c r="P200" s="6"/>
+      <c r="P200" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25">
       <c r="A201" s="3"/>
@@ -4308,7 +4302,7 @@
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
       <c r="O201" s="3"/>
-      <c r="P201" s="6"/>
+      <c r="P201" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
       <c r="A202" s="3"/>
@@ -4326,7 +4320,7 @@
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
-      <c r="P202" s="6"/>
+      <c r="P202" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
       <c r="A203" s="3"/>
@@ -4344,7 +4338,7 @@
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
-      <c r="P203" s="6"/>
+      <c r="P203" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
       <c r="A204" s="3"/>
@@ -4362,7 +4356,7 @@
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
       <c r="O204" s="3"/>
-      <c r="P204" s="6"/>
+      <c r="P204" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
       <c r="A205" s="3"/>
@@ -4380,7 +4374,7 @@
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
       <c r="O205" s="3"/>
-      <c r="P205" s="6"/>
+      <c r="P205" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
       <c r="A206" s="3"/>
@@ -4398,7 +4392,7 @@
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
       <c r="O206" s="3"/>
-      <c r="P206" s="6"/>
+      <c r="P206" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
       <c r="A207" s="3"/>
@@ -4416,7 +4410,7 @@
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
       <c r="O207" s="3"/>
-      <c r="P207" s="6"/>
+      <c r="P207" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
       <c r="A208" s="3"/>
@@ -4434,7 +4428,7 @@
       <c r="M208" s="3"/>
       <c r="N208" s="3"/>
       <c r="O208" s="3"/>
-      <c r="P208" s="6"/>
+      <c r="P208" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
       <c r="A209" s="3"/>
@@ -4452,7 +4446,7 @@
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
       <c r="O209" s="3"/>
-      <c r="P209" s="6"/>
+      <c r="P209" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
       <c r="A210" s="3"/>
@@ -4470,7 +4464,7 @@
       <c r="M210" s="3"/>
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
-      <c r="P210" s="6"/>
+      <c r="P210" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
       <c r="A211" s="3"/>
@@ -4488,7 +4482,7 @@
       <c r="M211" s="3"/>
       <c r="N211" s="3"/>
       <c r="O211" s="3"/>
-      <c r="P211" s="6"/>
+      <c r="P211" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
       <c r="A212" s="3"/>
@@ -4506,7 +4500,7 @@
       <c r="M212" s="3"/>
       <c r="N212" s="3"/>
       <c r="O212" s="3"/>
-      <c r="P212" s="6"/>
+      <c r="P212" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
       <c r="A213" s="3"/>
@@ -4524,7 +4518,7 @@
       <c r="M213" s="3"/>
       <c r="N213" s="3"/>
       <c r="O213" s="3"/>
-      <c r="P213" s="6"/>
+      <c r="P213" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
       <c r="A214" s="3"/>
@@ -4542,7 +4536,7 @@
       <c r="M214" s="3"/>
       <c r="N214" s="3"/>
       <c r="O214" s="3"/>
-      <c r="P214" s="6"/>
+      <c r="P214" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
       <c r="A215" s="3"/>
@@ -4560,7 +4554,7 @@
       <c r="M215" s="3"/>
       <c r="N215" s="3"/>
       <c r="O215" s="3"/>
-      <c r="P215" s="6"/>
+      <c r="P215" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
       <c r="A216" s="3"/>
@@ -4578,7 +4572,7 @@
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
       <c r="O216" s="3"/>
-      <c r="P216" s="6"/>
+      <c r="P216" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
       <c r="A217" s="3"/>
@@ -4596,7 +4590,7 @@
       <c r="M217" s="3"/>
       <c r="N217" s="3"/>
       <c r="O217" s="3"/>
-      <c r="P217" s="6"/>
+      <c r="P217" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
       <c r="A218" s="3"/>
@@ -4614,7 +4608,7 @@
       <c r="M218" s="3"/>
       <c r="N218" s="3"/>
       <c r="O218" s="3"/>
-      <c r="P218" s="6"/>
+      <c r="P218" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
       <c r="A219" s="3"/>
@@ -4632,7 +4626,7 @@
       <c r="M219" s="3"/>
       <c r="N219" s="3"/>
       <c r="O219" s="3"/>
-      <c r="P219" s="6"/>
+      <c r="P219" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
       <c r="A220" s="3"/>
@@ -4650,7 +4644,7 @@
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
       <c r="O220" s="3"/>
-      <c r="P220" s="6"/>
+      <c r="P220" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
       <c r="A221" s="3"/>
@@ -4668,7 +4662,7 @@
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
       <c r="O221" s="3"/>
-      <c r="P221" s="6"/>
+      <c r="P221" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
       <c r="A222" s="3"/>
@@ -4686,7 +4680,7 @@
       <c r="M222" s="3"/>
       <c r="N222" s="3"/>
       <c r="O222" s="3"/>
-      <c r="P222" s="6"/>
+      <c r="P222" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
       <c r="A223" s="3"/>
@@ -4704,7 +4698,7 @@
       <c r="M223" s="3"/>
       <c r="N223" s="3"/>
       <c r="O223" s="3"/>
-      <c r="P223" s="6"/>
+      <c r="P223" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
       <c r="A224" s="3"/>
@@ -4722,7 +4716,7 @@
       <c r="M224" s="3"/>
       <c r="N224" s="3"/>
       <c r="O224" s="3"/>
-      <c r="P224" s="6"/>
+      <c r="P224" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
       <c r="A225" s="3"/>
@@ -4740,7 +4734,7 @@
       <c r="M225" s="3"/>
       <c r="N225" s="3"/>
       <c r="O225" s="3"/>
-      <c r="P225" s="6"/>
+      <c r="P225" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25">
       <c r="A226" s="3"/>
@@ -4758,7 +4752,7 @@
       <c r="M226" s="3"/>
       <c r="N226" s="3"/>
       <c r="O226" s="3"/>
-      <c r="P226" s="6"/>
+      <c r="P226" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25">
       <c r="A227" s="3"/>
@@ -4776,7 +4770,7 @@
       <c r="M227" s="3"/>
       <c r="N227" s="3"/>
       <c r="O227" s="3"/>
-      <c r="P227" s="6"/>
+      <c r="P227" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25">
       <c r="A228" s="3"/>
@@ -4794,7 +4788,7 @@
       <c r="M228" s="3"/>
       <c r="N228" s="3"/>
       <c r="O228" s="3"/>
-      <c r="P228" s="6"/>
+      <c r="P228" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25">
       <c r="A229" s="3"/>
@@ -4812,7 +4806,7 @@
       <c r="M229" s="3"/>
       <c r="N229" s="3"/>
       <c r="O229" s="3"/>
-      <c r="P229" s="6"/>
+      <c r="P229" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25">
       <c r="A230" s="3"/>
@@ -4830,7 +4824,7 @@
       <c r="M230" s="3"/>
       <c r="N230" s="3"/>
       <c r="O230" s="3"/>
-      <c r="P230" s="6"/>
+      <c r="P230" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25">
       <c r="A231" s="3"/>
@@ -4848,7 +4842,7 @@
       <c r="M231" s="3"/>
       <c r="N231" s="3"/>
       <c r="O231" s="3"/>
-      <c r="P231" s="6"/>
+      <c r="P231" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
       <c r="A232" s="3"/>
@@ -4866,7 +4860,7 @@
       <c r="M232" s="3"/>
       <c r="N232" s="3"/>
       <c r="O232" s="3"/>
-      <c r="P232" s="6"/>
+      <c r="P232" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25">
       <c r="A233" s="3"/>
@@ -4884,7 +4878,7 @@
       <c r="M233" s="3"/>
       <c r="N233" s="3"/>
       <c r="O233" s="3"/>
-      <c r="P233" s="6"/>
+      <c r="P233" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
       <c r="A234" s="3"/>
@@ -4902,7 +4896,7 @@
       <c r="M234" s="3"/>
       <c r="N234" s="3"/>
       <c r="O234" s="3"/>
-      <c r="P234" s="6"/>
+      <c r="P234" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25">
       <c r="A235" s="3"/>
@@ -4920,7 +4914,7 @@
       <c r="M235" s="3"/>
       <c r="N235" s="3"/>
       <c r="O235" s="3"/>
-      <c r="P235" s="6"/>
+      <c r="P235" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25">
       <c r="A236" s="3"/>
@@ -4938,7 +4932,7 @@
       <c r="M236" s="3"/>
       <c r="N236" s="3"/>
       <c r="O236" s="3"/>
-      <c r="P236" s="6"/>
+      <c r="P236" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
       <c r="A237" s="3"/>
@@ -4956,7 +4950,7 @@
       <c r="M237" s="3"/>
       <c r="N237" s="3"/>
       <c r="O237" s="3"/>
-      <c r="P237" s="6"/>
+      <c r="P237" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25">
       <c r="A238" s="3"/>
@@ -4974,7 +4968,7 @@
       <c r="M238" s="3"/>
       <c r="N238" s="3"/>
       <c r="O238" s="3"/>
-      <c r="P238" s="6"/>
+      <c r="P238" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25">
       <c r="A239" s="3"/>
@@ -4992,7 +4986,7 @@
       <c r="M239" s="3"/>
       <c r="N239" s="3"/>
       <c r="O239" s="3"/>
-      <c r="P239" s="6"/>
+      <c r="P239" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25">
       <c r="A240" s="3"/>
@@ -5010,7 +5004,7 @@
       <c r="M240" s="3"/>
       <c r="N240" s="3"/>
       <c r="O240" s="3"/>
-      <c r="P240" s="6"/>
+      <c r="P240" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25">
       <c r="A241" s="3"/>
@@ -5028,7 +5022,7 @@
       <c r="M241" s="3"/>
       <c r="N241" s="3"/>
       <c r="O241" s="3"/>
-      <c r="P241" s="6"/>
+      <c r="P241" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25">
       <c r="A242" s="3"/>
@@ -5046,7 +5040,7 @@
       <c r="M242" s="3"/>
       <c r="N242" s="3"/>
       <c r="O242" s="3"/>
-      <c r="P242" s="6"/>
+      <c r="P242" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25">
       <c r="A243" s="3"/>
@@ -5064,7 +5058,7 @@
       <c r="M243" s="3"/>
       <c r="N243" s="3"/>
       <c r="O243" s="3"/>
-      <c r="P243" s="6"/>
+      <c r="P243" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25">
       <c r="A244" s="3"/>
@@ -5082,7 +5076,7 @@
       <c r="M244" s="3"/>
       <c r="N244" s="3"/>
       <c r="O244" s="3"/>
-      <c r="P244" s="6"/>
+      <c r="P244" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25">
       <c r="A245" s="3"/>
@@ -5100,7 +5094,7 @@
       <c r="M245" s="3"/>
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
-      <c r="P245" s="6"/>
+      <c r="P245" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25">
       <c r="A246" s="3"/>
@@ -5118,7 +5112,7 @@
       <c r="M246" s="3"/>
       <c r="N246" s="3"/>
       <c r="O246" s="3"/>
-      <c r="P246" s="6"/>
+      <c r="P246" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25">
       <c r="A247" s="3"/>
@@ -5136,7 +5130,7 @@
       <c r="M247" s="3"/>
       <c r="N247" s="3"/>
       <c r="O247" s="3"/>
-      <c r="P247" s="6"/>
+      <c r="P247" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25">
       <c r="A248" s="3"/>
@@ -5154,7 +5148,7 @@
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
       <c r="O248" s="3"/>
-      <c r="P248" s="6"/>
+      <c r="P248" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25">
       <c r="A249" s="3"/>
@@ -5172,7 +5166,7 @@
       <c r="M249" s="3"/>
       <c r="N249" s="3"/>
       <c r="O249" s="3"/>
-      <c r="P249" s="6"/>
+      <c r="P249" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25">
       <c r="A250" s="3"/>
@@ -5190,7 +5184,7 @@
       <c r="M250" s="3"/>
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
-      <c r="P250" s="6"/>
+      <c r="P250" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25">
       <c r="A251" s="3"/>
@@ -5208,7 +5202,7 @@
       <c r="M251" s="3"/>
       <c r="N251" s="3"/>
       <c r="O251" s="3"/>
-      <c r="P251" s="6"/>
+      <c r="P251" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25">
       <c r="A252" s="3"/>
@@ -5226,7 +5220,7 @@
       <c r="M252" s="3"/>
       <c r="N252" s="3"/>
       <c r="O252" s="3"/>
-      <c r="P252" s="6"/>
+      <c r="P252" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25">
       <c r="A253" s="3"/>
@@ -5244,7 +5238,7 @@
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
       <c r="O253" s="3"/>
-      <c r="P253" s="6"/>
+      <c r="P253" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25">
       <c r="A254" s="3"/>
@@ -5262,7 +5256,7 @@
       <c r="M254" s="3"/>
       <c r="N254" s="3"/>
       <c r="O254" s="3"/>
-      <c r="P254" s="6"/>
+      <c r="P254" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25">
       <c r="A255" s="3"/>
@@ -5280,7 +5274,7 @@
       <c r="M255" s="3"/>
       <c r="N255" s="3"/>
       <c r="O255" s="3"/>
-      <c r="P255" s="6"/>
+      <c r="P255" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25">
       <c r="A256" s="3"/>
@@ -5298,7 +5292,7 @@
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
       <c r="O256" s="3"/>
-      <c r="P256" s="6"/>
+      <c r="P256" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25">
       <c r="A257" s="3"/>
@@ -5316,7 +5310,7 @@
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
       <c r="O257" s="3"/>
-      <c r="P257" s="6"/>
+      <c r="P257" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25">
       <c r="A258" s="3"/>
@@ -5334,7 +5328,7 @@
       <c r="M258" s="3"/>
       <c r="N258" s="3"/>
       <c r="O258" s="3"/>
-      <c r="P258" s="6"/>
+      <c r="P258" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25">
       <c r="A259" s="3"/>
@@ -5352,7 +5346,7 @@
       <c r="M259" s="3"/>
       <c r="N259" s="3"/>
       <c r="O259" s="3"/>
-      <c r="P259" s="6"/>
+      <c r="P259" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25">
       <c r="A260" s="3"/>
@@ -5370,7 +5364,7 @@
       <c r="M260" s="3"/>
       <c r="N260" s="3"/>
       <c r="O260" s="3"/>
-      <c r="P260" s="6"/>
+      <c r="P260" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25">
       <c r="A261" s="3"/>
@@ -5388,7 +5382,7 @@
       <c r="M261" s="3"/>
       <c r="N261" s="3"/>
       <c r="O261" s="3"/>
-      <c r="P261" s="6"/>
+      <c r="P261" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25">
       <c r="A262" s="3"/>
@@ -5406,7 +5400,7 @@
       <c r="M262" s="3"/>
       <c r="N262" s="3"/>
       <c r="O262" s="3"/>
-      <c r="P262" s="6"/>
+      <c r="P262" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25">
       <c r="A263" s="3"/>
@@ -5424,7 +5418,7 @@
       <c r="M263" s="3"/>
       <c r="N263" s="3"/>
       <c r="O263" s="3"/>
-      <c r="P263" s="6"/>
+      <c r="P263" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25">
       <c r="A264" s="3"/>
@@ -5442,7 +5436,7 @@
       <c r="M264" s="3"/>
       <c r="N264" s="3"/>
       <c r="O264" s="3"/>
-      <c r="P264" s="6"/>
+      <c r="P264" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25">
       <c r="A265" s="3"/>
@@ -5460,7 +5454,7 @@
       <c r="M265" s="3"/>
       <c r="N265" s="3"/>
       <c r="O265" s="3"/>
-      <c r="P265" s="6"/>
+      <c r="P265" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25">
       <c r="A266" s="3"/>
@@ -5478,7 +5472,7 @@
       <c r="M266" s="3"/>
       <c r="N266" s="3"/>
       <c r="O266" s="3"/>
-      <c r="P266" s="6"/>
+      <c r="P266" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25">
       <c r="A267" s="3"/>
@@ -5496,7 +5490,7 @@
       <c r="M267" s="3"/>
       <c r="N267" s="3"/>
       <c r="O267" s="3"/>
-      <c r="P267" s="6"/>
+      <c r="P267" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25">
       <c r="A268" s="3"/>
@@ -5514,7 +5508,7 @@
       <c r="M268" s="3"/>
       <c r="N268" s="3"/>
       <c r="O268" s="3"/>
-      <c r="P268" s="6"/>
+      <c r="P268" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25">
       <c r="A269" s="3"/>
@@ -5532,7 +5526,7 @@
       <c r="M269" s="3"/>
       <c r="N269" s="3"/>
       <c r="O269" s="3"/>
-      <c r="P269" s="6"/>
+      <c r="P269" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25">
       <c r="A270" s="3"/>
@@ -5550,7 +5544,7 @@
       <c r="M270" s="3"/>
       <c r="N270" s="3"/>
       <c r="O270" s="3"/>
-      <c r="P270" s="6"/>
+      <c r="P270" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25">
       <c r="A271" s="3"/>
@@ -5568,7 +5562,7 @@
       <c r="M271" s="3"/>
       <c r="N271" s="3"/>
       <c r="O271" s="3"/>
-      <c r="P271" s="6"/>
+      <c r="P271" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25">
       <c r="A272" s="3"/>
@@ -5586,7 +5580,7 @@
       <c r="M272" s="3"/>
       <c r="N272" s="3"/>
       <c r="O272" s="3"/>
-      <c r="P272" s="6"/>
+      <c r="P272" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25">
       <c r="A273" s="3"/>
@@ -5604,7 +5598,7 @@
       <c r="M273" s="3"/>
       <c r="N273" s="3"/>
       <c r="O273" s="3"/>
-      <c r="P273" s="6"/>
+      <c r="P273" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25">
       <c r="A274" s="3"/>
@@ -5622,7 +5616,7 @@
       <c r="M274" s="3"/>
       <c r="N274" s="3"/>
       <c r="O274" s="3"/>
-      <c r="P274" s="6"/>
+      <c r="P274" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25">
       <c r="A275" s="3"/>
@@ -5640,7 +5634,7 @@
       <c r="M275" s="3"/>
       <c r="N275" s="3"/>
       <c r="O275" s="3"/>
-      <c r="P275" s="6"/>
+      <c r="P275" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25">
       <c r="A276" s="3"/>
@@ -5658,7 +5652,7 @@
       <c r="M276" s="3"/>
       <c r="N276" s="3"/>
       <c r="O276" s="3"/>
-      <c r="P276" s="6"/>
+      <c r="P276" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25">
       <c r="A277" s="3"/>
@@ -5676,7 +5670,7 @@
       <c r="M277" s="3"/>
       <c r="N277" s="3"/>
       <c r="O277" s="3"/>
-      <c r="P277" s="6"/>
+      <c r="P277" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25">
       <c r="A278" s="3"/>
@@ -5694,7 +5688,7 @@
       <c r="M278" s="3"/>
       <c r="N278" s="3"/>
       <c r="O278" s="3"/>
-      <c r="P278" s="6"/>
+      <c r="P278" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25">
       <c r="A279" s="3"/>
@@ -5712,7 +5706,7 @@
       <c r="M279" s="3"/>
       <c r="N279" s="3"/>
       <c r="O279" s="3"/>
-      <c r="P279" s="6"/>
+      <c r="P279" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25">
       <c r="A280" s="3"/>
@@ -5730,7 +5724,7 @@
       <c r="M280" s="3"/>
       <c r="N280" s="3"/>
       <c r="O280" s="3"/>
-      <c r="P280" s="6"/>
+      <c r="P280" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25">
       <c r="A281" s="3"/>
@@ -5748,7 +5742,7 @@
       <c r="M281" s="3"/>
       <c r="N281" s="3"/>
       <c r="O281" s="3"/>
-      <c r="P281" s="6"/>
+      <c r="P281" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25">
       <c r="A282" s="3"/>
@@ -5766,7 +5760,7 @@
       <c r="M282" s="3"/>
       <c r="N282" s="3"/>
       <c r="O282" s="3"/>
-      <c r="P282" s="6"/>
+      <c r="P282" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25">
       <c r="A283" s="3"/>
@@ -5784,7 +5778,7 @@
       <c r="M283" s="3"/>
       <c r="N283" s="3"/>
       <c r="O283" s="3"/>
-      <c r="P283" s="6"/>
+      <c r="P283" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25">
       <c r="A284" s="3"/>
@@ -5802,7 +5796,7 @@
       <c r="M284" s="3"/>
       <c r="N284" s="3"/>
       <c r="O284" s="3"/>
-      <c r="P284" s="6"/>
+      <c r="P284" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25">
       <c r="A285" s="3"/>
@@ -5820,7 +5814,7 @@
       <c r="M285" s="3"/>
       <c r="N285" s="3"/>
       <c r="O285" s="3"/>
-      <c r="P285" s="6"/>
+      <c r="P285" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25">
       <c r="A286" s="3"/>
@@ -5838,7 +5832,7 @@
       <c r="M286" s="3"/>
       <c r="N286" s="3"/>
       <c r="O286" s="3"/>
-      <c r="P286" s="6"/>
+      <c r="P286" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25">
       <c r="A287" s="3"/>
@@ -5856,7 +5850,7 @@
       <c r="M287" s="3"/>
       <c r="N287" s="3"/>
       <c r="O287" s="3"/>
-      <c r="P287" s="6"/>
+      <c r="P287" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25">
       <c r="A288" s="3"/>
@@ -5874,7 +5868,7 @@
       <c r="M288" s="3"/>
       <c r="N288" s="3"/>
       <c r="O288" s="3"/>
-      <c r="P288" s="6"/>
+      <c r="P288" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25">
       <c r="A289" s="3"/>
@@ -5892,7 +5886,7 @@
       <c r="M289" s="3"/>
       <c r="N289" s="3"/>
       <c r="O289" s="3"/>
-      <c r="P289" s="6"/>
+      <c r="P289" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25">
       <c r="A290" s="3"/>
@@ -5910,7 +5904,7 @@
       <c r="M290" s="3"/>
       <c r="N290" s="3"/>
       <c r="O290" s="3"/>
-      <c r="P290" s="6"/>
+      <c r="P290" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25">
       <c r="A291" s="3"/>
@@ -5928,7 +5922,7 @@
       <c r="M291" s="3"/>
       <c r="N291" s="3"/>
       <c r="O291" s="3"/>
-      <c r="P291" s="6"/>
+      <c r="P291" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25">
       <c r="A292" s="3"/>
@@ -5946,7 +5940,7 @@
       <c r="M292" s="3"/>
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
-      <c r="P292" s="6"/>
+      <c r="P292" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25">
       <c r="A293" s="3"/>
@@ -5964,7 +5958,7 @@
       <c r="M293" s="3"/>
       <c r="N293" s="3"/>
       <c r="O293" s="3"/>
-      <c r="P293" s="6"/>
+      <c r="P293" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25">
       <c r="A294" s="3"/>
@@ -5982,7 +5976,7 @@
       <c r="M294" s="3"/>
       <c r="N294" s="3"/>
       <c r="O294" s="3"/>
-      <c r="P294" s="6"/>
+      <c r="P294" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25">
       <c r="A295" s="3"/>
@@ -6000,7 +5994,7 @@
       <c r="M295" s="3"/>
       <c r="N295" s="3"/>
       <c r="O295" s="3"/>
-      <c r="P295" s="6"/>
+      <c r="P295" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25">
       <c r="A296" s="3"/>
@@ -6018,7 +6012,7 @@
       <c r="M296" s="3"/>
       <c r="N296" s="3"/>
       <c r="O296" s="3"/>
-      <c r="P296" s="6"/>
+      <c r="P296" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25">
       <c r="A297" s="3"/>
@@ -6036,7 +6030,7 @@
       <c r="M297" s="3"/>
       <c r="N297" s="3"/>
       <c r="O297" s="3"/>
-      <c r="P297" s="6"/>
+      <c r="P297" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25">
       <c r="A298" s="3"/>
@@ -6054,7 +6048,7 @@
       <c r="M298" s="3"/>
       <c r="N298" s="3"/>
       <c r="O298" s="3"/>
-      <c r="P298" s="6"/>
+      <c r="P298" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25">
       <c r="A299" s="3"/>
@@ -6072,7 +6066,7 @@
       <c r="M299" s="3"/>
       <c r="N299" s="3"/>
       <c r="O299" s="3"/>
-      <c r="P299" s="6"/>
+      <c r="P299" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25">
       <c r="A300" s="3"/>
@@ -6090,7 +6084,7 @@
       <c r="M300" s="3"/>
       <c r="N300" s="3"/>
       <c r="O300" s="3"/>
-      <c r="P300" s="6"/>
+      <c r="P300" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25">
       <c r="A301" s="3"/>
@@ -6108,7 +6102,7 @@
       <c r="M301" s="3"/>
       <c r="N301" s="3"/>
       <c r="O301" s="3"/>
-      <c r="P301" s="6"/>
+      <c r="P301" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25">
       <c r="A302" s="3"/>
@@ -6126,7 +6120,7 @@
       <c r="M302" s="3"/>
       <c r="N302" s="3"/>
       <c r="O302" s="3"/>
-      <c r="P302" s="6"/>
+      <c r="P302" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25">
       <c r="A303" s="3"/>
@@ -6144,7 +6138,7 @@
       <c r="M303" s="3"/>
       <c r="N303" s="3"/>
       <c r="O303" s="3"/>
-      <c r="P303" s="6"/>
+      <c r="P303" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25">
       <c r="A304" s="3"/>
@@ -6162,7 +6156,7 @@
       <c r="M304" s="3"/>
       <c r="N304" s="3"/>
       <c r="O304" s="3"/>
-      <c r="P304" s="6"/>
+      <c r="P304" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25">
       <c r="A305" s="3"/>
@@ -6180,7 +6174,7 @@
       <c r="M305" s="3"/>
       <c r="N305" s="3"/>
       <c r="O305" s="3"/>
-      <c r="P305" s="6"/>
+      <c r="P305" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25">
       <c r="A306" s="3"/>
@@ -6198,7 +6192,7 @@
       <c r="M306" s="3"/>
       <c r="N306" s="3"/>
       <c r="O306" s="3"/>
-      <c r="P306" s="6"/>
+      <c r="P306" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25">
       <c r="A307" s="3"/>
@@ -6216,7 +6210,7 @@
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
       <c r="O307" s="3"/>
-      <c r="P307" s="6"/>
+      <c r="P307" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25">
       <c r="A308" s="3"/>
@@ -6234,7 +6228,7 @@
       <c r="M308" s="3"/>
       <c r="N308" s="3"/>
       <c r="O308" s="3"/>
-      <c r="P308" s="6"/>
+      <c r="P308" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25">
       <c r="A309" s="3"/>
@@ -6252,7 +6246,7 @@
       <c r="M309" s="3"/>
       <c r="N309" s="3"/>
       <c r="O309" s="3"/>
-      <c r="P309" s="6"/>
+      <c r="P309" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25">
       <c r="A310" s="3"/>
@@ -6270,7 +6264,7 @@
       <c r="M310" s="3"/>
       <c r="N310" s="3"/>
       <c r="O310" s="3"/>
-      <c r="P310" s="6"/>
+      <c r="P310" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25">
       <c r="A311" s="3"/>
@@ -6288,7 +6282,7 @@
       <c r="M311" s="3"/>
       <c r="N311" s="3"/>
       <c r="O311" s="3"/>
-      <c r="P311" s="6"/>
+      <c r="P311" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25">
       <c r="A312" s="3"/>
@@ -6306,7 +6300,7 @@
       <c r="M312" s="3"/>
       <c r="N312" s="3"/>
       <c r="O312" s="3"/>
-      <c r="P312" s="6"/>
+      <c r="P312" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25">
       <c r="A313" s="3"/>
@@ -6324,7 +6318,7 @@
       <c r="M313" s="3"/>
       <c r="N313" s="3"/>
       <c r="O313" s="3"/>
-      <c r="P313" s="6"/>
+      <c r="P313" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25">
       <c r="A314" s="3"/>
@@ -6342,7 +6336,7 @@
       <c r="M314" s="3"/>
       <c r="N314" s="3"/>
       <c r="O314" s="3"/>
-      <c r="P314" s="6"/>
+      <c r="P314" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25">
       <c r="A315" s="3"/>
@@ -6360,7 +6354,7 @@
       <c r="M315" s="3"/>
       <c r="N315" s="3"/>
       <c r="O315" s="3"/>
-      <c r="P315" s="6"/>
+      <c r="P315" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25">
       <c r="A316" s="3"/>
@@ -6378,7 +6372,7 @@
       <c r="M316" s="3"/>
       <c r="N316" s="3"/>
       <c r="O316" s="3"/>
-      <c r="P316" s="6"/>
+      <c r="P316" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25">
       <c r="A317" s="3"/>
@@ -6396,7 +6390,7 @@
       <c r="M317" s="3"/>
       <c r="N317" s="3"/>
       <c r="O317" s="3"/>
-      <c r="P317" s="6"/>
+      <c r="P317" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25">
       <c r="A318" s="3"/>
@@ -6414,7 +6408,7 @@
       <c r="M318" s="3"/>
       <c r="N318" s="3"/>
       <c r="O318" s="3"/>
-      <c r="P318" s="6"/>
+      <c r="P318" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25">
       <c r="A319" s="3"/>
@@ -6432,7 +6426,7 @@
       <c r="M319" s="3"/>
       <c r="N319" s="3"/>
       <c r="O319" s="3"/>
-      <c r="P319" s="6"/>
+      <c r="P319" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25">
       <c r="A320" s="3"/>
@@ -6450,7 +6444,7 @@
       <c r="M320" s="3"/>
       <c r="N320" s="3"/>
       <c r="O320" s="3"/>
-      <c r="P320" s="6"/>
+      <c r="P320" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25">
       <c r="A321" s="3"/>
@@ -6468,7 +6462,7 @@
       <c r="M321" s="3"/>
       <c r="N321" s="3"/>
       <c r="O321" s="3"/>
-      <c r="P321" s="6"/>
+      <c r="P321" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25">
       <c r="A322" s="3"/>
@@ -6486,7 +6480,7 @@
       <c r="M322" s="3"/>
       <c r="N322" s="3"/>
       <c r="O322" s="3"/>
-      <c r="P322" s="6"/>
+      <c r="P322" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25">
       <c r="A323" s="3"/>
@@ -6504,7 +6498,7 @@
       <c r="M323" s="3"/>
       <c r="N323" s="3"/>
       <c r="O323" s="3"/>
-      <c r="P323" s="6"/>
+      <c r="P323" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25">
       <c r="A324" s="3"/>
@@ -6522,7 +6516,7 @@
       <c r="M324" s="3"/>
       <c r="N324" s="3"/>
       <c r="O324" s="3"/>
-      <c r="P324" s="6"/>
+      <c r="P324" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25">
       <c r="A325" s="3"/>
@@ -6540,7 +6534,7 @@
       <c r="M325" s="3"/>
       <c r="N325" s="3"/>
       <c r="O325" s="3"/>
-      <c r="P325" s="6"/>
+      <c r="P325" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25">
       <c r="A326" s="3"/>
@@ -6558,7 +6552,7 @@
       <c r="M326" s="3"/>
       <c r="N326" s="3"/>
       <c r="O326" s="3"/>
-      <c r="P326" s="6"/>
+      <c r="P326" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25">
       <c r="A327" s="3"/>
@@ -6576,7 +6570,7 @@
       <c r="M327" s="3"/>
       <c r="N327" s="3"/>
       <c r="O327" s="3"/>
-      <c r="P327" s="6"/>
+      <c r="P327" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25">
       <c r="A328" s="3"/>
@@ -6594,7 +6588,7 @@
       <c r="M328" s="3"/>
       <c r="N328" s="3"/>
       <c r="O328" s="3"/>
-      <c r="P328" s="6"/>
+      <c r="P328" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25">
       <c r="A329" s="3"/>
@@ -6612,7 +6606,7 @@
       <c r="M329" s="3"/>
       <c r="N329" s="3"/>
       <c r="O329" s="3"/>
-      <c r="P329" s="6"/>
+      <c r="P329" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25">
       <c r="A330" s="3"/>
@@ -6630,7 +6624,7 @@
       <c r="M330" s="3"/>
       <c r="N330" s="3"/>
       <c r="O330" s="3"/>
-      <c r="P330" s="6"/>
+      <c r="P330" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25">
       <c r="A331" s="3"/>
@@ -6648,7 +6642,7 @@
       <c r="M331" s="3"/>
       <c r="N331" s="3"/>
       <c r="O331" s="3"/>
-      <c r="P331" s="6"/>
+      <c r="P331" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25">
       <c r="A332" s="3"/>
@@ -6666,7 +6660,7 @@
       <c r="M332" s="3"/>
       <c r="N332" s="3"/>
       <c r="O332" s="3"/>
-      <c r="P332" s="6"/>
+      <c r="P332" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25">
       <c r="A333" s="3"/>
@@ -6684,7 +6678,7 @@
       <c r="M333" s="3"/>
       <c r="N333" s="3"/>
       <c r="O333" s="3"/>
-      <c r="P333" s="6"/>
+      <c r="P333" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25">
       <c r="A334" s="3"/>
@@ -6702,7 +6696,7 @@
       <c r="M334" s="3"/>
       <c r="N334" s="3"/>
       <c r="O334" s="3"/>
-      <c r="P334" s="6"/>
+      <c r="P334" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25">
       <c r="A335" s="3"/>
@@ -6720,7 +6714,7 @@
       <c r="M335" s="3"/>
       <c r="N335" s="3"/>
       <c r="O335" s="3"/>
-      <c r="P335" s="6"/>
+      <c r="P335" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25">
       <c r="A336" s="3"/>
@@ -6738,7 +6732,7 @@
       <c r="M336" s="3"/>
       <c r="N336" s="3"/>
       <c r="O336" s="3"/>
-      <c r="P336" s="6"/>
+      <c r="P336" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25">
       <c r="A337" s="3"/>
@@ -6756,7 +6750,7 @@
       <c r="M337" s="3"/>
       <c r="N337" s="3"/>
       <c r="O337" s="3"/>
-      <c r="P337" s="6"/>
+      <c r="P337" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25">
       <c r="A338" s="3"/>
@@ -6774,7 +6768,7 @@
       <c r="M338" s="3"/>
       <c r="N338" s="3"/>
       <c r="O338" s="3"/>
-      <c r="P338" s="6"/>
+      <c r="P338" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25">
       <c r="A339" s="3"/>
@@ -6792,7 +6786,7 @@
       <c r="M339" s="3"/>
       <c r="N339" s="3"/>
       <c r="O339" s="3"/>
-      <c r="P339" s="6"/>
+      <c r="P339" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25">
       <c r="A340" s="3"/>
@@ -6810,7 +6804,7 @@
       <c r="M340" s="3"/>
       <c r="N340" s="3"/>
       <c r="O340" s="3"/>
-      <c r="P340" s="6"/>
+      <c r="P340" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25">
       <c r="A341" s="3"/>
@@ -6828,7 +6822,7 @@
       <c r="M341" s="3"/>
       <c r="N341" s="3"/>
       <c r="O341" s="3"/>
-      <c r="P341" s="6"/>
+      <c r="P341" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25">
       <c r="A342" s="3"/>
@@ -6846,7 +6840,7 @@
       <c r="M342" s="3"/>
       <c r="N342" s="3"/>
       <c r="O342" s="3"/>
-      <c r="P342" s="6"/>
+      <c r="P342" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25">
       <c r="A343" s="3"/>
@@ -6864,7 +6858,7 @@
       <c r="M343" s="3"/>
       <c r="N343" s="3"/>
       <c r="O343" s="3"/>
-      <c r="P343" s="6"/>
+      <c r="P343" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25">
       <c r="A344" s="3"/>
@@ -6882,7 +6876,7 @@
       <c r="M344" s="3"/>
       <c r="N344" s="3"/>
       <c r="O344" s="3"/>
-      <c r="P344" s="6"/>
+      <c r="P344" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25">
       <c r="A345" s="3"/>
@@ -6900,7 +6894,7 @@
       <c r="M345" s="3"/>
       <c r="N345" s="3"/>
       <c r="O345" s="3"/>
-      <c r="P345" s="6"/>
+      <c r="P345" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25">
       <c r="A346" s="3"/>
@@ -6918,7 +6912,7 @@
       <c r="M346" s="3"/>
       <c r="N346" s="3"/>
       <c r="O346" s="3"/>
-      <c r="P346" s="6"/>
+      <c r="P346" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25">
       <c r="A347" s="3"/>
@@ -6936,7 +6930,7 @@
       <c r="M347" s="3"/>
       <c r="N347" s="3"/>
       <c r="O347" s="3"/>
-      <c r="P347" s="6"/>
+      <c r="P347" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25">
       <c r="A348" s="3"/>
@@ -6954,7 +6948,7 @@
       <c r="M348" s="3"/>
       <c r="N348" s="3"/>
       <c r="O348" s="3"/>
-      <c r="P348" s="6"/>
+      <c r="P348" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25">
       <c r="A349" s="3"/>
@@ -6972,7 +6966,7 @@
       <c r="M349" s="3"/>
       <c r="N349" s="3"/>
       <c r="O349" s="3"/>
-      <c r="P349" s="6"/>
+      <c r="P349" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25">
       <c r="A350" s="3"/>
@@ -6990,7 +6984,7 @@
       <c r="M350" s="3"/>
       <c r="N350" s="3"/>
       <c r="O350" s="3"/>
-      <c r="P350" s="6"/>
+      <c r="P350" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25">
       <c r="A351" s="3"/>
@@ -7008,7 +7002,7 @@
       <c r="M351" s="3"/>
       <c r="N351" s="3"/>
       <c r="O351" s="3"/>
-      <c r="P351" s="6"/>
+      <c r="P351" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25">
       <c r="A352" s="3"/>
@@ -7026,7 +7020,7 @@
       <c r="M352" s="3"/>
       <c r="N352" s="3"/>
       <c r="O352" s="3"/>
-      <c r="P352" s="6"/>
+      <c r="P352" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25">
       <c r="A353" s="3"/>
@@ -7044,7 +7038,7 @@
       <c r="M353" s="3"/>
       <c r="N353" s="3"/>
       <c r="O353" s="3"/>
-      <c r="P353" s="6"/>
+      <c r="P353" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25">
       <c r="A354" s="3"/>
@@ -7062,7 +7056,7 @@
       <c r="M354" s="3"/>
       <c r="N354" s="3"/>
       <c r="O354" s="3"/>
-      <c r="P354" s="6"/>
+      <c r="P354" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25">
       <c r="A355" s="3"/>
@@ -7080,7 +7074,7 @@
       <c r="M355" s="3"/>
       <c r="N355" s="3"/>
       <c r="O355" s="3"/>
-      <c r="P355" s="6"/>
+      <c r="P355" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25">
       <c r="A356" s="3"/>
@@ -7098,7 +7092,7 @@
       <c r="M356" s="3"/>
       <c r="N356" s="3"/>
       <c r="O356" s="3"/>
-      <c r="P356" s="6"/>
+      <c r="P356" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25">
       <c r="A357" s="3"/>
@@ -7116,7 +7110,7 @@
       <c r="M357" s="3"/>
       <c r="N357" s="3"/>
       <c r="O357" s="3"/>
-      <c r="P357" s="6"/>
+      <c r="P357" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25">
       <c r="A358" s="3"/>
@@ -7134,7 +7128,7 @@
       <c r="M358" s="3"/>
       <c r="N358" s="3"/>
       <c r="O358" s="3"/>
-      <c r="P358" s="6"/>
+      <c r="P358" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25">
       <c r="A359" s="3"/>
@@ -7152,7 +7146,7 @@
       <c r="M359" s="3"/>
       <c r="N359" s="3"/>
       <c r="O359" s="3"/>
-      <c r="P359" s="6"/>
+      <c r="P359" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25">
       <c r="A360" s="3"/>
@@ -7170,7 +7164,7 @@
       <c r="M360" s="3"/>
       <c r="N360" s="3"/>
       <c r="O360" s="3"/>
-      <c r="P360" s="6"/>
+      <c r="P360" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25">
       <c r="A361" s="3"/>
@@ -7188,7 +7182,7 @@
       <c r="M361" s="3"/>
       <c r="N361" s="3"/>
       <c r="O361" s="3"/>
-      <c r="P361" s="6"/>
+      <c r="P361" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25">
       <c r="A362" s="3"/>
@@ -7206,7 +7200,7 @@
       <c r="M362" s="3"/>
       <c r="N362" s="3"/>
       <c r="O362" s="3"/>
-      <c r="P362" s="6"/>
+      <c r="P362" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25">
       <c r="A363" s="3"/>
@@ -7224,7 +7218,7 @@
       <c r="M363" s="3"/>
       <c r="N363" s="3"/>
       <c r="O363" s="3"/>
-      <c r="P363" s="6"/>
+      <c r="P363" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25">
       <c r="A364" s="3"/>
@@ -7242,7 +7236,7 @@
       <c r="M364" s="3"/>
       <c r="N364" s="3"/>
       <c r="O364" s="3"/>
-      <c r="P364" s="6"/>
+      <c r="P364" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25">
       <c r="A365" s="3"/>
@@ -7260,7 +7254,7 @@
       <c r="M365" s="3"/>
       <c r="N365" s="3"/>
       <c r="O365" s="3"/>
-      <c r="P365" s="6"/>
+      <c r="P365" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25">
       <c r="A366" s="3"/>
@@ -7278,7 +7272,7 @@
       <c r="M366" s="3"/>
       <c r="N366" s="3"/>
       <c r="O366" s="3"/>
-      <c r="P366" s="6"/>
+      <c r="P366" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25">
       <c r="A367" s="3"/>
@@ -7296,7 +7290,7 @@
       <c r="M367" s="3"/>
       <c r="N367" s="3"/>
       <c r="O367" s="3"/>
-      <c r="P367" s="6"/>
+      <c r="P367" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25">
       <c r="A368" s="3"/>
@@ -7314,7 +7308,7 @@
       <c r="M368" s="3"/>
       <c r="N368" s="3"/>
       <c r="O368" s="3"/>
-      <c r="P368" s="6"/>
+      <c r="P368" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25">
       <c r="A369" s="3"/>
@@ -7332,7 +7326,7 @@
       <c r="M369" s="3"/>
       <c r="N369" s="3"/>
       <c r="O369" s="3"/>
-      <c r="P369" s="6"/>
+      <c r="P369" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25">
       <c r="A370" s="3"/>
@@ -7350,7 +7344,7 @@
       <c r="M370" s="3"/>
       <c r="N370" s="3"/>
       <c r="O370" s="3"/>
-      <c r="P370" s="6"/>
+      <c r="P370" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25">
       <c r="A371" s="3"/>
@@ -7368,7 +7362,7 @@
       <c r="M371" s="3"/>
       <c r="N371" s="3"/>
       <c r="O371" s="3"/>
-      <c r="P371" s="6"/>
+      <c r="P371" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25">
       <c r="A372" s="3"/>
@@ -7386,7 +7380,7 @@
       <c r="M372" s="3"/>
       <c r="N372" s="3"/>
       <c r="O372" s="3"/>
-      <c r="P372" s="6"/>
+      <c r="P372" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25">
       <c r="A373" s="3"/>
@@ -7404,7 +7398,7 @@
       <c r="M373" s="3"/>
       <c r="N373" s="3"/>
       <c r="O373" s="3"/>
-      <c r="P373" s="6"/>
+      <c r="P373" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25">
       <c r="A374" s="3"/>
@@ -7422,7 +7416,7 @@
       <c r="M374" s="3"/>
       <c r="N374" s="3"/>
       <c r="O374" s="3"/>
-      <c r="P374" s="6"/>
+      <c r="P374" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25">
       <c r="A375" s="3"/>
@@ -7440,7 +7434,7 @@
       <c r="M375" s="3"/>
       <c r="N375" s="3"/>
       <c r="O375" s="3"/>
-      <c r="P375" s="6"/>
+      <c r="P375" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25">
       <c r="A376" s="3"/>
@@ -7458,7 +7452,7 @@
       <c r="M376" s="3"/>
       <c r="N376" s="3"/>
       <c r="O376" s="3"/>
-      <c r="P376" s="6"/>
+      <c r="P376" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25">
       <c r="A377" s="3"/>
@@ -7476,7 +7470,7 @@
       <c r="M377" s="3"/>
       <c r="N377" s="3"/>
       <c r="O377" s="3"/>
-      <c r="P377" s="6"/>
+      <c r="P377" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25">
       <c r="A378" s="3"/>
@@ -7494,7 +7488,7 @@
       <c r="M378" s="3"/>
       <c r="N378" s="3"/>
       <c r="O378" s="3"/>
-      <c r="P378" s="6"/>
+      <c r="P378" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25">
       <c r="A379" s="3"/>
@@ -7512,7 +7506,7 @@
       <c r="M379" s="3"/>
       <c r="N379" s="3"/>
       <c r="O379" s="3"/>
-      <c r="P379" s="6"/>
+      <c r="P379" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25">
       <c r="A380" s="3"/>
@@ -7530,7 +7524,7 @@
       <c r="M380" s="3"/>
       <c r="N380" s="3"/>
       <c r="O380" s="3"/>
-      <c r="P380" s="6"/>
+      <c r="P380" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25">
       <c r="A381" s="3"/>
@@ -7548,7 +7542,7 @@
       <c r="M381" s="3"/>
       <c r="N381" s="3"/>
       <c r="O381" s="3"/>
-      <c r="P381" s="6"/>
+      <c r="P381" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25">
       <c r="A382" s="3"/>
@@ -7566,7 +7560,7 @@
       <c r="M382" s="3"/>
       <c r="N382" s="3"/>
       <c r="O382" s="3"/>
-      <c r="P382" s="6"/>
+      <c r="P382" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25">
       <c r="A383" s="3"/>
@@ -7584,7 +7578,7 @@
       <c r="M383" s="3"/>
       <c r="N383" s="3"/>
       <c r="O383" s="3"/>
-      <c r="P383" s="6"/>
+      <c r="P383" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25">
       <c r="A384" s="3"/>
@@ -7602,7 +7596,7 @@
       <c r="M384" s="3"/>
       <c r="N384" s="3"/>
       <c r="O384" s="3"/>
-      <c r="P384" s="6"/>
+      <c r="P384" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25">
       <c r="A385" s="3"/>
@@ -7620,7 +7614,7 @@
       <c r="M385" s="3"/>
       <c r="N385" s="3"/>
       <c r="O385" s="3"/>
-      <c r="P385" s="6"/>
+      <c r="P385" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25">
       <c r="A386" s="3"/>
@@ -7638,7 +7632,7 @@
       <c r="M386" s="3"/>
       <c r="N386" s="3"/>
       <c r="O386" s="3"/>
-      <c r="P386" s="6"/>
+      <c r="P386" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25">
       <c r="A387" s="3"/>
@@ -7656,7 +7650,7 @@
       <c r="M387" s="3"/>
       <c r="N387" s="3"/>
       <c r="O387" s="3"/>
-      <c r="P387" s="6"/>
+      <c r="P387" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25">
       <c r="A388" s="3"/>
@@ -7674,7 +7668,7 @@
       <c r="M388" s="3"/>
       <c r="N388" s="3"/>
       <c r="O388" s="3"/>
-      <c r="P388" s="6"/>
+      <c r="P388" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25">
       <c r="A389" s="3"/>
@@ -7692,7 +7686,7 @@
       <c r="M389" s="3"/>
       <c r="N389" s="3"/>
       <c r="O389" s="3"/>
-      <c r="P389" s="6"/>
+      <c r="P389" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25">
       <c r="A390" s="3"/>
@@ -7710,7 +7704,7 @@
       <c r="M390" s="3"/>
       <c r="N390" s="3"/>
       <c r="O390" s="3"/>
-      <c r="P390" s="6"/>
+      <c r="P390" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25">
       <c r="A391" s="3"/>
@@ -7728,7 +7722,7 @@
       <c r="M391" s="3"/>
       <c r="N391" s="3"/>
       <c r="O391" s="3"/>
-      <c r="P391" s="6"/>
+      <c r="P391" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25">
       <c r="A392" s="3"/>
@@ -7746,7 +7740,7 @@
       <c r="M392" s="3"/>
       <c r="N392" s="3"/>
       <c r="O392" s="3"/>
-      <c r="P392" s="6"/>
+      <c r="P392" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25">
       <c r="A393" s="3"/>
@@ -7764,7 +7758,7 @@
       <c r="M393" s="3"/>
       <c r="N393" s="3"/>
       <c r="O393" s="3"/>
-      <c r="P393" s="6"/>
+      <c r="P393" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25">
       <c r="A394" s="3"/>
@@ -7782,7 +7776,7 @@
       <c r="M394" s="3"/>
       <c r="N394" s="3"/>
       <c r="O394" s="3"/>
-      <c r="P394" s="6"/>
+      <c r="P394" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25">
       <c r="A395" s="3"/>
@@ -7800,7 +7794,7 @@
       <c r="M395" s="3"/>
       <c r="N395" s="3"/>
       <c r="O395" s="3"/>
-      <c r="P395" s="6"/>
+      <c r="P395" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25">
       <c r="A396" s="3"/>
@@ -7818,7 +7812,7 @@
       <c r="M396" s="3"/>
       <c r="N396" s="3"/>
       <c r="O396" s="3"/>
-      <c r="P396" s="6"/>
+      <c r="P396" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25">
       <c r="A397" s="3"/>
@@ -7836,7 +7830,7 @@
       <c r="M397" s="3"/>
       <c r="N397" s="3"/>
       <c r="O397" s="3"/>
-      <c r="P397" s="6"/>
+      <c r="P397" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25">
       <c r="A398" s="3"/>
@@ -7854,7 +7848,7 @@
       <c r="M398" s="3"/>
       <c r="N398" s="3"/>
       <c r="O398" s="3"/>
-      <c r="P398" s="6"/>
+      <c r="P398" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25">
       <c r="A399" s="3"/>
@@ -7872,7 +7866,7 @@
       <c r="M399" s="3"/>
       <c r="N399" s="3"/>
       <c r="O399" s="3"/>
-      <c r="P399" s="6"/>
+      <c r="P399" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25">
       <c r="A400" s="3"/>
@@ -7890,7 +7884,7 @@
       <c r="M400" s="3"/>
       <c r="N400" s="3"/>
       <c r="O400" s="3"/>
-      <c r="P400" s="6"/>
+      <c r="P400" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25">
       <c r="A401" s="3"/>
@@ -7908,7 +7902,7 @@
       <c r="M401" s="3"/>
       <c r="N401" s="3"/>
       <c r="O401" s="3"/>
-      <c r="P401" s="6"/>
+      <c r="P401" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25">
       <c r="A402" s="3"/>
@@ -7926,7 +7920,7 @@
       <c r="M402" s="3"/>
       <c r="N402" s="3"/>
       <c r="O402" s="3"/>
-      <c r="P402" s="6"/>
+      <c r="P402" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25">
       <c r="A403" s="3"/>
@@ -7944,7 +7938,7 @@
       <c r="M403" s="3"/>
       <c r="N403" s="3"/>
       <c r="O403" s="3"/>
-      <c r="P403" s="6"/>
+      <c r="P403" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25">
       <c r="A404" s="3"/>
@@ -7962,7 +7956,7 @@
       <c r="M404" s="3"/>
       <c r="N404" s="3"/>
       <c r="O404" s="3"/>
-      <c r="P404" s="6"/>
+      <c r="P404" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25">
       <c r="A405" s="3"/>
@@ -7980,7 +7974,7 @@
       <c r="M405" s="3"/>
       <c r="N405" s="3"/>
       <c r="O405" s="3"/>
-      <c r="P405" s="6"/>
+      <c r="P405" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25">
       <c r="A406" s="3"/>
@@ -7998,7 +7992,7 @@
       <c r="M406" s="3"/>
       <c r="N406" s="3"/>
       <c r="O406" s="3"/>
-      <c r="P406" s="6"/>
+      <c r="P406" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25">
       <c r="A407" s="3"/>
@@ -8016,7 +8010,7 @@
       <c r="M407" s="3"/>
       <c r="N407" s="3"/>
       <c r="O407" s="3"/>
-      <c r="P407" s="6"/>
+      <c r="P407" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25">
       <c r="A408" s="3"/>
@@ -8034,7 +8028,7 @@
       <c r="M408" s="3"/>
       <c r="N408" s="3"/>
       <c r="O408" s="3"/>
-      <c r="P408" s="6"/>
+      <c r="P408" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25">
       <c r="A409" s="3"/>
@@ -8052,7 +8046,7 @@
       <c r="M409" s="3"/>
       <c r="N409" s="3"/>
       <c r="O409" s="3"/>
-      <c r="P409" s="6"/>
+      <c r="P409" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25">
       <c r="A410" s="3"/>
@@ -8070,7 +8064,7 @@
       <c r="M410" s="3"/>
       <c r="N410" s="3"/>
       <c r="O410" s="3"/>
-      <c r="P410" s="6"/>
+      <c r="P410" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25">
       <c r="A411" s="3"/>
@@ -8088,7 +8082,7 @@
       <c r="M411" s="3"/>
       <c r="N411" s="3"/>
       <c r="O411" s="3"/>
-      <c r="P411" s="6"/>
+      <c r="P411" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25">
       <c r="A412" s="3"/>
@@ -8106,7 +8100,7 @@
       <c r="M412" s="3"/>
       <c r="N412" s="3"/>
       <c r="O412" s="3"/>
-      <c r="P412" s="6"/>
+      <c r="P412" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25">
       <c r="A413" s="3"/>
@@ -8124,7 +8118,7 @@
       <c r="M413" s="3"/>
       <c r="N413" s="3"/>
       <c r="O413" s="3"/>
-      <c r="P413" s="6"/>
+      <c r="P413" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25">
       <c r="A414" s="3"/>
@@ -8142,7 +8136,7 @@
       <c r="M414" s="3"/>
       <c r="N414" s="3"/>
       <c r="O414" s="3"/>
-      <c r="P414" s="6"/>
+      <c r="P414" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25">
       <c r="A415" s="3"/>
@@ -8160,7 +8154,7 @@
       <c r="M415" s="3"/>
       <c r="N415" s="3"/>
       <c r="O415" s="3"/>
-      <c r="P415" s="6"/>
+      <c r="P415" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25">
       <c r="A416" s="3"/>
@@ -8178,7 +8172,7 @@
       <c r="M416" s="3"/>
       <c r="N416" s="3"/>
       <c r="O416" s="3"/>
-      <c r="P416" s="6"/>
+      <c r="P416" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25">
       <c r="A417" s="3"/>
@@ -8196,7 +8190,7 @@
       <c r="M417" s="3"/>
       <c r="N417" s="3"/>
       <c r="O417" s="3"/>
-      <c r="P417" s="6"/>
+      <c r="P417" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25">
       <c r="A418" s="3"/>
@@ -8214,7 +8208,7 @@
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
       <c r="O418" s="3"/>
-      <c r="P418" s="6"/>
+      <c r="P418" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25">
       <c r="A419" s="3"/>
@@ -8232,7 +8226,7 @@
       <c r="M419" s="3"/>
       <c r="N419" s="3"/>
       <c r="O419" s="3"/>
-      <c r="P419" s="6"/>
+      <c r="P419" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25">
       <c r="A420" s="3"/>
@@ -8250,7 +8244,7 @@
       <c r="M420" s="3"/>
       <c r="N420" s="3"/>
       <c r="O420" s="3"/>
-      <c r="P420" s="6"/>
+      <c r="P420" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25">
       <c r="A421" s="3"/>
@@ -8268,7 +8262,7 @@
       <c r="M421" s="3"/>
       <c r="N421" s="3"/>
       <c r="O421" s="3"/>
-      <c r="P421" s="6"/>
+      <c r="P421" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25">
       <c r="A422" s="3"/>
@@ -8286,7 +8280,7 @@
       <c r="M422" s="3"/>
       <c r="N422" s="3"/>
       <c r="O422" s="3"/>
-      <c r="P422" s="6"/>
+      <c r="P422" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25">
       <c r="A423" s="3"/>
@@ -8304,7 +8298,7 @@
       <c r="M423" s="3"/>
       <c r="N423" s="3"/>
       <c r="O423" s="3"/>
-      <c r="P423" s="6"/>
+      <c r="P423" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25">
       <c r="A424" s="3"/>
@@ -8322,7 +8316,7 @@
       <c r="M424" s="3"/>
       <c r="N424" s="3"/>
       <c r="O424" s="3"/>
-      <c r="P424" s="6"/>
+      <c r="P424" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25">
       <c r="A425" s="3"/>
@@ -8340,7 +8334,7 @@
       <c r="M425" s="3"/>
       <c r="N425" s="3"/>
       <c r="O425" s="3"/>
-      <c r="P425" s="6"/>
+      <c r="P425" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25">
       <c r="A426" s="3"/>
@@ -8358,7 +8352,7 @@
       <c r="M426" s="3"/>
       <c r="N426" s="3"/>
       <c r="O426" s="3"/>
-      <c r="P426" s="6"/>
+      <c r="P426" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25">
       <c r="A427" s="3"/>
@@ -8376,7 +8370,7 @@
       <c r="M427" s="3"/>
       <c r="N427" s="3"/>
       <c r="O427" s="3"/>
-      <c r="P427" s="6"/>
+      <c r="P427" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25">
       <c r="A428" s="3"/>
@@ -8394,7 +8388,7 @@
       <c r="M428" s="3"/>
       <c r="N428" s="3"/>
       <c r="O428" s="3"/>
-      <c r="P428" s="6"/>
+      <c r="P428" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25">
       <c r="A429" s="3"/>
@@ -8412,7 +8406,7 @@
       <c r="M429" s="3"/>
       <c r="N429" s="3"/>
       <c r="O429" s="3"/>
-      <c r="P429" s="6"/>
+      <c r="P429" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25">
       <c r="A430" s="3"/>
@@ -8430,7 +8424,7 @@
       <c r="M430" s="3"/>
       <c r="N430" s="3"/>
       <c r="O430" s="3"/>
-      <c r="P430" s="6"/>
+      <c r="P430" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25">
       <c r="A431" s="3"/>
@@ -8448,7 +8442,7 @@
       <c r="M431" s="3"/>
       <c r="N431" s="3"/>
       <c r="O431" s="3"/>
-      <c r="P431" s="6"/>
+      <c r="P431" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25">
       <c r="A432" s="3"/>
@@ -8466,7 +8460,7 @@
       <c r="M432" s="3"/>
       <c r="N432" s="3"/>
       <c r="O432" s="3"/>
-      <c r="P432" s="6"/>
+      <c r="P432" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25">
       <c r="A433" s="3"/>
@@ -8484,7 +8478,7 @@
       <c r="M433" s="3"/>
       <c r="N433" s="3"/>
       <c r="O433" s="3"/>
-      <c r="P433" s="6"/>
+      <c r="P433" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25">
       <c r="A434" s="3"/>
@@ -8502,7 +8496,7 @@
       <c r="M434" s="3"/>
       <c r="N434" s="3"/>
       <c r="O434" s="3"/>
-      <c r="P434" s="6"/>
+      <c r="P434" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25">
       <c r="A435" s="3"/>
@@ -8520,7 +8514,7 @@
       <c r="M435" s="3"/>
       <c r="N435" s="3"/>
       <c r="O435" s="3"/>
-      <c r="P435" s="6"/>
+      <c r="P435" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25">
       <c r="A436" s="3"/>
@@ -8538,7 +8532,7 @@
       <c r="M436" s="3"/>
       <c r="N436" s="3"/>
       <c r="O436" s="3"/>
-      <c r="P436" s="6"/>
+      <c r="P436" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25">
       <c r="A437" s="3"/>
@@ -8556,7 +8550,7 @@
       <c r="M437" s="3"/>
       <c r="N437" s="3"/>
       <c r="O437" s="3"/>
-      <c r="P437" s="6"/>
+      <c r="P437" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25">
       <c r="A438" s="3"/>
@@ -8574,7 +8568,7 @@
       <c r="M438" s="3"/>
       <c r="N438" s="3"/>
       <c r="O438" s="3"/>
-      <c r="P438" s="6"/>
+      <c r="P438" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25">
       <c r="A439" s="3"/>
@@ -8592,7 +8586,7 @@
       <c r="M439" s="3"/>
       <c r="N439" s="3"/>
       <c r="O439" s="3"/>
-      <c r="P439" s="6"/>
+      <c r="P439" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25">
       <c r="A440" s="3"/>
@@ -8610,7 +8604,7 @@
       <c r="M440" s="3"/>
       <c r="N440" s="3"/>
       <c r="O440" s="3"/>
-      <c r="P440" s="6"/>
+      <c r="P440" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25">
       <c r="A441" s="3"/>
@@ -8628,7 +8622,7 @@
       <c r="M441" s="3"/>
       <c r="N441" s="3"/>
       <c r="O441" s="3"/>
-      <c r="P441" s="6"/>
+      <c r="P441" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25">
       <c r="A442" s="3"/>
@@ -8646,7 +8640,7 @@
       <c r="M442" s="3"/>
       <c r="N442" s="3"/>
       <c r="O442" s="3"/>
-      <c r="P442" s="6"/>
+      <c r="P442" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25">
       <c r="A443" s="3"/>
@@ -8664,7 +8658,7 @@
       <c r="M443" s="3"/>
       <c r="N443" s="3"/>
       <c r="O443" s="3"/>
-      <c r="P443" s="6"/>
+      <c r="P443" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25">
       <c r="A444" s="3"/>
@@ -8682,7 +8676,7 @@
       <c r="M444" s="3"/>
       <c r="N444" s="3"/>
       <c r="O444" s="3"/>
-      <c r="P444" s="6"/>
+      <c r="P444" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25">
       <c r="A445" s="3"/>
@@ -8700,7 +8694,7 @@
       <c r="M445" s="3"/>
       <c r="N445" s="3"/>
       <c r="O445" s="3"/>
-      <c r="P445" s="6"/>
+      <c r="P445" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25">
       <c r="A446" s="3"/>
@@ -8718,7 +8712,7 @@
       <c r="M446" s="3"/>
       <c r="N446" s="3"/>
       <c r="O446" s="3"/>
-      <c r="P446" s="6"/>
+      <c r="P446" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25">
       <c r="A447" s="3"/>
@@ -8736,7 +8730,7 @@
       <c r="M447" s="3"/>
       <c r="N447" s="3"/>
       <c r="O447" s="3"/>
-      <c r="P447" s="6"/>
+      <c r="P447" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25">
       <c r="A448" s="3"/>
@@ -8754,7 +8748,7 @@
       <c r="M448" s="3"/>
       <c r="N448" s="3"/>
       <c r="O448" s="3"/>
-      <c r="P448" s="6"/>
+      <c r="P448" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25">
       <c r="A449" s="3"/>
@@ -8772,7 +8766,7 @@
       <c r="M449" s="3"/>
       <c r="N449" s="3"/>
       <c r="O449" s="3"/>
-      <c r="P449" s="6"/>
+      <c r="P449" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25">
       <c r="A450" s="3"/>
@@ -8790,7 +8784,7 @@
       <c r="M450" s="3"/>
       <c r="N450" s="3"/>
       <c r="O450" s="3"/>
-      <c r="P450" s="6"/>
+      <c r="P450" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25">
       <c r="A451" s="3"/>
@@ -8808,7 +8802,7 @@
       <c r="M451" s="3"/>
       <c r="N451" s="3"/>
       <c r="O451" s="3"/>
-      <c r="P451" s="6"/>
+      <c r="P451" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25">
       <c r="A452" s="3"/>
@@ -8826,7 +8820,7 @@
       <c r="M452" s="3"/>
       <c r="N452" s="3"/>
       <c r="O452" s="3"/>
-      <c r="P452" s="6"/>
+      <c r="P452" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25">
       <c r="A453" s="3"/>
@@ -8844,7 +8838,7 @@
       <c r="M453" s="3"/>
       <c r="N453" s="3"/>
       <c r="O453" s="3"/>
-      <c r="P453" s="6"/>
+      <c r="P453" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25">
       <c r="A454" s="3"/>
@@ -8862,7 +8856,7 @@
       <c r="M454" s="3"/>
       <c r="N454" s="3"/>
       <c r="O454" s="3"/>
-      <c r="P454" s="6"/>
+      <c r="P454" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25">
       <c r="A455" s="3"/>
@@ -8880,7 +8874,7 @@
       <c r="M455" s="3"/>
       <c r="N455" s="3"/>
       <c r="O455" s="3"/>
-      <c r="P455" s="6"/>
+      <c r="P455" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25">
       <c r="A456" s="3"/>
@@ -8898,7 +8892,7 @@
       <c r="M456" s="3"/>
       <c r="N456" s="3"/>
       <c r="O456" s="3"/>
-      <c r="P456" s="6"/>
+      <c r="P456" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25">
       <c r="A457" s="3"/>
@@ -8916,7 +8910,7 @@
       <c r="M457" s="3"/>
       <c r="N457" s="3"/>
       <c r="O457" s="3"/>
-      <c r="P457" s="6"/>
+      <c r="P457" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25">
       <c r="A458" s="3"/>
@@ -8934,7 +8928,7 @@
       <c r="M458" s="3"/>
       <c r="N458" s="3"/>
       <c r="O458" s="3"/>
-      <c r="P458" s="6"/>
+      <c r="P458" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25">
       <c r="A459" s="3"/>
@@ -8952,7 +8946,7 @@
       <c r="M459" s="3"/>
       <c r="N459" s="3"/>
       <c r="O459" s="3"/>
-      <c r="P459" s="6"/>
+      <c r="P459" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25">
       <c r="A460" s="3"/>
@@ -8970,7 +8964,7 @@
       <c r="M460" s="3"/>
       <c r="N460" s="3"/>
       <c r="O460" s="3"/>
-      <c r="P460" s="6"/>
+      <c r="P460" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25">
       <c r="A461" s="3"/>
@@ -8988,7 +8982,7 @@
       <c r="M461" s="3"/>
       <c r="N461" s="3"/>
       <c r="O461" s="3"/>
-      <c r="P461" s="6"/>
+      <c r="P461" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25">
       <c r="A462" s="3"/>
@@ -9006,7 +9000,7 @@
       <c r="M462" s="3"/>
       <c r="N462" s="3"/>
       <c r="O462" s="3"/>
-      <c r="P462" s="6"/>
+      <c r="P462" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25">
       <c r="A463" s="3"/>
@@ -9024,7 +9018,7 @@
       <c r="M463" s="3"/>
       <c r="N463" s="3"/>
       <c r="O463" s="3"/>
-      <c r="P463" s="6"/>
+      <c r="P463" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25">
       <c r="A464" s="3"/>
@@ -9042,7 +9036,7 @@
       <c r="M464" s="3"/>
       <c r="N464" s="3"/>
       <c r="O464" s="3"/>
-      <c r="P464" s="6"/>
+      <c r="P464" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25">
       <c r="A465" s="3"/>
@@ -9060,7 +9054,7 @@
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>
       <c r="O465" s="3"/>
-      <c r="P465" s="6"/>
+      <c r="P465" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25">
       <c r="A466" s="3"/>
@@ -9078,7 +9072,7 @@
       <c r="M466" s="3"/>
       <c r="N466" s="3"/>
       <c r="O466" s="3"/>
-      <c r="P466" s="6"/>
+      <c r="P466" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25">
       <c r="A467" s="3"/>
@@ -9096,7 +9090,7 @@
       <c r="M467" s="3"/>
       <c r="N467" s="3"/>
       <c r="O467" s="3"/>
-      <c r="P467" s="6"/>
+      <c r="P467" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25">
       <c r="A468" s="3"/>
@@ -9114,7 +9108,7 @@
       <c r="M468" s="3"/>
       <c r="N468" s="3"/>
       <c r="O468" s="3"/>
-      <c r="P468" s="6"/>
+      <c r="P468" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25">
       <c r="A469" s="3"/>
@@ -9132,7 +9126,7 @@
       <c r="M469" s="3"/>
       <c r="N469" s="3"/>
       <c r="O469" s="3"/>
-      <c r="P469" s="6"/>
+      <c r="P469" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25">
       <c r="A470" s="3"/>
@@ -9150,7 +9144,7 @@
       <c r="M470" s="3"/>
       <c r="N470" s="3"/>
       <c r="O470" s="3"/>
-      <c r="P470" s="6"/>
+      <c r="P470" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25">
       <c r="A471" s="3"/>
@@ -9168,7 +9162,7 @@
       <c r="M471" s="3"/>
       <c r="N471" s="3"/>
       <c r="O471" s="3"/>
-      <c r="P471" s="6"/>
+      <c r="P471" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25">
       <c r="A472" s="3"/>
@@ -9186,7 +9180,7 @@
       <c r="M472" s="3"/>
       <c r="N472" s="3"/>
       <c r="O472" s="3"/>
-      <c r="P472" s="6"/>
+      <c r="P472" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25">
       <c r="A473" s="3"/>
@@ -9204,7 +9198,7 @@
       <c r="M473" s="3"/>
       <c r="N473" s="3"/>
       <c r="O473" s="3"/>
-      <c r="P473" s="6"/>
+      <c r="P473" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25">
       <c r="A474" s="3"/>
@@ -9222,7 +9216,7 @@
       <c r="M474" s="3"/>
       <c r="N474" s="3"/>
       <c r="O474" s="3"/>
-      <c r="P474" s="6"/>
+      <c r="P474" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25">
       <c r="A475" s="3"/>
@@ -9240,7 +9234,7 @@
       <c r="M475" s="3"/>
       <c r="N475" s="3"/>
       <c r="O475" s="3"/>
-      <c r="P475" s="6"/>
+      <c r="P475" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25">
       <c r="A476" s="3"/>
@@ -9258,7 +9252,7 @@
       <c r="M476" s="3"/>
       <c r="N476" s="3"/>
       <c r="O476" s="3"/>
-      <c r="P476" s="6"/>
+      <c r="P476" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25">
       <c r="A477" s="3"/>
@@ -9276,7 +9270,7 @@
       <c r="M477" s="3"/>
       <c r="N477" s="3"/>
       <c r="O477" s="3"/>
-      <c r="P477" s="6"/>
+      <c r="P477" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25">
       <c r="A478" s="3"/>
@@ -9294,7 +9288,7 @@
       <c r="M478" s="3"/>
       <c r="N478" s="3"/>
       <c r="O478" s="3"/>
-      <c r="P478" s="6"/>
+      <c r="P478" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25">
       <c r="A479" s="3"/>
@@ -9312,7 +9306,7 @@
       <c r="M479" s="3"/>
       <c r="N479" s="3"/>
       <c r="O479" s="3"/>
-      <c r="P479" s="6"/>
+      <c r="P479" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25">
       <c r="A480" s="3"/>
@@ -9330,7 +9324,7 @@
       <c r="M480" s="3"/>
       <c r="N480" s="3"/>
       <c r="O480" s="3"/>
-      <c r="P480" s="6"/>
+      <c r="P480" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25">
       <c r="A481" s="3"/>
@@ -9348,7 +9342,7 @@
       <c r="M481" s="3"/>
       <c r="N481" s="3"/>
       <c r="O481" s="3"/>
-      <c r="P481" s="6"/>
+      <c r="P481" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25">
       <c r="A482" s="3"/>
@@ -9366,7 +9360,7 @@
       <c r="M482" s="3"/>
       <c r="N482" s="3"/>
       <c r="O482" s="3"/>
-      <c r="P482" s="6"/>
+      <c r="P482" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25">
       <c r="A483" s="3"/>
@@ -9384,7 +9378,7 @@
       <c r="M483" s="3"/>
       <c r="N483" s="3"/>
       <c r="O483" s="3"/>
-      <c r="P483" s="6"/>
+      <c r="P483" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25">
       <c r="A484" s="3"/>
@@ -9402,7 +9396,7 @@
       <c r="M484" s="3"/>
       <c r="N484" s="3"/>
       <c r="O484" s="3"/>
-      <c r="P484" s="6"/>
+      <c r="P484" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25">
       <c r="A485" s="3"/>
@@ -9420,7 +9414,7 @@
       <c r="M485" s="3"/>
       <c r="N485" s="3"/>
       <c r="O485" s="3"/>
-      <c r="P485" s="6"/>
+      <c r="P485" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25">
       <c r="A486" s="3"/>
@@ -9438,7 +9432,7 @@
       <c r="M486" s="3"/>
       <c r="N486" s="3"/>
       <c r="O486" s="3"/>
-      <c r="P486" s="6"/>
+      <c r="P486" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25">
       <c r="A487" s="3"/>
@@ -9456,7 +9450,7 @@
       <c r="M487" s="3"/>
       <c r="N487" s="3"/>
       <c r="O487" s="3"/>
-      <c r="P487" s="6"/>
+      <c r="P487" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25">
       <c r="A488" s="3"/>
@@ -9474,7 +9468,7 @@
       <c r="M488" s="3"/>
       <c r="N488" s="3"/>
       <c r="O488" s="3"/>
-      <c r="P488" s="6"/>
+      <c r="P488" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25">
       <c r="A489" s="3"/>
@@ -9492,7 +9486,7 @@
       <c r="M489" s="3"/>
       <c r="N489" s="3"/>
       <c r="O489" s="3"/>
-      <c r="P489" s="6"/>
+      <c r="P489" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25">
       <c r="A490" s="3"/>
@@ -9510,7 +9504,7 @@
       <c r="M490" s="3"/>
       <c r="N490" s="3"/>
       <c r="O490" s="3"/>
-      <c r="P490" s="6"/>
+      <c r="P490" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25">
       <c r="A491" s="3"/>
@@ -9528,7 +9522,7 @@
       <c r="M491" s="3"/>
       <c r="N491" s="3"/>
       <c r="O491" s="3"/>
-      <c r="P491" s="6"/>
+      <c r="P491" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25">
       <c r="A492" s="3"/>
@@ -9546,7 +9540,7 @@
       <c r="M492" s="3"/>
       <c r="N492" s="3"/>
       <c r="O492" s="3"/>
-      <c r="P492" s="6"/>
+      <c r="P492" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25">
       <c r="A493" s="3"/>
@@ -9564,7 +9558,7 @@
       <c r="M493" s="3"/>
       <c r="N493" s="3"/>
       <c r="O493" s="3"/>
-      <c r="P493" s="6"/>
+      <c r="P493" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25">
       <c r="A494" s="3"/>
@@ -9582,7 +9576,7 @@
       <c r="M494" s="3"/>
       <c r="N494" s="3"/>
       <c r="O494" s="3"/>
-      <c r="P494" s="6"/>
+      <c r="P494" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25">
       <c r="A495" s="3"/>
@@ -9600,7 +9594,7 @@
       <c r="M495" s="3"/>
       <c r="N495" s="3"/>
       <c r="O495" s="3"/>
-      <c r="P495" s="6"/>
+      <c r="P495" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25">
       <c r="A496" s="3"/>
@@ -9618,7 +9612,7 @@
       <c r="M496" s="3"/>
       <c r="N496" s="3"/>
       <c r="O496" s="3"/>
-      <c r="P496" s="6"/>
+      <c r="P496" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25">
       <c r="A497" s="3"/>
@@ -9636,7 +9630,7 @@
       <c r="M497" s="3"/>
       <c r="N497" s="3"/>
       <c r="O497" s="3"/>
-      <c r="P497" s="6"/>
+      <c r="P497" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25">
       <c r="A498" s="3"/>
@@ -9654,7 +9648,7 @@
       <c r="M498" s="3"/>
       <c r="N498" s="3"/>
       <c r="O498" s="3"/>
-      <c r="P498" s="6"/>
+      <c r="P498" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25">
       <c r="A499" s="3"/>
@@ -9672,7 +9666,7 @@
       <c r="M499" s="3"/>
       <c r="N499" s="3"/>
       <c r="O499" s="3"/>
-      <c r="P499" s="6"/>
+      <c r="P499" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25">
       <c r="A500" s="3"/>
@@ -9690,7 +9684,7 @@
       <c r="M500" s="3"/>
       <c r="N500" s="3"/>
       <c r="O500" s="3"/>
-      <c r="P500" s="6"/>
+      <c r="P500" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25">
       <c r="A501" s="3"/>
@@ -9708,7 +9702,7 @@
       <c r="M501" s="3"/>
       <c r="N501" s="3"/>
       <c r="O501" s="3"/>
-      <c r="P501" s="6"/>
+      <c r="P501" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25">
       <c r="A502" s="3"/>
@@ -9726,7 +9720,7 @@
       <c r="M502" s="3"/>
       <c r="N502" s="3"/>
       <c r="O502" s="3"/>
-      <c r="P502" s="6"/>
+      <c r="P502" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25">
       <c r="A503" s="3"/>
@@ -9744,7 +9738,7 @@
       <c r="M503" s="3"/>
       <c r="N503" s="3"/>
       <c r="O503" s="3"/>
-      <c r="P503" s="6"/>
+      <c r="P503" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25">
       <c r="A504" s="3"/>
@@ -9762,7 +9756,7 @@
       <c r="M504" s="3"/>
       <c r="N504" s="3"/>
       <c r="O504" s="3"/>
-      <c r="P504" s="6"/>
+      <c r="P504" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25">
       <c r="A505" s="3"/>
@@ -9780,7 +9774,7 @@
       <c r="M505" s="3"/>
       <c r="N505" s="3"/>
       <c r="O505" s="3"/>
-      <c r="P505" s="6"/>
+      <c r="P505" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25">
       <c r="A506" s="3"/>
@@ -9798,7 +9792,7 @@
       <c r="M506" s="3"/>
       <c r="N506" s="3"/>
       <c r="O506" s="3"/>
-      <c r="P506" s="6"/>
+      <c r="P506" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25">
       <c r="A507" s="3"/>
@@ -9816,7 +9810,7 @@
       <c r="M507" s="3"/>
       <c r="N507" s="3"/>
       <c r="O507" s="3"/>
-      <c r="P507" s="6"/>
+      <c r="P507" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25">
       <c r="A508" s="3"/>
@@ -9834,7 +9828,7 @@
       <c r="M508" s="3"/>
       <c r="N508" s="3"/>
       <c r="O508" s="3"/>
-      <c r="P508" s="6"/>
+      <c r="P508" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25">
       <c r="A509" s="3"/>
@@ -9852,7 +9846,7 @@
       <c r="M509" s="3"/>
       <c r="N509" s="3"/>
       <c r="O509" s="3"/>
-      <c r="P509" s="6"/>
+      <c r="P509" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25">
       <c r="A510" s="3"/>
@@ -9870,7 +9864,7 @@
       <c r="M510" s="3"/>
       <c r="N510" s="3"/>
       <c r="O510" s="3"/>
-      <c r="P510" s="6"/>
+      <c r="P510" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25">
       <c r="A511" s="3"/>
@@ -9888,7 +9882,7 @@
       <c r="M511" s="3"/>
       <c r="N511" s="3"/>
       <c r="O511" s="3"/>
-      <c r="P511" s="6"/>
+      <c r="P511" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25">
       <c r="A512" s="3"/>
@@ -9906,7 +9900,7 @@
       <c r="M512" s="3"/>
       <c r="N512" s="3"/>
       <c r="O512" s="3"/>
-      <c r="P512" s="6"/>
+      <c r="P512" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25">
       <c r="A513" s="3"/>
@@ -9924,7 +9918,7 @@
       <c r="M513" s="3"/>
       <c r="N513" s="3"/>
       <c r="O513" s="3"/>
-      <c r="P513" s="6"/>
+      <c r="P513" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25">
       <c r="A514" s="3"/>
@@ -9942,7 +9936,7 @@
       <c r="M514" s="3"/>
       <c r="N514" s="3"/>
       <c r="O514" s="3"/>
-      <c r="P514" s="6"/>
+      <c r="P514" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25">
       <c r="A515" s="3"/>
@@ -9960,7 +9954,7 @@
       <c r="M515" s="3"/>
       <c r="N515" s="3"/>
       <c r="O515" s="3"/>
-      <c r="P515" s="6"/>
+      <c r="P515" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25">
       <c r="A516" s="3"/>
@@ -9978,7 +9972,7 @@
       <c r="M516" s="3"/>
       <c r="N516" s="3"/>
       <c r="O516" s="3"/>
-      <c r="P516" s="6"/>
+      <c r="P516" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25">
       <c r="A517" s="3"/>
@@ -9996,7 +9990,7 @@
       <c r="M517" s="3"/>
       <c r="N517" s="3"/>
       <c r="O517" s="3"/>
-      <c r="P517" s="6"/>
+      <c r="P517" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25">
       <c r="A518" s="3"/>
@@ -10014,7 +10008,7 @@
       <c r="M518" s="3"/>
       <c r="N518" s="3"/>
       <c r="O518" s="3"/>
-      <c r="P518" s="6"/>
+      <c r="P518" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25">
       <c r="A519" s="3"/>
@@ -10032,7 +10026,7 @@
       <c r="M519" s="3"/>
       <c r="N519" s="3"/>
       <c r="O519" s="3"/>
-      <c r="P519" s="6"/>
+      <c r="P519" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25">
       <c r="A520" s="3"/>
@@ -10050,7 +10044,7 @@
       <c r="M520" s="3"/>
       <c r="N520" s="3"/>
       <c r="O520" s="3"/>
-      <c r="P520" s="6"/>
+      <c r="P520" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25">
       <c r="A521" s="3"/>
@@ -10068,7 +10062,7 @@
       <c r="M521" s="3"/>
       <c r="N521" s="3"/>
       <c r="O521" s="3"/>
-      <c r="P521" s="6"/>
+      <c r="P521" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25">
       <c r="A522" s="3"/>
@@ -10086,7 +10080,7 @@
       <c r="M522" s="3"/>
       <c r="N522" s="3"/>
       <c r="O522" s="3"/>
-      <c r="P522" s="6"/>
+      <c r="P522" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25">
       <c r="A523" s="3"/>
@@ -10104,7 +10098,7 @@
       <c r="M523" s="3"/>
       <c r="N523" s="3"/>
       <c r="O523" s="3"/>
-      <c r="P523" s="6"/>
+      <c r="P523" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25">
       <c r="A524" s="3"/>
@@ -10122,7 +10116,7 @@
       <c r="M524" s="3"/>
       <c r="N524" s="3"/>
       <c r="O524" s="3"/>
-      <c r="P524" s="6"/>
+      <c r="P524" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25">
       <c r="A525" s="3"/>
@@ -10140,7 +10134,7 @@
       <c r="M525" s="3"/>
       <c r="N525" s="3"/>
       <c r="O525" s="3"/>
-      <c r="P525" s="6"/>
+      <c r="P525" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25">
       <c r="A526" s="3"/>
@@ -10158,7 +10152,7 @@
       <c r="M526" s="3"/>
       <c r="N526" s="3"/>
       <c r="O526" s="3"/>
-      <c r="P526" s="6"/>
+      <c r="P526" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25">
       <c r="A527" s="3"/>
@@ -10176,7 +10170,7 @@
       <c r="M527" s="3"/>
       <c r="N527" s="3"/>
       <c r="O527" s="3"/>
-      <c r="P527" s="6"/>
+      <c r="P527" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25">
       <c r="A528" s="3"/>
@@ -10194,7 +10188,7 @@
       <c r="M528" s="3"/>
       <c r="N528" s="3"/>
       <c r="O528" s="3"/>
-      <c r="P528" s="6"/>
+      <c r="P528" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25">
       <c r="A529" s="3"/>
@@ -10212,7 +10206,7 @@
       <c r="M529" s="3"/>
       <c r="N529" s="3"/>
       <c r="O529" s="3"/>
-      <c r="P529" s="6"/>
+      <c r="P529" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25">
       <c r="A530" s="3"/>
@@ -10230,7 +10224,7 @@
       <c r="M530" s="3"/>
       <c r="N530" s="3"/>
       <c r="O530" s="3"/>
-      <c r="P530" s="6"/>
+      <c r="P530" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25">
       <c r="A531" s="3"/>
@@ -10248,7 +10242,7 @@
       <c r="M531" s="3"/>
       <c r="N531" s="3"/>
       <c r="O531" s="3"/>
-      <c r="P531" s="6"/>
+      <c r="P531" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25">
       <c r="A532" s="3"/>
@@ -10266,7 +10260,7 @@
       <c r="M532" s="3"/>
       <c r="N532" s="3"/>
       <c r="O532" s="3"/>
-      <c r="P532" s="6"/>
+      <c r="P532" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25">
       <c r="A533" s="3"/>
@@ -10284,7 +10278,7 @@
       <c r="M533" s="3"/>
       <c r="N533" s="3"/>
       <c r="O533" s="3"/>
-      <c r="P533" s="6"/>
+      <c r="P533" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25">
       <c r="A534" s="3"/>
@@ -10302,7 +10296,7 @@
       <c r="M534" s="3"/>
       <c r="N534" s="3"/>
       <c r="O534" s="3"/>
-      <c r="P534" s="6"/>
+      <c r="P534" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25">
       <c r="A535" s="3"/>
@@ -10320,7 +10314,7 @@
       <c r="M535" s="3"/>
       <c r="N535" s="3"/>
       <c r="O535" s="3"/>
-      <c r="P535" s="6"/>
+      <c r="P535" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25">
       <c r="A536" s="3"/>
@@ -10338,7 +10332,7 @@
       <c r="M536" s="3"/>
       <c r="N536" s="3"/>
       <c r="O536" s="3"/>
-      <c r="P536" s="6"/>
+      <c r="P536" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25">
       <c r="A537" s="3"/>
@@ -10356,7 +10350,7 @@
       <c r="M537" s="3"/>
       <c r="N537" s="3"/>
       <c r="O537" s="3"/>
-      <c r="P537" s="6"/>
+      <c r="P537" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="17.25">
       <c r="A538" s="3"/>
@@ -10374,7 +10368,7 @@
       <c r="M538" s="3"/>
       <c r="N538" s="3"/>
       <c r="O538" s="3"/>
-      <c r="P538" s="6"/>
+      <c r="P538" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="17.25">
       <c r="A539" s="3"/>
@@ -10392,7 +10386,7 @@
       <c r="M539" s="3"/>
       <c r="N539" s="3"/>
       <c r="O539" s="3"/>
-      <c r="P539" s="6"/>
+      <c r="P539" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="17.25">
       <c r="A540" s="3"/>
@@ -10410,7 +10404,7 @@
       <c r="M540" s="3"/>
       <c r="N540" s="3"/>
       <c r="O540" s="3"/>
-      <c r="P540" s="6"/>
+      <c r="P540" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="17.25">
       <c r="A541" s="3"/>
@@ -10428,7 +10422,7 @@
       <c r="M541" s="3"/>
       <c r="N541" s="3"/>
       <c r="O541" s="3"/>
-      <c r="P541" s="6"/>
+      <c r="P541" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="17.25">
       <c r="A542" s="3"/>
@@ -10446,7 +10440,7 @@
       <c r="M542" s="3"/>
       <c r="N542" s="3"/>
       <c r="O542" s="3"/>
-      <c r="P542" s="6"/>
+      <c r="P542" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="17.25">
       <c r="A543" s="3"/>
@@ -10464,7 +10458,7 @@
       <c r="M543" s="3"/>
       <c r="N543" s="3"/>
       <c r="O543" s="3"/>
-      <c r="P543" s="6"/>
+      <c r="P543" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="17.25">
       <c r="A544" s="3"/>
@@ -10482,7 +10476,7 @@
       <c r="M544" s="3"/>
       <c r="N544" s="3"/>
       <c r="O544" s="3"/>
-      <c r="P544" s="6"/>
+      <c r="P544" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="17.25">
       <c r="A545" s="3"/>
@@ -10500,7 +10494,7 @@
       <c r="M545" s="3"/>
       <c r="N545" s="3"/>
       <c r="O545" s="3"/>
-      <c r="P545" s="6"/>
+      <c r="P545" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="17.25">
       <c r="A546" s="3"/>
@@ -10518,7 +10512,7 @@
       <c r="M546" s="3"/>
       <c r="N546" s="3"/>
       <c r="O546" s="3"/>
-      <c r="P546" s="6"/>
+      <c r="P546" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="17.25">
       <c r="A547" s="3"/>
@@ -10536,7 +10530,7 @@
       <c r="M547" s="3"/>
       <c r="N547" s="3"/>
       <c r="O547" s="3"/>
-      <c r="P547" s="6"/>
+      <c r="P547" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="17.25">
       <c r="A548" s="3"/>
@@ -10554,7 +10548,7 @@
       <c r="M548" s="3"/>
       <c r="N548" s="3"/>
       <c r="O548" s="3"/>
-      <c r="P548" s="6"/>
+      <c r="P548" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="17.25">
       <c r="A549" s="3"/>
@@ -10572,7 +10566,7 @@
       <c r="M549" s="3"/>
       <c r="N549" s="3"/>
       <c r="O549" s="3"/>
-      <c r="P549" s="6"/>
+      <c r="P549" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="17.25">
       <c r="A550" s="3"/>
@@ -10590,7 +10584,7 @@
       <c r="M550" s="3"/>
       <c r="N550" s="3"/>
       <c r="O550" s="3"/>
-      <c r="P550" s="6"/>
+      <c r="P550" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="17.25">
       <c r="A551" s="3"/>
@@ -10608,7 +10602,7 @@
       <c r="M551" s="3"/>
       <c r="N551" s="3"/>
       <c r="O551" s="3"/>
-      <c r="P551" s="6"/>
+      <c r="P551" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="17.25">
       <c r="A552" s="3"/>
@@ -10626,7 +10620,7 @@
       <c r="M552" s="3"/>
       <c r="N552" s="3"/>
       <c r="O552" s="3"/>
-      <c r="P552" s="6"/>
+      <c r="P552" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="17.25">
       <c r="A553" s="3"/>
@@ -10644,7 +10638,7 @@
       <c r="M553" s="3"/>
       <c r="N553" s="3"/>
       <c r="O553" s="3"/>
-      <c r="P553" s="6"/>
+      <c r="P553" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="17.25">
       <c r="A554" s="3"/>
@@ -10662,7 +10656,7 @@
       <c r="M554" s="3"/>
       <c r="N554" s="3"/>
       <c r="O554" s="3"/>
-      <c r="P554" s="6"/>
+      <c r="P554" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="17.25">
       <c r="A555" s="3"/>
@@ -10680,7 +10674,7 @@
       <c r="M555" s="3"/>
       <c r="N555" s="3"/>
       <c r="O555" s="3"/>
-      <c r="P555" s="6"/>
+      <c r="P555" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="17.25">
       <c r="A556" s="3"/>
@@ -10698,7 +10692,7 @@
       <c r="M556" s="3"/>
       <c r="N556" s="3"/>
       <c r="O556" s="3"/>
-      <c r="P556" s="6"/>
+      <c r="P556" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="17.25">
       <c r="A557" s="3"/>
@@ -10716,7 +10710,7 @@
       <c r="M557" s="3"/>
       <c r="N557" s="3"/>
       <c r="O557" s="3"/>
-      <c r="P557" s="6"/>
+      <c r="P557" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="17.25">
       <c r="A558" s="3"/>
@@ -10734,7 +10728,7 @@
       <c r="M558" s="3"/>
       <c r="N558" s="3"/>
       <c r="O558" s="3"/>
-      <c r="P558" s="6"/>
+      <c r="P558" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="17.25">
       <c r="A559" s="3"/>
@@ -10752,7 +10746,7 @@
       <c r="M559" s="3"/>
       <c r="N559" s="3"/>
       <c r="O559" s="3"/>
-      <c r="P559" s="6"/>
+      <c r="P559" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="17.25">
       <c r="A560" s="3"/>
@@ -10770,7 +10764,7 @@
       <c r="M560" s="3"/>
       <c r="N560" s="3"/>
       <c r="O560" s="3"/>
-      <c r="P560" s="6"/>
+      <c r="P560" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="17.25">
       <c r="A561" s="3"/>
@@ -10788,7 +10782,7 @@
       <c r="M561" s="3"/>
       <c r="N561" s="3"/>
       <c r="O561" s="3"/>
-      <c r="P561" s="6"/>
+      <c r="P561" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="17.25">
       <c r="A562" s="3"/>
@@ -10806,7 +10800,7 @@
       <c r="M562" s="3"/>
       <c r="N562" s="3"/>
       <c r="O562" s="3"/>
-      <c r="P562" s="6"/>
+      <c r="P562" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="17.25">
       <c r="A563" s="3"/>
@@ -10824,7 +10818,7 @@
       <c r="M563" s="3"/>
       <c r="N563" s="3"/>
       <c r="O563" s="3"/>
-      <c r="P563" s="6"/>
+      <c r="P563" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="17.25">
       <c r="A564" s="3"/>
@@ -10842,7 +10836,7 @@
       <c r="M564" s="3"/>
       <c r="N564" s="3"/>
       <c r="O564" s="3"/>
-      <c r="P564" s="6"/>
+      <c r="P564" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="17.25">
       <c r="A565" s="3"/>
@@ -10860,7 +10854,7 @@
       <c r="M565" s="3"/>
       <c r="N565" s="3"/>
       <c r="O565" s="3"/>
-      <c r="P565" s="6"/>
+      <c r="P565" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="17.25">
       <c r="A566" s="3"/>
@@ -10878,7 +10872,7 @@
       <c r="M566" s="3"/>
       <c r="N566" s="3"/>
       <c r="O566" s="3"/>
-      <c r="P566" s="6"/>
+      <c r="P566" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="17.25">
       <c r="A567" s="3"/>
@@ -10896,7 +10890,7 @@
       <c r="M567" s="3"/>
       <c r="N567" s="3"/>
       <c r="O567" s="3"/>
-      <c r="P567" s="6"/>
+      <c r="P567" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="17.25">
       <c r="A568" s="3"/>
@@ -10914,7 +10908,7 @@
       <c r="M568" s="3"/>
       <c r="N568" s="3"/>
       <c r="O568" s="3"/>
-      <c r="P568" s="6"/>
+      <c r="P568" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="17.25">
       <c r="A569" s="3"/>
@@ -10932,7 +10926,7 @@
       <c r="M569" s="3"/>
       <c r="N569" s="3"/>
       <c r="O569" s="3"/>
-      <c r="P569" s="6"/>
+      <c r="P569" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="17.25">
       <c r="A570" s="3"/>
@@ -10950,7 +10944,7 @@
       <c r="M570" s="3"/>
       <c r="N570" s="3"/>
       <c r="O570" s="3"/>
-      <c r="P570" s="6"/>
+      <c r="P570" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="17.25">
       <c r="A571" s="3"/>
@@ -10968,7 +10962,7 @@
       <c r="M571" s="3"/>
       <c r="N571" s="3"/>
       <c r="O571" s="3"/>
-      <c r="P571" s="6"/>
+      <c r="P571" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="17.25">
       <c r="A572" s="3"/>
@@ -10986,7 +10980,7 @@
       <c r="M572" s="3"/>
       <c r="N572" s="3"/>
       <c r="O572" s="3"/>
-      <c r="P572" s="6"/>
+      <c r="P572" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="17.25">
       <c r="A573" s="3"/>
@@ -11004,7 +10998,7 @@
       <c r="M573" s="3"/>
       <c r="N573" s="3"/>
       <c r="O573" s="3"/>
-      <c r="P573" s="6"/>
+      <c r="P573" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="17.25">
       <c r="A574" s="3"/>
@@ -11022,7 +11016,7 @@
       <c r="M574" s="3"/>
       <c r="N574" s="3"/>
       <c r="O574" s="3"/>
-      <c r="P574" s="6"/>
+      <c r="P574" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="17.25">
       <c r="A575" s="3"/>
@@ -11040,7 +11034,7 @@
       <c r="M575" s="3"/>
       <c r="N575" s="3"/>
       <c r="O575" s="3"/>
-      <c r="P575" s="6"/>
+      <c r="P575" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="17.25">
       <c r="A576" s="3"/>
@@ -11058,7 +11052,7 @@
       <c r="M576" s="3"/>
       <c r="N576" s="3"/>
       <c r="O576" s="3"/>
-      <c r="P576" s="6"/>
+      <c r="P576" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="17.25">
       <c r="A577" s="3"/>
@@ -11076,7 +11070,7 @@
       <c r="M577" s="3"/>
       <c r="N577" s="3"/>
       <c r="O577" s="3"/>
-      <c r="P577" s="6"/>
+      <c r="P577" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="17.25">
       <c r="A578" s="3"/>
@@ -11094,7 +11088,7 @@
       <c r="M578" s="3"/>
       <c r="N578" s="3"/>
       <c r="O578" s="3"/>
-      <c r="P578" s="6"/>
+      <c r="P578" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="17.25">
       <c r="A579" s="3"/>
@@ -11112,7 +11106,7 @@
       <c r="M579" s="3"/>
       <c r="N579" s="3"/>
       <c r="O579" s="3"/>
-      <c r="P579" s="6"/>
+      <c r="P579" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="17.25">
       <c r="A580" s="3"/>
@@ -11130,7 +11124,7 @@
       <c r="M580" s="3"/>
       <c r="N580" s="3"/>
       <c r="O580" s="3"/>
-      <c r="P580" s="6"/>
+      <c r="P580" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="17.25">
       <c r="A581" s="3"/>
@@ -11148,7 +11142,7 @@
       <c r="M581" s="3"/>
       <c r="N581" s="3"/>
       <c r="O581" s="3"/>
-      <c r="P581" s="6"/>
+      <c r="P581" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="17.25">
       <c r="A582" s="3"/>
@@ -11166,7 +11160,7 @@
       <c r="M582" s="3"/>
       <c r="N582" s="3"/>
       <c r="O582" s="3"/>
-      <c r="P582" s="6"/>
+      <c r="P582" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="17.25">
       <c r="A583" s="3"/>
@@ -11184,7 +11178,7 @@
       <c r="M583" s="3"/>
       <c r="N583" s="3"/>
       <c r="O583" s="3"/>
-      <c r="P583" s="6"/>
+      <c r="P583" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="17.25">
       <c r="A584" s="3"/>
@@ -11202,7 +11196,7 @@
       <c r="M584" s="3"/>
       <c r="N584" s="3"/>
       <c r="O584" s="3"/>
-      <c r="P584" s="6"/>
+      <c r="P584" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="17.25">
       <c r="A585" s="3"/>
@@ -11220,7 +11214,7 @@
       <c r="M585" s="3"/>
       <c r="N585" s="3"/>
       <c r="O585" s="3"/>
-      <c r="P585" s="6"/>
+      <c r="P585" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="17.25">
       <c r="A586" s="3"/>
@@ -11238,7 +11232,7 @@
       <c r="M586" s="3"/>
       <c r="N586" s="3"/>
       <c r="O586" s="3"/>
-      <c r="P586" s="6"/>
+      <c r="P586" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="17.25">
       <c r="A587" s="3"/>
@@ -11256,7 +11250,7 @@
       <c r="M587" s="3"/>
       <c r="N587" s="3"/>
       <c r="O587" s="3"/>
-      <c r="P587" s="6"/>
+      <c r="P587" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="17.25">
       <c r="A588" s="3"/>
@@ -11274,7 +11268,7 @@
       <c r="M588" s="3"/>
       <c r="N588" s="3"/>
       <c r="O588" s="3"/>
-      <c r="P588" s="6"/>
+      <c r="P588" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="17.25">
       <c r="A589" s="3"/>
@@ -11292,7 +11286,7 @@
       <c r="M589" s="3"/>
       <c r="N589" s="3"/>
       <c r="O589" s="3"/>
-      <c r="P589" s="6"/>
+      <c r="P589" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="17.25">
       <c r="A590" s="3"/>
@@ -11310,7 +11304,7 @@
       <c r="M590" s="3"/>
       <c r="N590" s="3"/>
       <c r="O590" s="3"/>
-      <c r="P590" s="6"/>
+      <c r="P590" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="17.25">
       <c r="A591" s="3"/>
@@ -11328,7 +11322,7 @@
       <c r="M591" s="3"/>
       <c r="N591" s="3"/>
       <c r="O591" s="3"/>
-      <c r="P591" s="6"/>
+      <c r="P591" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="17.25">
       <c r="A592" s="3"/>
@@ -11346,7 +11340,7 @@
       <c r="M592" s="3"/>
       <c r="N592" s="3"/>
       <c r="O592" s="3"/>
-      <c r="P592" s="6"/>
+      <c r="P592" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="17.25">
       <c r="A593" s="3"/>
@@ -11364,7 +11358,7 @@
       <c r="M593" s="3"/>
       <c r="N593" s="3"/>
       <c r="O593" s="3"/>
-      <c r="P593" s="6"/>
+      <c r="P593" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="17.25">
       <c r="A594" s="3"/>
@@ -11382,7 +11376,7 @@
       <c r="M594" s="3"/>
       <c r="N594" s="3"/>
       <c r="O594" s="3"/>
-      <c r="P594" s="6"/>
+      <c r="P594" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="17.25">
       <c r="A595" s="3"/>
@@ -11400,7 +11394,7 @@
       <c r="M595" s="3"/>
       <c r="N595" s="3"/>
       <c r="O595" s="3"/>
-      <c r="P595" s="6"/>
+      <c r="P595" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="17.25">
       <c r="A596" s="3"/>
@@ -11418,7 +11412,7 @@
       <c r="M596" s="3"/>
       <c r="N596" s="3"/>
       <c r="O596" s="3"/>
-      <c r="P596" s="6"/>
+      <c r="P596" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="17.25">
       <c r="A597" s="3"/>
@@ -11436,7 +11430,7 @@
       <c r="M597" s="3"/>
       <c r="N597" s="3"/>
       <c r="O597" s="3"/>
-      <c r="P597" s="6"/>
+      <c r="P597" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="17.25">
       <c r="A598" s="3"/>
@@ -11454,7 +11448,7 @@
       <c r="M598" s="3"/>
       <c r="N598" s="3"/>
       <c r="O598" s="3"/>
-      <c r="P598" s="6"/>
+      <c r="P598" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="17.25">
       <c r="A599" s="3"/>
@@ -11472,7 +11466,7 @@
       <c r="M599" s="3"/>
       <c r="N599" s="3"/>
       <c r="O599" s="3"/>
-      <c r="P599" s="6"/>
+      <c r="P599" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="17.25">
       <c r="A600" s="3"/>
@@ -11490,7 +11484,7 @@
       <c r="M600" s="3"/>
       <c r="N600" s="3"/>
       <c r="O600" s="3"/>
-      <c r="P600" s="6"/>
+      <c r="P600" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="17.25">
       <c r="A601" s="3"/>
@@ -11508,7 +11502,7 @@
       <c r="M601" s="3"/>
       <c r="N601" s="3"/>
       <c r="O601" s="3"/>
-      <c r="P601" s="6"/>
+      <c r="P601" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="17.25">
       <c r="A602" s="3"/>
@@ -11526,7 +11520,7 @@
       <c r="M602" s="3"/>
       <c r="N602" s="3"/>
       <c r="O602" s="3"/>
-      <c r="P602" s="6"/>
+      <c r="P602" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="17.25">
       <c r="A603" s="3"/>
@@ -11544,7 +11538,7 @@
       <c r="M603" s="3"/>
       <c r="N603" s="3"/>
       <c r="O603" s="3"/>
-      <c r="P603" s="6"/>
+      <c r="P603" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="17.25">
       <c r="A604" s="3"/>
@@ -11562,7 +11556,7 @@
       <c r="M604" s="3"/>
       <c r="N604" s="3"/>
       <c r="O604" s="3"/>
-      <c r="P604" s="6"/>
+      <c r="P604" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="17.25">
       <c r="A605" s="3"/>
@@ -11580,7 +11574,7 @@
       <c r="M605" s="3"/>
       <c r="N605" s="3"/>
       <c r="O605" s="3"/>
-      <c r="P605" s="6"/>
+      <c r="P605" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="17.25">
       <c r="A606" s="3"/>
@@ -11598,7 +11592,7 @@
       <c r="M606" s="3"/>
       <c r="N606" s="3"/>
       <c r="O606" s="3"/>
-      <c r="P606" s="6"/>
+      <c r="P606" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="17.25">
       <c r="A607" s="3"/>
@@ -11616,7 +11610,7 @@
       <c r="M607" s="3"/>
       <c r="N607" s="3"/>
       <c r="O607" s="3"/>
-      <c r="P607" s="6"/>
+      <c r="P607" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="17.25">
       <c r="A608" s="3"/>
@@ -11634,7 +11628,7 @@
       <c r="M608" s="3"/>
       <c r="N608" s="3"/>
       <c r="O608" s="3"/>
-      <c r="P608" s="6"/>
+      <c r="P608" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="17.25">
       <c r="A609" s="3"/>
@@ -11652,7 +11646,7 @@
       <c r="M609" s="3"/>
       <c r="N609" s="3"/>
       <c r="O609" s="3"/>
-      <c r="P609" s="6"/>
+      <c r="P609" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="17.25">
       <c r="A610" s="3"/>
@@ -11670,7 +11664,7 @@
       <c r="M610" s="3"/>
       <c r="N610" s="3"/>
       <c r="O610" s="3"/>
-      <c r="P610" s="6"/>
+      <c r="P610" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="17.25">
       <c r="A611" s="3"/>
@@ -11688,7 +11682,7 @@
       <c r="M611" s="3"/>
       <c r="N611" s="3"/>
       <c r="O611" s="3"/>
-      <c r="P611" s="6"/>
+      <c r="P611" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="17.25">
       <c r="A612" s="3"/>
@@ -11706,7 +11700,7 @@
       <c r="M612" s="3"/>
       <c r="N612" s="3"/>
       <c r="O612" s="3"/>
-      <c r="P612" s="6"/>
+      <c r="P612" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="17.25">
       <c r="A613" s="3"/>
@@ -11724,7 +11718,7 @@
       <c r="M613" s="3"/>
       <c r="N613" s="3"/>
       <c r="O613" s="3"/>
-      <c r="P613" s="6"/>
+      <c r="P613" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="17.25">
       <c r="A614" s="3"/>
@@ -11742,7 +11736,7 @@
       <c r="M614" s="3"/>
       <c r="N614" s="3"/>
       <c r="O614" s="3"/>
-      <c r="P614" s="6"/>
+      <c r="P614" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="17.25">
       <c r="A615" s="3"/>
@@ -11760,7 +11754,7 @@
       <c r="M615" s="3"/>
       <c r="N615" s="3"/>
       <c r="O615" s="3"/>
-      <c r="P615" s="6"/>
+      <c r="P615" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="17.25">
       <c r="A616" s="3"/>
@@ -11778,7 +11772,7 @@
       <c r="M616" s="3"/>
       <c r="N616" s="3"/>
       <c r="O616" s="3"/>
-      <c r="P616" s="6"/>
+      <c r="P616" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="17.25">
       <c r="A617" s="3"/>
@@ -11796,7 +11790,7 @@
       <c r="M617" s="3"/>
       <c r="N617" s="3"/>
       <c r="O617" s="3"/>
-      <c r="P617" s="6"/>
+      <c r="P617" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="17.25">
       <c r="A618" s="3"/>
@@ -11814,7 +11808,7 @@
       <c r="M618" s="3"/>
       <c r="N618" s="3"/>
       <c r="O618" s="3"/>
-      <c r="P618" s="6"/>
+      <c r="P618" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="17.25">
       <c r="A619" s="3"/>
@@ -11832,7 +11826,7 @@
       <c r="M619" s="3"/>
       <c r="N619" s="3"/>
       <c r="O619" s="3"/>
-      <c r="P619" s="6"/>
+      <c r="P619" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="17.25">
       <c r="A620" s="3"/>
@@ -11850,7 +11844,7 @@
       <c r="M620" s="3"/>
       <c r="N620" s="3"/>
       <c r="O620" s="3"/>
-      <c r="P620" s="6"/>
+      <c r="P620" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="17.25">
       <c r="A621" s="3"/>
@@ -11868,7 +11862,7 @@
       <c r="M621" s="3"/>
       <c r="N621" s="3"/>
       <c r="O621" s="3"/>
-      <c r="P621" s="6"/>
+      <c r="P621" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="17.25">
       <c r="A622" s="3"/>
@@ -11886,7 +11880,7 @@
       <c r="M622" s="3"/>
       <c r="N622" s="3"/>
       <c r="O622" s="3"/>
-      <c r="P622" s="6"/>
+      <c r="P622" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="17.25">
       <c r="A623" s="3"/>
@@ -11904,7 +11898,7 @@
       <c r="M623" s="3"/>
       <c r="N623" s="3"/>
       <c r="O623" s="3"/>
-      <c r="P623" s="6"/>
+      <c r="P623" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="17.25">
       <c r="A624" s="3"/>
@@ -11922,7 +11916,7 @@
       <c r="M624" s="3"/>
       <c r="N624" s="3"/>
       <c r="O624" s="3"/>
-      <c r="P624" s="6"/>
+      <c r="P624" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="17.25">
       <c r="A625" s="3"/>
@@ -11940,7 +11934,7 @@
       <c r="M625" s="3"/>
       <c r="N625" s="3"/>
       <c r="O625" s="3"/>
-      <c r="P625" s="6"/>
+      <c r="P625" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="17.25">
       <c r="A626" s="3"/>
@@ -11958,7 +11952,7 @@
       <c r="M626" s="3"/>
       <c r="N626" s="3"/>
       <c r="O626" s="3"/>
-      <c r="P626" s="6"/>
+      <c r="P626" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="17.25">
       <c r="A627" s="3"/>
@@ -11976,7 +11970,7 @@
       <c r="M627" s="3"/>
       <c r="N627" s="3"/>
       <c r="O627" s="3"/>
-      <c r="P627" s="6"/>
+      <c r="P627" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="17.25">
       <c r="A628" s="3"/>
@@ -11994,7 +11988,7 @@
       <c r="M628" s="3"/>
       <c r="N628" s="3"/>
       <c r="O628" s="3"/>
-      <c r="P628" s="6"/>
+      <c r="P628" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="17.25">
       <c r="A629" s="3"/>
@@ -12012,7 +12006,7 @@
       <c r="M629" s="3"/>
       <c r="N629" s="3"/>
       <c r="O629" s="3"/>
-      <c r="P629" s="6"/>
+      <c r="P629" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="17.25">
       <c r="A630" s="3"/>
@@ -12030,7 +12024,7 @@
       <c r="M630" s="3"/>
       <c r="N630" s="3"/>
       <c r="O630" s="3"/>
-      <c r="P630" s="6"/>
+      <c r="P630" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="17.25">
       <c r="A631" s="3"/>
@@ -12048,7 +12042,7 @@
       <c r="M631" s="3"/>
       <c r="N631" s="3"/>
       <c r="O631" s="3"/>
-      <c r="P631" s="6"/>
+      <c r="P631" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="17.25">
       <c r="A632" s="3"/>
@@ -12066,7 +12060,7 @@
       <c r="M632" s="3"/>
       <c r="N632" s="3"/>
       <c r="O632" s="3"/>
-      <c r="P632" s="6"/>
+      <c r="P632" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="17.25">
       <c r="A633" s="3"/>
@@ -12084,7 +12078,7 @@
       <c r="M633" s="3"/>
       <c r="N633" s="3"/>
       <c r="O633" s="3"/>
-      <c r="P633" s="6"/>
+      <c r="P633" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="17.25">
       <c r="A634" s="3"/>
@@ -12102,7 +12096,7 @@
       <c r="M634" s="3"/>
       <c r="N634" s="3"/>
       <c r="O634" s="3"/>
-      <c r="P634" s="6"/>
+      <c r="P634" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="17.25">
       <c r="A635" s="3"/>
@@ -12120,7 +12114,7 @@
       <c r="M635" s="3"/>
       <c r="N635" s="3"/>
       <c r="O635" s="3"/>
-      <c r="P635" s="6"/>
+      <c r="P635" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="17.25">
       <c r="A636" s="3"/>
@@ -12138,7 +12132,7 @@
       <c r="M636" s="3"/>
       <c r="N636" s="3"/>
       <c r="O636" s="3"/>
-      <c r="P636" s="6"/>
+      <c r="P636" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="17.25">
       <c r="A637" s="3"/>
@@ -12156,7 +12150,7 @@
       <c r="M637" s="3"/>
       <c r="N637" s="3"/>
       <c r="O637" s="3"/>
-      <c r="P637" s="6"/>
+      <c r="P637" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="17.25">
       <c r="A638" s="3"/>
@@ -12174,7 +12168,7 @@
       <c r="M638" s="3"/>
       <c r="N638" s="3"/>
       <c r="O638" s="3"/>
-      <c r="P638" s="6"/>
+      <c r="P638" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="17.25">
       <c r="A639" s="3"/>
@@ -12192,7 +12186,7 @@
       <c r="M639" s="3"/>
       <c r="N639" s="3"/>
       <c r="O639" s="3"/>
-      <c r="P639" s="6"/>
+      <c r="P639" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="17.25">
       <c r="A640" s="3"/>
@@ -12210,7 +12204,7 @@
       <c r="M640" s="3"/>
       <c r="N640" s="3"/>
       <c r="O640" s="3"/>
-      <c r="P640" s="6"/>
+      <c r="P640" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="17.25">
       <c r="A641" s="3"/>
@@ -12228,7 +12222,7 @@
       <c r="M641" s="3"/>
       <c r="N641" s="3"/>
       <c r="O641" s="3"/>
-      <c r="P641" s="6"/>
+      <c r="P641" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="17.25">
       <c r="A642" s="3"/>
@@ -12246,7 +12240,7 @@
       <c r="M642" s="3"/>
       <c r="N642" s="3"/>
       <c r="O642" s="3"/>
-      <c r="P642" s="6"/>
+      <c r="P642" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="17.25">
       <c r="A643" s="3"/>
@@ -12264,7 +12258,7 @@
       <c r="M643" s="3"/>
       <c r="N643" s="3"/>
       <c r="O643" s="3"/>
-      <c r="P643" s="6"/>
+      <c r="P643" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="17.25">
       <c r="A644" s="3"/>
@@ -12282,7 +12276,7 @@
       <c r="M644" s="3"/>
       <c r="N644" s="3"/>
       <c r="O644" s="3"/>
-      <c r="P644" s="6"/>
+      <c r="P644" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="17.25">
       <c r="A645" s="3"/>
@@ -12300,7 +12294,7 @@
       <c r="M645" s="3"/>
       <c r="N645" s="3"/>
       <c r="O645" s="3"/>
-      <c r="P645" s="6"/>
+      <c r="P645" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="17.25">
       <c r="A646" s="3"/>
@@ -12318,7 +12312,7 @@
       <c r="M646" s="3"/>
       <c r="N646" s="3"/>
       <c r="O646" s="3"/>
-      <c r="P646" s="6"/>
+      <c r="P646" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="17.25">
       <c r="A647" s="3"/>
@@ -12336,7 +12330,7 @@
       <c r="M647" s="3"/>
       <c r="N647" s="3"/>
       <c r="O647" s="3"/>
-      <c r="P647" s="6"/>
+      <c r="P647" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="17.25">
       <c r="A648" s="3"/>
@@ -12354,7 +12348,7 @@
       <c r="M648" s="3"/>
       <c r="N648" s="3"/>
       <c r="O648" s="3"/>
-      <c r="P648" s="6"/>
+      <c r="P648" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="17.25">
       <c r="A649" s="3"/>
@@ -12372,7 +12366,7 @@
       <c r="M649" s="3"/>
       <c r="N649" s="3"/>
       <c r="O649" s="3"/>
-      <c r="P649" s="6"/>
+      <c r="P649" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="17.25">
       <c r="A650" s="3"/>
@@ -12390,7 +12384,7 @@
       <c r="M650" s="3"/>
       <c r="N650" s="3"/>
       <c r="O650" s="3"/>
-      <c r="P650" s="6"/>
+      <c r="P650" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="17.25">
       <c r="A651" s="3"/>
@@ -12408,7 +12402,7 @@
       <c r="M651" s="3"/>
       <c r="N651" s="3"/>
       <c r="O651" s="3"/>
-      <c r="P651" s="6"/>
+      <c r="P651" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="17.25">
       <c r="A652" s="3"/>
@@ -12426,7 +12420,7 @@
       <c r="M652" s="3"/>
       <c r="N652" s="3"/>
       <c r="O652" s="3"/>
-      <c r="P652" s="6"/>
+      <c r="P652" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="17.25">
       <c r="A653" s="3"/>
@@ -12444,7 +12438,7 @@
       <c r="M653" s="3"/>
       <c r="N653" s="3"/>
       <c r="O653" s="3"/>
-      <c r="P653" s="6"/>
+      <c r="P653" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="17.25">
       <c r="A654" s="3"/>
@@ -12462,7 +12456,7 @@
       <c r="M654" s="3"/>
       <c r="N654" s="3"/>
       <c r="O654" s="3"/>
-      <c r="P654" s="6"/>
+      <c r="P654" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="17.25">
       <c r="A655" s="3"/>
@@ -12480,7 +12474,7 @@
       <c r="M655" s="3"/>
       <c r="N655" s="3"/>
       <c r="O655" s="3"/>
-      <c r="P655" s="6"/>
+      <c r="P655" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="17.25">
       <c r="A656" s="3"/>
@@ -12498,7 +12492,7 @@
       <c r="M656" s="3"/>
       <c r="N656" s="3"/>
       <c r="O656" s="3"/>
-      <c r="P656" s="6"/>
+      <c r="P656" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="17.25">
       <c r="A657" s="3"/>
@@ -12516,7 +12510,7 @@
       <c r="M657" s="3"/>
       <c r="N657" s="3"/>
       <c r="O657" s="3"/>
-      <c r="P657" s="6"/>
+      <c r="P657" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="17.25">
       <c r="A658" s="3"/>
@@ -12534,7 +12528,7 @@
       <c r="M658" s="3"/>
       <c r="N658" s="3"/>
       <c r="O658" s="3"/>
-      <c r="P658" s="6"/>
+      <c r="P658" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="17.25">
       <c r="A659" s="3"/>
@@ -12552,7 +12546,7 @@
       <c r="M659" s="3"/>
       <c r="N659" s="3"/>
       <c r="O659" s="3"/>
-      <c r="P659" s="6"/>
+      <c r="P659" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="17.25">
       <c r="A660" s="3"/>
@@ -12570,7 +12564,7 @@
       <c r="M660" s="3"/>
       <c r="N660" s="3"/>
       <c r="O660" s="3"/>
-      <c r="P660" s="6"/>
+      <c r="P660" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="17.25">
       <c r="A661" s="3"/>
@@ -12588,7 +12582,7 @@
       <c r="M661" s="3"/>
       <c r="N661" s="3"/>
       <c r="O661" s="3"/>
-      <c r="P661" s="6"/>
+      <c r="P661" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="17.25">
       <c r="A662" s="3"/>
@@ -12606,7 +12600,7 @@
       <c r="M662" s="3"/>
       <c r="N662" s="3"/>
       <c r="O662" s="3"/>
-      <c r="P662" s="6"/>
+      <c r="P662" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="17.25">
       <c r="A663" s="3"/>
@@ -12624,7 +12618,7 @@
       <c r="M663" s="3"/>
       <c r="N663" s="3"/>
       <c r="O663" s="3"/>
-      <c r="P663" s="6"/>
+      <c r="P663" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="17.25">
       <c r="A664" s="3"/>
@@ -12642,7 +12636,7 @@
       <c r="M664" s="3"/>
       <c r="N664" s="3"/>
       <c r="O664" s="3"/>
-      <c r="P664" s="6"/>
+      <c r="P664" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="17.25">
       <c r="A665" s="3"/>
@@ -12660,7 +12654,7 @@
       <c r="M665" s="3"/>
       <c r="N665" s="3"/>
       <c r="O665" s="3"/>
-      <c r="P665" s="6"/>
+      <c r="P665" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="17.25">
       <c r="A666" s="3"/>
@@ -12678,7 +12672,7 @@
       <c r="M666" s="3"/>
       <c r="N666" s="3"/>
       <c r="O666" s="3"/>
-      <c r="P666" s="6"/>
+      <c r="P666" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="17.25">
       <c r="A667" s="3"/>
@@ -12696,7 +12690,7 @@
       <c r="M667" s="3"/>
       <c r="N667" s="3"/>
       <c r="O667" s="3"/>
-      <c r="P667" s="6"/>
+      <c r="P667" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="17.25">
       <c r="A668" s="3"/>
@@ -12714,7 +12708,7 @@
       <c r="M668" s="3"/>
       <c r="N668" s="3"/>
       <c r="O668" s="3"/>
-      <c r="P668" s="6"/>
+      <c r="P668" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="17.25">
       <c r="A669" s="3"/>
@@ -12732,7 +12726,7 @@
       <c r="M669" s="3"/>
       <c r="N669" s="3"/>
       <c r="O669" s="3"/>
-      <c r="P669" s="6"/>
+      <c r="P669" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="17.25">
       <c r="A670" s="3"/>
@@ -12750,7 +12744,7 @@
       <c r="M670" s="3"/>
       <c r="N670" s="3"/>
       <c r="O670" s="3"/>
-      <c r="P670" s="6"/>
+      <c r="P670" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="17.25">
       <c r="A671" s="3"/>
@@ -12768,7 +12762,7 @@
       <c r="M671" s="3"/>
       <c r="N671" s="3"/>
       <c r="O671" s="3"/>
-      <c r="P671" s="6"/>
+      <c r="P671" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="17.25">
       <c r="A672" s="3"/>
@@ -12786,7 +12780,7 @@
       <c r="M672" s="3"/>
       <c r="N672" s="3"/>
       <c r="O672" s="3"/>
-      <c r="P672" s="6"/>
+      <c r="P672" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="17.25">
       <c r="A673" s="3"/>
@@ -12804,7 +12798,7 @@
       <c r="M673" s="3"/>
       <c r="N673" s="3"/>
       <c r="O673" s="3"/>
-      <c r="P673" s="6"/>
+      <c r="P673" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="17.25">
       <c r="A674" s="3"/>
@@ -12822,7 +12816,7 @@
       <c r="M674" s="3"/>
       <c r="N674" s="3"/>
       <c r="O674" s="3"/>
-      <c r="P674" s="6"/>
+      <c r="P674" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="17.25">
       <c r="A675" s="3"/>
@@ -12840,7 +12834,7 @@
       <c r="M675" s="3"/>
       <c r="N675" s="3"/>
       <c r="O675" s="3"/>
-      <c r="P675" s="6"/>
+      <c r="P675" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="17.25">
       <c r="A676" s="3"/>
@@ -12858,7 +12852,7 @@
       <c r="M676" s="3"/>
       <c r="N676" s="3"/>
       <c r="O676" s="3"/>
-      <c r="P676" s="6"/>
+      <c r="P676" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="17.25">
       <c r="A677" s="3"/>
@@ -12876,7 +12870,7 @@
       <c r="M677" s="3"/>
       <c r="N677" s="3"/>
       <c r="O677" s="3"/>
-      <c r="P677" s="6"/>
+      <c r="P677" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="17.25">
       <c r="A678" s="3"/>
@@ -12894,7 +12888,7 @@
       <c r="M678" s="3"/>
       <c r="N678" s="3"/>
       <c r="O678" s="3"/>
-      <c r="P678" s="6"/>
+      <c r="P678" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="17.25">
       <c r="A679" s="3"/>
@@ -12912,7 +12906,7 @@
       <c r="M679" s="3"/>
       <c r="N679" s="3"/>
       <c r="O679" s="3"/>
-      <c r="P679" s="6"/>
+      <c r="P679" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="17.25">
       <c r="A680" s="3"/>
@@ -12930,7 +12924,7 @@
       <c r="M680" s="3"/>
       <c r="N680" s="3"/>
       <c r="O680" s="3"/>
-      <c r="P680" s="6"/>
+      <c r="P680" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="17.25">
       <c r="A681" s="3"/>
@@ -12948,7 +12942,7 @@
       <c r="M681" s="3"/>
       <c r="N681" s="3"/>
       <c r="O681" s="3"/>
-      <c r="P681" s="6"/>
+      <c r="P681" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="17.25">
       <c r="A682" s="3"/>
@@ -12966,7 +12960,7 @@
       <c r="M682" s="3"/>
       <c r="N682" s="3"/>
       <c r="O682" s="3"/>
-      <c r="P682" s="6"/>
+      <c r="P682" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="17.25">
       <c r="A683" s="3"/>
@@ -12984,7 +12978,7 @@
       <c r="M683" s="3"/>
       <c r="N683" s="3"/>
       <c r="O683" s="3"/>
-      <c r="P683" s="6"/>
+      <c r="P683" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="17.25">
       <c r="A684" s="3"/>
@@ -13002,7 +12996,7 @@
       <c r="M684" s="3"/>
       <c r="N684" s="3"/>
       <c r="O684" s="3"/>
-      <c r="P684" s="6"/>
+      <c r="P684" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="17.25">
       <c r="A685" s="3"/>
@@ -13020,7 +13014,7 @@
       <c r="M685" s="3"/>
       <c r="N685" s="3"/>
       <c r="O685" s="3"/>
-      <c r="P685" s="6"/>
+      <c r="P685" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="17.25">
       <c r="A686" s="3"/>
@@ -13038,7 +13032,7 @@
       <c r="M686" s="3"/>
       <c r="N686" s="3"/>
       <c r="O686" s="3"/>
-      <c r="P686" s="6"/>
+      <c r="P686" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="17.25">
       <c r="A687" s="3"/>
@@ -13056,7 +13050,7 @@
       <c r="M687" s="3"/>
       <c r="N687" s="3"/>
       <c r="O687" s="3"/>
-      <c r="P687" s="6"/>
+      <c r="P687" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="17.25">
       <c r="A688" s="3"/>
@@ -13074,7 +13068,7 @@
       <c r="M688" s="3"/>
       <c r="N688" s="3"/>
       <c r="O688" s="3"/>
-      <c r="P688" s="6"/>
+      <c r="P688" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="17.25">
       <c r="A689" s="3"/>
@@ -13092,7 +13086,7 @@
       <c r="M689" s="3"/>
       <c r="N689" s="3"/>
       <c r="O689" s="3"/>
-      <c r="P689" s="6"/>
+      <c r="P689" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="17.25">
       <c r="A690" s="3"/>
@@ -13110,7 +13104,7 @@
       <c r="M690" s="3"/>
       <c r="N690" s="3"/>
       <c r="O690" s="3"/>
-      <c r="P690" s="6"/>
+      <c r="P690" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="17.25">
       <c r="A691" s="3"/>
@@ -13128,7 +13122,7 @@
       <c r="M691" s="3"/>
       <c r="N691" s="3"/>
       <c r="O691" s="3"/>
-      <c r="P691" s="6"/>
+      <c r="P691" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="17.25">
       <c r="A692" s="3"/>
@@ -13146,7 +13140,7 @@
       <c r="M692" s="3"/>
       <c r="N692" s="3"/>
       <c r="O692" s="3"/>
-      <c r="P692" s="6"/>
+      <c r="P692" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="17.25">
       <c r="A693" s="3"/>
@@ -13164,7 +13158,7 @@
       <c r="M693" s="3"/>
       <c r="N693" s="3"/>
       <c r="O693" s="3"/>
-      <c r="P693" s="6"/>
+      <c r="P693" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="17.25">
       <c r="A694" s="3"/>
@@ -13182,7 +13176,7 @@
       <c r="M694" s="3"/>
       <c r="N694" s="3"/>
       <c r="O694" s="3"/>
-      <c r="P694" s="6"/>
+      <c r="P694" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="17.25">
       <c r="A695" s="3"/>
@@ -13200,7 +13194,7 @@
       <c r="M695" s="3"/>
       <c r="N695" s="3"/>
       <c r="O695" s="3"/>
-      <c r="P695" s="6"/>
+      <c r="P695" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="17.25">
       <c r="A696" s="3"/>
@@ -13218,7 +13212,7 @@
       <c r="M696" s="3"/>
       <c r="N696" s="3"/>
       <c r="O696" s="3"/>
-      <c r="P696" s="6"/>
+      <c r="P696" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="17.25">
       <c r="A697" s="3"/>
@@ -13236,7 +13230,7 @@
       <c r="M697" s="3"/>
       <c r="N697" s="3"/>
       <c r="O697" s="3"/>
-      <c r="P697" s="6"/>
+      <c r="P697" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="17.25">
       <c r="A698" s="3"/>
@@ -13254,7 +13248,7 @@
       <c r="M698" s="3"/>
       <c r="N698" s="3"/>
       <c r="O698" s="3"/>
-      <c r="P698" s="6"/>
+      <c r="P698" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="17.25">
       <c r="A699" s="3"/>
@@ -13272,7 +13266,7 @@
       <c r="M699" s="3"/>
       <c r="N699" s="3"/>
       <c r="O699" s="3"/>
-      <c r="P699" s="6"/>
+      <c r="P699" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="17.25">
       <c r="A700" s="3"/>
@@ -13290,7 +13284,7 @@
       <c r="M700" s="3"/>
       <c r="N700" s="3"/>
       <c r="O700" s="3"/>
-      <c r="P700" s="6"/>
+      <c r="P700" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="17.25">
       <c r="A701" s="3"/>
@@ -13308,7 +13302,7 @@
       <c r="M701" s="3"/>
       <c r="N701" s="3"/>
       <c r="O701" s="3"/>
-      <c r="P701" s="6"/>
+      <c r="P701" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="17.25">
       <c r="A702" s="3"/>
@@ -13326,7 +13320,7 @@
       <c r="M702" s="3"/>
       <c r="N702" s="3"/>
       <c r="O702" s="3"/>
-      <c r="P702" s="6"/>
+      <c r="P702" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="17.25">
       <c r="A703" s="3"/>
@@ -13344,7 +13338,7 @@
       <c r="M703" s="3"/>
       <c r="N703" s="3"/>
       <c r="O703" s="3"/>
-      <c r="P703" s="6"/>
+      <c r="P703" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="17.25">
       <c r="A704" s="3"/>
@@ -13362,7 +13356,7 @@
       <c r="M704" s="3"/>
       <c r="N704" s="3"/>
       <c r="O704" s="3"/>
-      <c r="P704" s="6"/>
+      <c r="P704" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="17.25">
       <c r="A705" s="3"/>
@@ -13380,7 +13374,7 @@
       <c r="M705" s="3"/>
       <c r="N705" s="3"/>
       <c r="O705" s="3"/>
-      <c r="P705" s="6"/>
+      <c r="P705" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="17.25">
       <c r="A706" s="3"/>
@@ -13398,7 +13392,7 @@
       <c r="M706" s="3"/>
       <c r="N706" s="3"/>
       <c r="O706" s="3"/>
-      <c r="P706" s="6"/>
+      <c r="P706" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="17.25">
       <c r="A707" s="3"/>
@@ -13416,7 +13410,7 @@
       <c r="M707" s="3"/>
       <c r="N707" s="3"/>
       <c r="O707" s="3"/>
-      <c r="P707" s="6"/>
+      <c r="P707" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="17.25">
       <c r="A708" s="3"/>
@@ -13434,7 +13428,7 @@
       <c r="M708" s="3"/>
       <c r="N708" s="3"/>
       <c r="O708" s="3"/>
-      <c r="P708" s="6"/>
+      <c r="P708" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="17.25">
       <c r="A709" s="3"/>
@@ -13452,7 +13446,7 @@
       <c r="M709" s="3"/>
       <c r="N709" s="3"/>
       <c r="O709" s="3"/>
-      <c r="P709" s="6"/>
+      <c r="P709" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="17.25">
       <c r="A710" s="3"/>
@@ -13470,7 +13464,7 @@
       <c r="M710" s="3"/>
       <c r="N710" s="3"/>
       <c r="O710" s="3"/>
-      <c r="P710" s="6"/>
+      <c r="P710" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="17.25">
       <c r="A711" s="3"/>
@@ -13488,7 +13482,7 @@
       <c r="M711" s="3"/>
       <c r="N711" s="3"/>
       <c r="O711" s="3"/>
-      <c r="P711" s="6"/>
+      <c r="P711" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="17.25">
       <c r="A712" s="3"/>
@@ -13506,7 +13500,7 @@
       <c r="M712" s="3"/>
       <c r="N712" s="3"/>
       <c r="O712" s="3"/>
-      <c r="P712" s="6"/>
+      <c r="P712" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="17.25">
       <c r="A713" s="3"/>
@@ -13524,7 +13518,7 @@
       <c r="M713" s="3"/>
       <c r="N713" s="3"/>
       <c r="O713" s="3"/>
-      <c r="P713" s="6"/>
+      <c r="P713" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="17.25">
       <c r="A714" s="3"/>
@@ -13542,7 +13536,7 @@
       <c r="M714" s="3"/>
       <c r="N714" s="3"/>
       <c r="O714" s="3"/>
-      <c r="P714" s="6"/>
+      <c r="P714" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="17.25">
       <c r="A715" s="3"/>
@@ -13560,7 +13554,7 @@
       <c r="M715" s="3"/>
       <c r="N715" s="3"/>
       <c r="O715" s="3"/>
-      <c r="P715" s="6"/>
+      <c r="P715" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="17.25">
       <c r="A716" s="3"/>
@@ -13578,7 +13572,7 @@
       <c r="M716" s="3"/>
       <c r="N716" s="3"/>
       <c r="O716" s="3"/>
-      <c r="P716" s="6"/>
+      <c r="P716" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="17.25">
       <c r="A717" s="3"/>
@@ -13596,7 +13590,7 @@
       <c r="M717" s="3"/>
       <c r="N717" s="3"/>
       <c r="O717" s="3"/>
-      <c r="P717" s="6"/>
+      <c r="P717" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="17.25">
       <c r="A718" s="3"/>
@@ -13614,7 +13608,7 @@
       <c r="M718" s="3"/>
       <c r="N718" s="3"/>
       <c r="O718" s="3"/>
-      <c r="P718" s="6"/>
+      <c r="P718" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="17.25">
       <c r="A719" s="3"/>
@@ -13632,7 +13626,7 @@
       <c r="M719" s="3"/>
       <c r="N719" s="3"/>
       <c r="O719" s="3"/>
-      <c r="P719" s="6"/>
+      <c r="P719" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="17.25">
       <c r="A720" s="3"/>
@@ -13650,7 +13644,7 @@
       <c r="M720" s="3"/>
       <c r="N720" s="3"/>
       <c r="O720" s="3"/>
-      <c r="P720" s="6"/>
+      <c r="P720" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="17.25">
       <c r="A721" s="3"/>
@@ -13668,7 +13662,7 @@
       <c r="M721" s="3"/>
       <c r="N721" s="3"/>
       <c r="O721" s="3"/>
-      <c r="P721" s="6"/>
+      <c r="P721" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="17.25">
       <c r="A722" s="3"/>
@@ -13686,7 +13680,7 @@
       <c r="M722" s="3"/>
       <c r="N722" s="3"/>
       <c r="O722" s="3"/>
-      <c r="P722" s="6"/>
+      <c r="P722" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="17.25">
       <c r="A723" s="3"/>
@@ -13704,7 +13698,7 @@
       <c r="M723" s="3"/>
       <c r="N723" s="3"/>
       <c r="O723" s="3"/>
-      <c r="P723" s="6"/>
+      <c r="P723" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="17.25">
       <c r="A724" s="3"/>
@@ -13722,7 +13716,7 @@
       <c r="M724" s="3"/>
       <c r="N724" s="3"/>
       <c r="O724" s="3"/>
-      <c r="P724" s="6"/>
+      <c r="P724" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="17.25">
       <c r="A725" s="3"/>
@@ -13740,7 +13734,7 @@
       <c r="M725" s="3"/>
       <c r="N725" s="3"/>
       <c r="O725" s="3"/>
-      <c r="P725" s="6"/>
+      <c r="P725" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="17.25">
       <c r="A726" s="3"/>
@@ -13758,7 +13752,7 @@
       <c r="M726" s="3"/>
       <c r="N726" s="3"/>
       <c r="O726" s="3"/>
-      <c r="P726" s="6"/>
+      <c r="P726" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="17.25">
       <c r="A727" s="3"/>
@@ -13776,7 +13770,7 @@
       <c r="M727" s="3"/>
       <c r="N727" s="3"/>
       <c r="O727" s="3"/>
-      <c r="P727" s="6"/>
+      <c r="P727" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="17.25">
       <c r="A728" s="3"/>
@@ -13794,7 +13788,7 @@
       <c r="M728" s="3"/>
       <c r="N728" s="3"/>
       <c r="O728" s="3"/>
-      <c r="P728" s="6"/>
+      <c r="P728" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="17.25">
       <c r="A729" s="3"/>
@@ -13812,7 +13806,7 @@
       <c r="M729" s="3"/>
       <c r="N729" s="3"/>
       <c r="O729" s="3"/>
-      <c r="P729" s="6"/>
+      <c r="P729" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="17.25">
       <c r="A730" s="3"/>
@@ -13830,7 +13824,7 @@
       <c r="M730" s="3"/>
       <c r="N730" s="3"/>
       <c r="O730" s="3"/>
-      <c r="P730" s="6"/>
+      <c r="P730" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="17.25">
       <c r="A731" s="3"/>
@@ -13848,7 +13842,7 @@
       <c r="M731" s="3"/>
       <c r="N731" s="3"/>
       <c r="O731" s="3"/>
-      <c r="P731" s="6"/>
+      <c r="P731" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="17.25">
       <c r="A732" s="3"/>
@@ -13866,7 +13860,7 @@
       <c r="M732" s="3"/>
       <c r="N732" s="3"/>
       <c r="O732" s="3"/>
-      <c r="P732" s="6"/>
+      <c r="P732" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="17.25">
       <c r="A733" s="3"/>
@@ -13884,7 +13878,7 @@
       <c r="M733" s="3"/>
       <c r="N733" s="3"/>
       <c r="O733" s="3"/>
-      <c r="P733" s="6"/>
+      <c r="P733" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="17.25">
       <c r="A734" s="3"/>
@@ -13902,7 +13896,7 @@
       <c r="M734" s="3"/>
       <c r="N734" s="3"/>
       <c r="O734" s="3"/>
-      <c r="P734" s="6"/>
+      <c r="P734" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="17.25">
       <c r="A735" s="3"/>
@@ -13920,7 +13914,7 @@
       <c r="M735" s="3"/>
       <c r="N735" s="3"/>
       <c r="O735" s="3"/>
-      <c r="P735" s="6"/>
+      <c r="P735" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="17.25">
       <c r="A736" s="3"/>
@@ -13938,7 +13932,7 @@
       <c r="M736" s="3"/>
       <c r="N736" s="3"/>
       <c r="O736" s="3"/>
-      <c r="P736" s="6"/>
+      <c r="P736" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="17.25">
       <c r="A737" s="3"/>
@@ -13956,7 +13950,7 @@
       <c r="M737" s="3"/>
       <c r="N737" s="3"/>
       <c r="O737" s="3"/>
-      <c r="P737" s="6"/>
+      <c r="P737" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="17.25">
       <c r="A738" s="3"/>
@@ -13974,7 +13968,7 @@
       <c r="M738" s="3"/>
       <c r="N738" s="3"/>
       <c r="O738" s="3"/>
-      <c r="P738" s="6"/>
+      <c r="P738" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="17.25">
       <c r="A739" s="3"/>
@@ -13992,7 +13986,7 @@
       <c r="M739" s="3"/>
       <c r="N739" s="3"/>
       <c r="O739" s="3"/>
-      <c r="P739" s="6"/>
+      <c r="P739" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="17.25">
       <c r="A740" s="3"/>
@@ -14010,7 +14004,7 @@
       <c r="M740" s="3"/>
       <c r="N740" s="3"/>
       <c r="O740" s="3"/>
-      <c r="P740" s="6"/>
+      <c r="P740" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="17.25">
       <c r="A741" s="3"/>
@@ -14028,7 +14022,7 @@
       <c r="M741" s="3"/>
       <c r="N741" s="3"/>
       <c r="O741" s="3"/>
-      <c r="P741" s="6"/>
+      <c r="P741" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="17.25">
       <c r="A742" s="3"/>
@@ -14046,7 +14040,7 @@
       <c r="M742" s="3"/>
       <c r="N742" s="3"/>
       <c r="O742" s="3"/>
-      <c r="P742" s="6"/>
+      <c r="P742" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="17.25">
       <c r="A743" s="3"/>
@@ -14064,7 +14058,7 @@
       <c r="M743" s="3"/>
       <c r="N743" s="3"/>
       <c r="O743" s="3"/>
-      <c r="P743" s="6"/>
+      <c r="P743" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="17.25">
       <c r="A744" s="3"/>
@@ -14082,7 +14076,7 @@
       <c r="M744" s="3"/>
       <c r="N744" s="3"/>
       <c r="O744" s="3"/>
-      <c r="P744" s="6"/>
+      <c r="P744" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="17.25">
       <c r="A745" s="3"/>
@@ -14100,7 +14094,7 @@
       <c r="M745" s="3"/>
       <c r="N745" s="3"/>
       <c r="O745" s="3"/>
-      <c r="P745" s="6"/>
+      <c r="P745" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="17.25">
       <c r="A746" s="3"/>
@@ -14118,7 +14112,7 @@
       <c r="M746" s="3"/>
       <c r="N746" s="3"/>
       <c r="O746" s="3"/>
-      <c r="P746" s="6"/>
+      <c r="P746" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="17.25">
       <c r="A747" s="3"/>
@@ -14136,7 +14130,7 @@
       <c r="M747" s="3"/>
       <c r="N747" s="3"/>
       <c r="O747" s="3"/>
-      <c r="P747" s="6"/>
+      <c r="P747" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="17.25">
       <c r="A748" s="3"/>
@@ -14154,7 +14148,7 @@
       <c r="M748" s="3"/>
       <c r="N748" s="3"/>
       <c r="O748" s="3"/>
-      <c r="P748" s="6"/>
+      <c r="P748" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="17.25">
       <c r="A749" s="3"/>
@@ -14172,7 +14166,7 @@
       <c r="M749" s="3"/>
       <c r="N749" s="3"/>
       <c r="O749" s="3"/>
-      <c r="P749" s="6"/>
+      <c r="P749" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="17.25">
       <c r="A750" s="3"/>
@@ -14190,7 +14184,7 @@
       <c r="M750" s="3"/>
       <c r="N750" s="3"/>
       <c r="O750" s="3"/>
-      <c r="P750" s="6"/>
+      <c r="P750" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="17.25">
       <c r="A751" s="3"/>
@@ -14208,7 +14202,7 @@
       <c r="M751" s="3"/>
       <c r="N751" s="3"/>
       <c r="O751" s="3"/>
-      <c r="P751" s="6"/>
+      <c r="P751" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="17.25">
       <c r="A752" s="3"/>
@@ -14226,7 +14220,7 @@
       <c r="M752" s="3"/>
       <c r="N752" s="3"/>
       <c r="O752" s="3"/>
-      <c r="P752" s="6"/>
+      <c r="P752" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="17.25">
       <c r="A753" s="3"/>
@@ -14244,7 +14238,7 @@
       <c r="M753" s="3"/>
       <c r="N753" s="3"/>
       <c r="O753" s="3"/>
-      <c r="P753" s="6"/>
+      <c r="P753" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="17.25">
       <c r="A754" s="3"/>
@@ -14262,7 +14256,7 @@
       <c r="M754" s="3"/>
       <c r="N754" s="3"/>
       <c r="O754" s="3"/>
-      <c r="P754" s="6"/>
+      <c r="P754" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="17.25">
       <c r="A755" s="3"/>
@@ -14280,7 +14274,7 @@
       <c r="M755" s="3"/>
       <c r="N755" s="3"/>
       <c r="O755" s="3"/>
-      <c r="P755" s="6"/>
+      <c r="P755" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="17.25">
       <c r="A756" s="3"/>
@@ -14298,7 +14292,7 @@
       <c r="M756" s="3"/>
       <c r="N756" s="3"/>
       <c r="O756" s="3"/>
-      <c r="P756" s="6"/>
+      <c r="P756" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="17.25">
       <c r="A757" s="3"/>
@@ -14316,7 +14310,7 @@
       <c r="M757" s="3"/>
       <c r="N757" s="3"/>
       <c r="O757" s="3"/>
-      <c r="P757" s="6"/>
+      <c r="P757" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="17.25">
       <c r="A758" s="3"/>
@@ -14334,7 +14328,7 @@
       <c r="M758" s="3"/>
       <c r="N758" s="3"/>
       <c r="O758" s="3"/>
-      <c r="P758" s="6"/>
+      <c r="P758" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="17.25">
       <c r="A759" s="3"/>
@@ -14352,7 +14346,7 @@
       <c r="M759" s="3"/>
       <c r="N759" s="3"/>
       <c r="O759" s="3"/>
-      <c r="P759" s="6"/>
+      <c r="P759" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="17.25">
       <c r="A760" s="3"/>
@@ -14370,7 +14364,7 @@
       <c r="M760" s="3"/>
       <c r="N760" s="3"/>
       <c r="O760" s="3"/>
-      <c r="P760" s="6"/>
+      <c r="P760" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="17.25">
       <c r="A761" s="3"/>
@@ -14388,7 +14382,7 @@
       <c r="M761" s="3"/>
       <c r="N761" s="3"/>
       <c r="O761" s="3"/>
-      <c r="P761" s="6"/>
+      <c r="P761" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="17.25">
       <c r="A762" s="3"/>
@@ -14406,7 +14400,7 @@
       <c r="M762" s="3"/>
       <c r="N762" s="3"/>
       <c r="O762" s="3"/>
-      <c r="P762" s="6"/>
+      <c r="P762" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="17.25">
       <c r="A763" s="3"/>
@@ -14424,7 +14418,7 @@
       <c r="M763" s="3"/>
       <c r="N763" s="3"/>
       <c r="O763" s="3"/>
-      <c r="P763" s="6"/>
+      <c r="P763" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="17.25">
       <c r="A764" s="3"/>
@@ -14442,7 +14436,7 @@
       <c r="M764" s="3"/>
       <c r="N764" s="3"/>
       <c r="O764" s="3"/>
-      <c r="P764" s="6"/>
+      <c r="P764" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="17.25">
       <c r="A765" s="3"/>
@@ -14460,7 +14454,7 @@
       <c r="M765" s="3"/>
       <c r="N765" s="3"/>
       <c r="O765" s="3"/>
-      <c r="P765" s="6"/>
+      <c r="P765" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="17.25">
       <c r="A766" s="3"/>
@@ -14478,7 +14472,7 @@
       <c r="M766" s="3"/>
       <c r="N766" s="3"/>
       <c r="O766" s="3"/>
-      <c r="P766" s="6"/>
+      <c r="P766" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="17.25">
       <c r="A767" s="3"/>
@@ -14496,7 +14490,7 @@
       <c r="M767" s="3"/>
       <c r="N767" s="3"/>
       <c r="O767" s="3"/>
-      <c r="P767" s="6"/>
+      <c r="P767" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="17.25">
       <c r="A768" s="3"/>
@@ -14514,7 +14508,7 @@
       <c r="M768" s="3"/>
       <c r="N768" s="3"/>
       <c r="O768" s="3"/>
-      <c r="P768" s="6"/>
+      <c r="P768" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="17.25">
       <c r="A769" s="3"/>
@@ -14532,7 +14526,7 @@
       <c r="M769" s="3"/>
       <c r="N769" s="3"/>
       <c r="O769" s="3"/>
-      <c r="P769" s="6"/>
+      <c r="P769" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="17.25">
       <c r="A770" s="3"/>
@@ -14550,7 +14544,7 @@
       <c r="M770" s="3"/>
       <c r="N770" s="3"/>
       <c r="O770" s="3"/>
-      <c r="P770" s="6"/>
+      <c r="P770" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="17.25">
       <c r="A771" s="3"/>
@@ -14568,7 +14562,7 @@
       <c r="M771" s="3"/>
       <c r="N771" s="3"/>
       <c r="O771" s="3"/>
-      <c r="P771" s="6"/>
+      <c r="P771" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="17.25">
       <c r="A772" s="3"/>
@@ -14586,7 +14580,7 @@
       <c r="M772" s="3"/>
       <c r="N772" s="3"/>
       <c r="O772" s="3"/>
-      <c r="P772" s="6"/>
+      <c r="P772" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="17.25">
       <c r="A773" s="3"/>
@@ -14604,7 +14598,7 @@
       <c r="M773" s="3"/>
       <c r="N773" s="3"/>
       <c r="O773" s="3"/>
-      <c r="P773" s="6"/>
+      <c r="P773" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="17.25">
       <c r="A774" s="3"/>
@@ -14622,7 +14616,7 @@
       <c r="M774" s="3"/>
       <c r="N774" s="3"/>
       <c r="O774" s="3"/>
-      <c r="P774" s="6"/>
+      <c r="P774" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="17.25">
       <c r="A775" s="3"/>
@@ -14640,7 +14634,7 @@
       <c r="M775" s="3"/>
       <c r="N775" s="3"/>
       <c r="O775" s="3"/>
-      <c r="P775" s="6"/>
+      <c r="P775" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="17.25">
       <c r="A776" s="3"/>
@@ -14658,7 +14652,7 @@
       <c r="M776" s="3"/>
       <c r="N776" s="3"/>
       <c r="O776" s="3"/>
-      <c r="P776" s="6"/>
+      <c r="P776" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="17.25">
       <c r="A777" s="3"/>
@@ -14676,7 +14670,7 @@
       <c r="M777" s="3"/>
       <c r="N777" s="3"/>
       <c r="O777" s="3"/>
-      <c r="P777" s="6"/>
+      <c r="P777" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="17.25">
       <c r="A778" s="3"/>
@@ -14694,7 +14688,7 @@
       <c r="M778" s="3"/>
       <c r="N778" s="3"/>
       <c r="O778" s="3"/>
-      <c r="P778" s="6"/>
+      <c r="P778" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="17.25">
       <c r="A779" s="3"/>
@@ -14712,7 +14706,7 @@
       <c r="M779" s="3"/>
       <c r="N779" s="3"/>
       <c r="O779" s="3"/>
-      <c r="P779" s="6"/>
+      <c r="P779" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="17.25">
       <c r="A780" s="3"/>
@@ -14730,7 +14724,7 @@
       <c r="M780" s="3"/>
       <c r="N780" s="3"/>
       <c r="O780" s="3"/>
-      <c r="P780" s="6"/>
+      <c r="P780" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="17.25">
       <c r="A781" s="3"/>
@@ -14748,7 +14742,7 @@
       <c r="M781" s="3"/>
       <c r="N781" s="3"/>
       <c r="O781" s="3"/>
-      <c r="P781" s="6"/>
+      <c r="P781" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="17.25">
       <c r="A782" s="3"/>
@@ -14766,7 +14760,7 @@
       <c r="M782" s="3"/>
       <c r="N782" s="3"/>
       <c r="O782" s="3"/>
-      <c r="P782" s="6"/>
+      <c r="P782" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="17.25">
       <c r="A783" s="3"/>
@@ -14784,7 +14778,7 @@
       <c r="M783" s="3"/>
       <c r="N783" s="3"/>
       <c r="O783" s="3"/>
-      <c r="P783" s="6"/>
+      <c r="P783" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="17.25">
       <c r="A784" s="3"/>
@@ -14802,7 +14796,7 @@
       <c r="M784" s="3"/>
       <c r="N784" s="3"/>
       <c r="O784" s="3"/>
-      <c r="P784" s="6"/>
+      <c r="P784" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="17.25">
       <c r="A785" s="3"/>
@@ -14820,7 +14814,7 @@
       <c r="M785" s="3"/>
       <c r="N785" s="3"/>
       <c r="O785" s="3"/>
-      <c r="P785" s="6"/>
+      <c r="P785" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="17.25">
       <c r="A786" s="3"/>
@@ -14838,7 +14832,7 @@
       <c r="M786" s="3"/>
       <c r="N786" s="3"/>
       <c r="O786" s="3"/>
-      <c r="P786" s="6"/>
+      <c r="P786" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="17.25">
       <c r="A787" s="3"/>
@@ -14856,7 +14850,7 @@
       <c r="M787" s="3"/>
       <c r="N787" s="3"/>
       <c r="O787" s="3"/>
-      <c r="P787" s="6"/>
+      <c r="P787" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="17.25">
       <c r="A788" s="3"/>
@@ -14874,7 +14868,7 @@
       <c r="M788" s="3"/>
       <c r="N788" s="3"/>
       <c r="O788" s="3"/>
-      <c r="P788" s="6"/>
+      <c r="P788" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="17.25">
       <c r="A789" s="3"/>
@@ -14892,7 +14886,7 @@
       <c r="M789" s="3"/>
       <c r="N789" s="3"/>
       <c r="O789" s="3"/>
-      <c r="P789" s="6"/>
+      <c r="P789" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="17.25">
       <c r="A790" s="3"/>
@@ -14910,7 +14904,7 @@
       <c r="M790" s="3"/>
       <c r="N790" s="3"/>
       <c r="O790" s="3"/>
-      <c r="P790" s="6"/>
+      <c r="P790" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="17.25">
       <c r="A791" s="3"/>
@@ -14928,7 +14922,7 @@
       <c r="M791" s="3"/>
       <c r="N791" s="3"/>
       <c r="O791" s="3"/>
-      <c r="P791" s="6"/>
+      <c r="P791" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="17.25">
       <c r="A792" s="3"/>
@@ -14946,7 +14940,7 @@
       <c r="M792" s="3"/>
       <c r="N792" s="3"/>
       <c r="O792" s="3"/>
-      <c r="P792" s="6"/>
+      <c r="P792" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="17.25">
       <c r="A793" s="3"/>
@@ -14964,7 +14958,7 @@
       <c r="M793" s="3"/>
       <c r="N793" s="3"/>
       <c r="O793" s="3"/>
-      <c r="P793" s="6"/>
+      <c r="P793" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="17.25">
       <c r="A794" s="3"/>
@@ -14982,7 +14976,7 @@
       <c r="M794" s="3"/>
       <c r="N794" s="3"/>
       <c r="O794" s="3"/>
-      <c r="P794" s="6"/>
+      <c r="P794" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="17.25">
       <c r="A795" s="3"/>
@@ -15000,7 +14994,7 @@
       <c r="M795" s="3"/>
       <c r="N795" s="3"/>
       <c r="O795" s="3"/>
-      <c r="P795" s="6"/>
+      <c r="P795" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="17.25">
       <c r="A796" s="3"/>
@@ -15018,7 +15012,7 @@
       <c r="M796" s="3"/>
       <c r="N796" s="3"/>
       <c r="O796" s="3"/>
-      <c r="P796" s="6"/>
+      <c r="P796" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="17.25">
       <c r="A797" s="3"/>
@@ -15036,7 +15030,7 @@
       <c r="M797" s="3"/>
       <c r="N797" s="3"/>
       <c r="O797" s="3"/>
-      <c r="P797" s="6"/>
+      <c r="P797" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="17.25">
       <c r="A798" s="3"/>
@@ -15054,7 +15048,7 @@
       <c r="M798" s="3"/>
       <c r="N798" s="3"/>
       <c r="O798" s="3"/>
-      <c r="P798" s="6"/>
+      <c r="P798" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="17.25">
       <c r="A799" s="3"/>
@@ -15072,7 +15066,7 @@
       <c r="M799" s="3"/>
       <c r="N799" s="3"/>
       <c r="O799" s="3"/>
-      <c r="P799" s="6"/>
+      <c r="P799" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="17.25">
       <c r="A800" s="3"/>
@@ -15090,7 +15084,7 @@
       <c r="M800" s="3"/>
       <c r="N800" s="3"/>
       <c r="O800" s="3"/>
-      <c r="P800" s="6"/>
+      <c r="P800" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="17.25">
       <c r="A801" s="3"/>
@@ -15108,7 +15102,7 @@
       <c r="M801" s="3"/>
       <c r="N801" s="3"/>
       <c r="O801" s="3"/>
-      <c r="P801" s="6"/>
+      <c r="P801" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="17.25">
       <c r="A802" s="3"/>
@@ -15126,7 +15120,7 @@
       <c r="M802" s="3"/>
       <c r="N802" s="3"/>
       <c r="O802" s="3"/>
-      <c r="P802" s="6"/>
+      <c r="P802" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="17.25">
       <c r="A803" s="3"/>
@@ -15144,7 +15138,7 @@
       <c r="M803" s="3"/>
       <c r="N803" s="3"/>
       <c r="O803" s="3"/>
-      <c r="P803" s="6"/>
+      <c r="P803" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="17.25">
       <c r="A804" s="3"/>
@@ -15162,7 +15156,7 @@
       <c r="M804" s="3"/>
       <c r="N804" s="3"/>
       <c r="O804" s="3"/>
-      <c r="P804" s="6"/>
+      <c r="P804" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="17.25">
       <c r="A805" s="3"/>
@@ -15180,7 +15174,7 @@
       <c r="M805" s="3"/>
       <c r="N805" s="3"/>
       <c r="O805" s="3"/>
-      <c r="P805" s="6"/>
+      <c r="P805" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="17.25">
       <c r="A806" s="3"/>
@@ -15198,7 +15192,7 @@
       <c r="M806" s="3"/>
       <c r="N806" s="3"/>
       <c r="O806" s="3"/>
-      <c r="P806" s="6"/>
+      <c r="P806" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="17.25">
       <c r="A807" s="3"/>
@@ -15216,7 +15210,7 @@
       <c r="M807" s="3"/>
       <c r="N807" s="3"/>
       <c r="O807" s="3"/>
-      <c r="P807" s="6"/>
+      <c r="P807" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="17.25">
       <c r="A808" s="3"/>
@@ -15234,7 +15228,7 @@
       <c r="M808" s="3"/>
       <c r="N808" s="3"/>
       <c r="O808" s="3"/>
-      <c r="P808" s="6"/>
+      <c r="P808" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="17.25">
       <c r="A809" s="3"/>
@@ -15252,7 +15246,7 @@
       <c r="M809" s="3"/>
       <c r="N809" s="3"/>
       <c r="O809" s="3"/>
-      <c r="P809" s="6"/>
+      <c r="P809" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="17.25">
       <c r="A810" s="3"/>
@@ -15270,7 +15264,7 @@
       <c r="M810" s="3"/>
       <c r="N810" s="3"/>
       <c r="O810" s="3"/>
-      <c r="P810" s="6"/>
+      <c r="P810" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="17.25">
       <c r="A811" s="3"/>
@@ -15288,7 +15282,7 @@
       <c r="M811" s="3"/>
       <c r="N811" s="3"/>
       <c r="O811" s="3"/>
-      <c r="P811" s="6"/>
+      <c r="P811" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="17.25">
       <c r="A812" s="3"/>
@@ -15306,7 +15300,7 @@
       <c r="M812" s="3"/>
       <c r="N812" s="3"/>
       <c r="O812" s="3"/>
-      <c r="P812" s="6"/>
+      <c r="P812" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="17.25">
       <c r="A813" s="3"/>
@@ -15324,7 +15318,7 @@
       <c r="M813" s="3"/>
       <c r="N813" s="3"/>
       <c r="O813" s="3"/>
-      <c r="P813" s="6"/>
+      <c r="P813" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="17.25">
       <c r="A814" s="3"/>
@@ -15342,7 +15336,7 @@
       <c r="M814" s="3"/>
       <c r="N814" s="3"/>
       <c r="O814" s="3"/>
-      <c r="P814" s="6"/>
+      <c r="P814" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="17.25">
       <c r="A815" s="3"/>
@@ -15360,7 +15354,7 @@
       <c r="M815" s="3"/>
       <c r="N815" s="3"/>
       <c r="O815" s="3"/>
-      <c r="P815" s="6"/>
+      <c r="P815" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="17.25">
       <c r="A816" s="3"/>
@@ -15378,7 +15372,7 @@
       <c r="M816" s="3"/>
       <c r="N816" s="3"/>
       <c r="O816" s="3"/>
-      <c r="P816" s="6"/>
+      <c r="P816" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="17.25">
       <c r="A817" s="3"/>
@@ -15396,7 +15390,7 @@
       <c r="M817" s="3"/>
       <c r="N817" s="3"/>
       <c r="O817" s="3"/>
-      <c r="P817" s="6"/>
+      <c r="P817" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="17.25">
       <c r="A818" s="3"/>
@@ -15414,7 +15408,7 @@
       <c r="M818" s="3"/>
       <c r="N818" s="3"/>
       <c r="O818" s="3"/>
-      <c r="P818" s="6"/>
+      <c r="P818" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="17.25">
       <c r="A819" s="3"/>
@@ -15432,7 +15426,7 @@
       <c r="M819" s="3"/>
       <c r="N819" s="3"/>
       <c r="O819" s="3"/>
-      <c r="P819" s="6"/>
+      <c r="P819" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="17.25">
       <c r="A820" s="3"/>
@@ -15450,7 +15444,7 @@
       <c r="M820" s="3"/>
       <c r="N820" s="3"/>
       <c r="O820" s="3"/>
-      <c r="P820" s="6"/>
+      <c r="P820" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="17.25">
       <c r="A821" s="3"/>
@@ -15468,7 +15462,7 @@
       <c r="M821" s="3"/>
       <c r="N821" s="3"/>
       <c r="O821" s="3"/>
-      <c r="P821" s="6"/>
+      <c r="P821" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="17.25">
       <c r="A822" s="3"/>
@@ -15486,7 +15480,7 @@
       <c r="M822" s="3"/>
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
-      <c r="P822" s="6"/>
+      <c r="P822" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="17.25">
       <c r="A823" s="3"/>
@@ -15504,7 +15498,7 @@
       <c r="M823" s="3"/>
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
-      <c r="P823" s="6"/>
+      <c r="P823" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="17.25">
       <c r="A824" s="3"/>
@@ -15522,7 +15516,7 @@
       <c r="M824" s="3"/>
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
-      <c r="P824" s="6"/>
+      <c r="P824" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="17.25">
       <c r="A825" s="3"/>
@@ -15540,7 +15534,7 @@
       <c r="M825" s="3"/>
       <c r="N825" s="3"/>
       <c r="O825" s="3"/>
-      <c r="P825" s="6"/>
+      <c r="P825" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="17.25">
       <c r="A826" s="3"/>
@@ -15558,7 +15552,7 @@
       <c r="M826" s="3"/>
       <c r="N826" s="3"/>
       <c r="O826" s="3"/>
-      <c r="P826" s="6"/>
+      <c r="P826" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="17.25">
       <c r="A827" s="3"/>
@@ -15576,7 +15570,7 @@
       <c r="M827" s="3"/>
       <c r="N827" s="3"/>
       <c r="O827" s="3"/>
-      <c r="P827" s="6"/>
+      <c r="P827" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="17.25">
       <c r="A828" s="3"/>
@@ -15594,7 +15588,7 @@
       <c r="M828" s="3"/>
       <c r="N828" s="3"/>
       <c r="O828" s="3"/>
-      <c r="P828" s="6"/>
+      <c r="P828" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="17.25">
       <c r="A829" s="3"/>
@@ -15612,7 +15606,7 @@
       <c r="M829" s="3"/>
       <c r="N829" s="3"/>
       <c r="O829" s="3"/>
-      <c r="P829" s="6"/>
+      <c r="P829" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="17.25">
       <c r="A830" s="3"/>
@@ -15630,7 +15624,7 @@
       <c r="M830" s="3"/>
       <c r="N830" s="3"/>
       <c r="O830" s="3"/>
-      <c r="P830" s="6"/>
+      <c r="P830" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="17.25">
       <c r="A831" s="3"/>
@@ -15648,7 +15642,7 @@
       <c r="M831" s="3"/>
       <c r="N831" s="3"/>
       <c r="O831" s="3"/>
-      <c r="P831" s="6"/>
+      <c r="P831" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="17.25">
       <c r="A832" s="3"/>
@@ -15666,7 +15660,7 @@
       <c r="M832" s="3"/>
       <c r="N832" s="3"/>
       <c r="O832" s="3"/>
-      <c r="P832" s="6"/>
+      <c r="P832" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="17.25">
       <c r="A833" s="3"/>
@@ -15684,7 +15678,7 @@
       <c r="M833" s="3"/>
       <c r="N833" s="3"/>
       <c r="O833" s="3"/>
-      <c r="P833" s="6"/>
+      <c r="P833" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="17.25">
       <c r="A834" s="3"/>
@@ -15702,7 +15696,7 @@
       <c r="M834" s="3"/>
       <c r="N834" s="3"/>
       <c r="O834" s="3"/>
-      <c r="P834" s="6"/>
+      <c r="P834" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="17.25">
       <c r="A835" s="3"/>
@@ -15720,7 +15714,7 @@
       <c r="M835" s="3"/>
       <c r="N835" s="3"/>
       <c r="O835" s="3"/>
-      <c r="P835" s="6"/>
+      <c r="P835" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="17.25">
       <c r="A836" s="3"/>
@@ -15738,7 +15732,7 @@
       <c r="M836" s="3"/>
       <c r="N836" s="3"/>
       <c r="O836" s="3"/>
-      <c r="P836" s="6"/>
+      <c r="P836" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="17.25">
       <c r="A837" s="3"/>
@@ -15756,7 +15750,7 @@
       <c r="M837" s="3"/>
       <c r="N837" s="3"/>
       <c r="O837" s="3"/>
-      <c r="P837" s="6"/>
+      <c r="P837" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="17.25">
       <c r="A838" s="3"/>
@@ -15774,7 +15768,7 @@
       <c r="M838" s="3"/>
       <c r="N838" s="3"/>
       <c r="O838" s="3"/>
-      <c r="P838" s="6"/>
+      <c r="P838" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="17.25">
       <c r="A839" s="3"/>
@@ -15792,7 +15786,7 @@
       <c r="M839" s="3"/>
       <c r="N839" s="3"/>
       <c r="O839" s="3"/>
-      <c r="P839" s="6"/>
+      <c r="P839" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="17.25">
       <c r="A840" s="3"/>
@@ -15810,7 +15804,7 @@
       <c r="M840" s="3"/>
       <c r="N840" s="3"/>
       <c r="O840" s="3"/>
-      <c r="P840" s="6"/>
+      <c r="P840" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="17.25">
       <c r="A841" s="3"/>
@@ -15828,7 +15822,7 @@
       <c r="M841" s="3"/>
       <c r="N841" s="3"/>
       <c r="O841" s="3"/>
-      <c r="P841" s="6"/>
+      <c r="P841" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="17.25">
       <c r="A842" s="3"/>
@@ -15846,7 +15840,7 @@
       <c r="M842" s="3"/>
       <c r="N842" s="3"/>
       <c r="O842" s="3"/>
-      <c r="P842" s="6"/>
+      <c r="P842" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="17.25">
       <c r="A843" s="3"/>
@@ -15864,7 +15858,7 @@
       <c r="M843" s="3"/>
       <c r="N843" s="3"/>
       <c r="O843" s="3"/>
-      <c r="P843" s="6"/>
+      <c r="P843" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="17.25">
       <c r="A844" s="3"/>
@@ -15882,7 +15876,7 @@
       <c r="M844" s="3"/>
       <c r="N844" s="3"/>
       <c r="O844" s="3"/>
-      <c r="P844" s="6"/>
+      <c r="P844" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="17.25">
       <c r="A845" s="3"/>
@@ -15900,7 +15894,7 @@
       <c r="M845" s="3"/>
       <c r="N845" s="3"/>
       <c r="O845" s="3"/>
-      <c r="P845" s="6"/>
+      <c r="P845" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="17.25">
       <c r="A846" s="3"/>
@@ -15918,7 +15912,7 @@
       <c r="M846" s="3"/>
       <c r="N846" s="3"/>
       <c r="O846" s="3"/>
-      <c r="P846" s="6"/>
+      <c r="P846" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="17.25">
       <c r="A847" s="3"/>
@@ -15936,7 +15930,7 @@
       <c r="M847" s="3"/>
       <c r="N847" s="3"/>
       <c r="O847" s="3"/>
-      <c r="P847" s="6"/>
+      <c r="P847" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="17.25">
       <c r="A848" s="3"/>
@@ -15954,7 +15948,7 @@
       <c r="M848" s="3"/>
       <c r="N848" s="3"/>
       <c r="O848" s="3"/>
-      <c r="P848" s="6"/>
+      <c r="P848" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="17.25">
       <c r="A849" s="3"/>
@@ -15972,7 +15966,7 @@
       <c r="M849" s="3"/>
       <c r="N849" s="3"/>
       <c r="O849" s="3"/>
-      <c r="P849" s="6"/>
+      <c r="P849" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="17.25">
       <c r="A850" s="3"/>
@@ -15990,7 +15984,7 @@
       <c r="M850" s="3"/>
       <c r="N850" s="3"/>
       <c r="O850" s="3"/>
-      <c r="P850" s="6"/>
+      <c r="P850" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="17.25">
       <c r="A851" s="3"/>
@@ -16008,7 +16002,7 @@
       <c r="M851" s="3"/>
       <c r="N851" s="3"/>
       <c r="O851" s="3"/>
-      <c r="P851" s="6"/>
+      <c r="P851" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="17.25">
       <c r="A852" s="3"/>
@@ -16026,7 +16020,7 @@
       <c r="M852" s="3"/>
       <c r="N852" s="3"/>
       <c r="O852" s="3"/>
-      <c r="P852" s="6"/>
+      <c r="P852" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="17.25">
       <c r="A853" s="3"/>
@@ -16044,7 +16038,7 @@
       <c r="M853" s="3"/>
       <c r="N853" s="3"/>
       <c r="O853" s="3"/>
-      <c r="P853" s="6"/>
+      <c r="P853" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="17.25">
       <c r="A854" s="3"/>
@@ -16062,7 +16056,7 @@
       <c r="M854" s="3"/>
       <c r="N854" s="3"/>
       <c r="O854" s="3"/>
-      <c r="P854" s="6"/>
+      <c r="P854" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="17.25">
       <c r="A855" s="3"/>
@@ -16080,7 +16074,7 @@
       <c r="M855" s="3"/>
       <c r="N855" s="3"/>
       <c r="O855" s="3"/>
-      <c r="P855" s="6"/>
+      <c r="P855" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="17.25">
       <c r="A856" s="3"/>
@@ -16098,7 +16092,7 @@
       <c r="M856" s="3"/>
       <c r="N856" s="3"/>
       <c r="O856" s="3"/>
-      <c r="P856" s="6"/>
+      <c r="P856" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="17.25">
       <c r="A857" s="3"/>
@@ -16116,7 +16110,7 @@
       <c r="M857" s="3"/>
       <c r="N857" s="3"/>
       <c r="O857" s="3"/>
-      <c r="P857" s="6"/>
+      <c r="P857" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="17.25">
       <c r="A858" s="3"/>
@@ -16134,7 +16128,7 @@
       <c r="M858" s="3"/>
       <c r="N858" s="3"/>
       <c r="O858" s="3"/>
-      <c r="P858" s="6"/>
+      <c r="P858" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="17.25">
       <c r="A859" s="3"/>
@@ -16152,7 +16146,7 @@
       <c r="M859" s="3"/>
       <c r="N859" s="3"/>
       <c r="O859" s="3"/>
-      <c r="P859" s="6"/>
+      <c r="P859" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="17.25">
       <c r="A860" s="3"/>
@@ -16170,7 +16164,7 @@
       <c r="M860" s="3"/>
       <c r="N860" s="3"/>
       <c r="O860" s="3"/>
-      <c r="P860" s="6"/>
+      <c r="P860" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="17.25">
       <c r="A861" s="3"/>
@@ -16188,7 +16182,7 @@
       <c r="M861" s="3"/>
       <c r="N861" s="3"/>
       <c r="O861" s="3"/>
-      <c r="P861" s="6"/>
+      <c r="P861" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="17.25">
       <c r="A862" s="3"/>
@@ -16206,7 +16200,7 @@
       <c r="M862" s="3"/>
       <c r="N862" s="3"/>
       <c r="O862" s="3"/>
-      <c r="P862" s="6"/>
+      <c r="P862" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="17.25">
       <c r="A863" s="3"/>
@@ -16224,7 +16218,7 @@
       <c r="M863" s="3"/>
       <c r="N863" s="3"/>
       <c r="O863" s="3"/>
-      <c r="P863" s="6"/>
+      <c r="P863" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="17.25">
       <c r="A864" s="3"/>
@@ -16242,7 +16236,7 @@
       <c r="M864" s="3"/>
       <c r="N864" s="3"/>
       <c r="O864" s="3"/>
-      <c r="P864" s="6"/>
+      <c r="P864" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="17.25">
       <c r="A865" s="3"/>
@@ -16260,7 +16254,7 @@
       <c r="M865" s="3"/>
       <c r="N865" s="3"/>
       <c r="O865" s="3"/>
-      <c r="P865" s="6"/>
+      <c r="P865" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="17.25">
       <c r="A866" s="3"/>
@@ -16278,7 +16272,7 @@
       <c r="M866" s="3"/>
       <c r="N866" s="3"/>
       <c r="O866" s="3"/>
-      <c r="P866" s="6"/>
+      <c r="P866" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="17.25">
       <c r="A867" s="3"/>
@@ -16296,7 +16290,7 @@
       <c r="M867" s="3"/>
       <c r="N867" s="3"/>
       <c r="O867" s="3"/>
-      <c r="P867" s="6"/>
+      <c r="P867" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="17.25">
       <c r="A868" s="3"/>
@@ -16314,7 +16308,7 @@
       <c r="M868" s="3"/>
       <c r="N868" s="3"/>
       <c r="O868" s="3"/>
-      <c r="P868" s="6"/>
+      <c r="P868" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="17.25">
       <c r="A869" s="3"/>
@@ -16332,7 +16326,7 @@
       <c r="M869" s="3"/>
       <c r="N869" s="3"/>
       <c r="O869" s="3"/>
-      <c r="P869" s="6"/>
+      <c r="P869" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="17.25">
       <c r="A870" s="3"/>
@@ -16350,7 +16344,7 @@
       <c r="M870" s="3"/>
       <c r="N870" s="3"/>
       <c r="O870" s="3"/>
-      <c r="P870" s="6"/>
+      <c r="P870" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="17.25">
       <c r="A871" s="3"/>
@@ -16368,7 +16362,7 @@
       <c r="M871" s="3"/>
       <c r="N871" s="3"/>
       <c r="O871" s="3"/>
-      <c r="P871" s="6"/>
+      <c r="P871" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="17.25">
       <c r="A872" s="3"/>
@@ -16386,7 +16380,7 @@
       <c r="M872" s="3"/>
       <c r="N872" s="3"/>
       <c r="O872" s="3"/>
-      <c r="P872" s="6"/>
+      <c r="P872" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="17.25">
       <c r="A873" s="3"/>
@@ -16404,7 +16398,7 @@
       <c r="M873" s="3"/>
       <c r="N873" s="3"/>
       <c r="O873" s="3"/>
-      <c r="P873" s="6"/>
+      <c r="P873" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="17.25">
       <c r="A874" s="3"/>
@@ -16422,7 +16416,7 @@
       <c r="M874" s="3"/>
       <c r="N874" s="3"/>
       <c r="O874" s="3"/>
-      <c r="P874" s="6"/>
+      <c r="P874" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="17.25">
       <c r="A875" s="3"/>
@@ -16440,7 +16434,7 @@
       <c r="M875" s="3"/>
       <c r="N875" s="3"/>
       <c r="O875" s="3"/>
-      <c r="P875" s="6"/>
+      <c r="P875" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="17.25">
       <c r="A876" s="3"/>
@@ -16458,7 +16452,7 @@
       <c r="M876" s="3"/>
       <c r="N876" s="3"/>
       <c r="O876" s="3"/>
-      <c r="P876" s="6"/>
+      <c r="P876" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="17.25">
       <c r="A877" s="3"/>
@@ -16476,7 +16470,7 @@
       <c r="M877" s="3"/>
       <c r="N877" s="3"/>
       <c r="O877" s="3"/>
-      <c r="P877" s="6"/>
+      <c r="P877" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="17.25">
       <c r="A878" s="3"/>
@@ -16494,7 +16488,7 @@
       <c r="M878" s="3"/>
       <c r="N878" s="3"/>
       <c r="O878" s="3"/>
-      <c r="P878" s="6"/>
+      <c r="P878" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="17.25">
       <c r="A879" s="3"/>
@@ -16512,7 +16506,7 @@
       <c r="M879" s="3"/>
       <c r="N879" s="3"/>
       <c r="O879" s="3"/>
-      <c r="P879" s="6"/>
+      <c r="P879" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="17.25">
       <c r="A880" s="3"/>
@@ -16530,7 +16524,7 @@
       <c r="M880" s="3"/>
       <c r="N880" s="3"/>
       <c r="O880" s="3"/>
-      <c r="P880" s="6"/>
+      <c r="P880" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="17.25">
       <c r="A881" s="3"/>
@@ -16548,7 +16542,7 @@
       <c r="M881" s="3"/>
       <c r="N881" s="3"/>
       <c r="O881" s="3"/>
-      <c r="P881" s="6"/>
+      <c r="P881" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="17.25">
       <c r="A882" s="3"/>
@@ -16566,7 +16560,7 @@
       <c r="M882" s="3"/>
       <c r="N882" s="3"/>
       <c r="O882" s="3"/>
-      <c r="P882" s="6"/>
+      <c r="P882" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="17.25">
       <c r="A883" s="3"/>
@@ -16584,7 +16578,7 @@
       <c r="M883" s="3"/>
       <c r="N883" s="3"/>
       <c r="O883" s="3"/>
-      <c r="P883" s="6"/>
+      <c r="P883" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="17.25">
       <c r="A884" s="3"/>
@@ -16602,7 +16596,7 @@
       <c r="M884" s="3"/>
       <c r="N884" s="3"/>
       <c r="O884" s="3"/>
-      <c r="P884" s="6"/>
+      <c r="P884" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="17.25">
       <c r="A885" s="3"/>
@@ -16620,7 +16614,7 @@
       <c r="M885" s="3"/>
       <c r="N885" s="3"/>
       <c r="O885" s="3"/>
-      <c r="P885" s="6"/>
+      <c r="P885" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="17.25">
       <c r="A886" s="3"/>
@@ -16638,7 +16632,7 @@
       <c r="M886" s="3"/>
       <c r="N886" s="3"/>
       <c r="O886" s="3"/>
-      <c r="P886" s="6"/>
+      <c r="P886" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="17.25">
       <c r="A887" s="3"/>
@@ -16656,7 +16650,7 @@
       <c r="M887" s="3"/>
       <c r="N887" s="3"/>
       <c r="O887" s="3"/>
-      <c r="P887" s="6"/>
+      <c r="P887" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="17.25">
       <c r="A888" s="3"/>
@@ -16674,7 +16668,7 @@
       <c r="M888" s="3"/>
       <c r="N888" s="3"/>
       <c r="O888" s="3"/>
-      <c r="P888" s="6"/>
+      <c r="P888" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="17.25">
       <c r="A889" s="3"/>
@@ -16692,7 +16686,7 @@
       <c r="M889" s="3"/>
       <c r="N889" s="3"/>
       <c r="O889" s="3"/>
-      <c r="P889" s="6"/>
+      <c r="P889" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="17.25">
       <c r="A890" s="3"/>
@@ -16710,7 +16704,7 @@
       <c r="M890" s="3"/>
       <c r="N890" s="3"/>
       <c r="O890" s="3"/>
-      <c r="P890" s="6"/>
+      <c r="P890" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="17.25">
       <c r="A891" s="3"/>
@@ -16728,7 +16722,7 @@
       <c r="M891" s="3"/>
       <c r="N891" s="3"/>
       <c r="O891" s="3"/>
-      <c r="P891" s="6"/>
+      <c r="P891" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="17.25">
       <c r="A892" s="3"/>
@@ -16746,7 +16740,7 @@
       <c r="M892" s="3"/>
       <c r="N892" s="3"/>
       <c r="O892" s="3"/>
-      <c r="P892" s="6"/>
+      <c r="P892" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="17.25">
       <c r="A893" s="3"/>
@@ -16764,7 +16758,7 @@
       <c r="M893" s="3"/>
       <c r="N893" s="3"/>
       <c r="O893" s="3"/>
-      <c r="P893" s="6"/>
+      <c r="P893" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="17.25">
       <c r="A894" s="3"/>
@@ -16782,7 +16776,7 @@
       <c r="M894" s="3"/>
       <c r="N894" s="3"/>
       <c r="O894" s="3"/>
-      <c r="P894" s="6"/>
+      <c r="P894" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="17.25">
       <c r="A895" s="3"/>
@@ -16800,7 +16794,7 @@
       <c r="M895" s="3"/>
       <c r="N895" s="3"/>
       <c r="O895" s="3"/>
-      <c r="P895" s="6"/>
+      <c r="P895" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="17.25">
       <c r="A896" s="3"/>
@@ -16818,7 +16812,7 @@
       <c r="M896" s="3"/>
       <c r="N896" s="3"/>
       <c r="O896" s="3"/>
-      <c r="P896" s="6"/>
+      <c r="P896" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="17.25">
       <c r="A897" s="3"/>
@@ -16836,7 +16830,7 @@
       <c r="M897" s="3"/>
       <c r="N897" s="3"/>
       <c r="O897" s="3"/>
-      <c r="P897" s="6"/>
+      <c r="P897" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="17.25">
       <c r="A898" s="3"/>
@@ -16854,7 +16848,7 @@
       <c r="M898" s="3"/>
       <c r="N898" s="3"/>
       <c r="O898" s="3"/>
-      <c r="P898" s="6"/>
+      <c r="P898" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="17.25">
       <c r="A899" s="3"/>
@@ -16872,7 +16866,7 @@
       <c r="M899" s="3"/>
       <c r="N899" s="3"/>
       <c r="O899" s="3"/>
-      <c r="P899" s="6"/>
+      <c r="P899" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="17.25">
       <c r="A900" s="3"/>
@@ -16890,7 +16884,7 @@
       <c r="M900" s="3"/>
       <c r="N900" s="3"/>
       <c r="O900" s="3"/>
-      <c r="P900" s="6"/>
+      <c r="P900" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="17.25">
       <c r="A901" s="3"/>
@@ -16908,7 +16902,7 @@
       <c r="M901" s="3"/>
       <c r="N901" s="3"/>
       <c r="O901" s="3"/>
-      <c r="P901" s="6"/>
+      <c r="P901" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="17.25">
       <c r="A902" s="3"/>
@@ -16926,7 +16920,7 @@
       <c r="M902" s="3"/>
       <c r="N902" s="3"/>
       <c r="O902" s="3"/>
-      <c r="P902" s="6"/>
+      <c r="P902" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="17.25">
       <c r="A903" s="3"/>
@@ -16944,7 +16938,7 @@
       <c r="M903" s="3"/>
       <c r="N903" s="3"/>
       <c r="O903" s="3"/>
-      <c r="P903" s="6"/>
+      <c r="P903" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="17.25">
       <c r="A904" s="3"/>
@@ -16962,7 +16956,7 @@
       <c r="M904" s="3"/>
       <c r="N904" s="3"/>
       <c r="O904" s="3"/>
-      <c r="P904" s="6"/>
+      <c r="P904" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="17.25">
       <c r="A905" s="3"/>
@@ -16980,7 +16974,7 @@
       <c r="M905" s="3"/>
       <c r="N905" s="3"/>
       <c r="O905" s="3"/>
-      <c r="P905" s="6"/>
+      <c r="P905" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="17.25">
       <c r="A906" s="3"/>
@@ -16998,7 +16992,7 @@
       <c r="M906" s="3"/>
       <c r="N906" s="3"/>
       <c r="O906" s="3"/>
-      <c r="P906" s="6"/>
+      <c r="P906" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="17.25">
       <c r="A907" s="3"/>
@@ -17016,7 +17010,7 @@
       <c r="M907" s="3"/>
       <c r="N907" s="3"/>
       <c r="O907" s="3"/>
-      <c r="P907" s="6"/>
+      <c r="P907" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="17.25">
       <c r="A908" s="3"/>
@@ -17034,7 +17028,7 @@
       <c r="M908" s="3"/>
       <c r="N908" s="3"/>
       <c r="O908" s="3"/>
-      <c r="P908" s="6"/>
+      <c r="P908" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="17.25">
       <c r="A909" s="3"/>
@@ -17052,7 +17046,7 @@
       <c r="M909" s="3"/>
       <c r="N909" s="3"/>
       <c r="O909" s="3"/>
-      <c r="P909" s="6"/>
+      <c r="P909" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="17.25">
       <c r="A910" s="3"/>
@@ -17070,7 +17064,7 @@
       <c r="M910" s="3"/>
       <c r="N910" s="3"/>
       <c r="O910" s="3"/>
-      <c r="P910" s="6"/>
+      <c r="P910" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="17.25">
       <c r="A911" s="3"/>
@@ -17088,7 +17082,7 @@
       <c r="M911" s="3"/>
       <c r="N911" s="3"/>
       <c r="O911" s="3"/>
-      <c r="P911" s="6"/>
+      <c r="P911" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="17.25">
       <c r="A912" s="3"/>
@@ -17106,7 +17100,7 @@
       <c r="M912" s="3"/>
       <c r="N912" s="3"/>
       <c r="O912" s="3"/>
-      <c r="P912" s="6"/>
+      <c r="P912" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="17.25">
       <c r="A913" s="3"/>
@@ -17124,7 +17118,7 @@
       <c r="M913" s="3"/>
       <c r="N913" s="3"/>
       <c r="O913" s="3"/>
-      <c r="P913" s="6"/>
+      <c r="P913" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="17.25">
       <c r="A914" s="3"/>
@@ -17142,7 +17136,7 @@
       <c r="M914" s="3"/>
       <c r="N914" s="3"/>
       <c r="O914" s="3"/>
-      <c r="P914" s="6"/>
+      <c r="P914" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="17.25">
       <c r="A915" s="3"/>
@@ -17160,7 +17154,7 @@
       <c r="M915" s="3"/>
       <c r="N915" s="3"/>
       <c r="O915" s="3"/>
-      <c r="P915" s="6"/>
+      <c r="P915" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="17.25">
       <c r="A916" s="3"/>
@@ -17178,7 +17172,7 @@
       <c r="M916" s="3"/>
       <c r="N916" s="3"/>
       <c r="O916" s="3"/>
-      <c r="P916" s="6"/>
+      <c r="P916" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="17.25">
       <c r="A917" s="3"/>
@@ -17196,7 +17190,7 @@
       <c r="M917" s="3"/>
       <c r="N917" s="3"/>
       <c r="O917" s="3"/>
-      <c r="P917" s="6"/>
+      <c r="P917" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="17.25">
       <c r="A918" s="3"/>
@@ -17214,7 +17208,7 @@
       <c r="M918" s="3"/>
       <c r="N918" s="3"/>
       <c r="O918" s="3"/>
-      <c r="P918" s="6"/>
+      <c r="P918" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="17.25">
       <c r="A919" s="3"/>
@@ -17232,7 +17226,7 @@
       <c r="M919" s="3"/>
       <c r="N919" s="3"/>
       <c r="O919" s="3"/>
-      <c r="P919" s="6"/>
+      <c r="P919" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="17.25">
       <c r="A920" s="3"/>
@@ -17250,7 +17244,7 @@
       <c r="M920" s="3"/>
       <c r="N920" s="3"/>
       <c r="O920" s="3"/>
-      <c r="P920" s="6"/>
+      <c r="P920" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="17.25">
       <c r="A921" s="3"/>
@@ -17268,7 +17262,7 @@
       <c r="M921" s="3"/>
       <c r="N921" s="3"/>
       <c r="O921" s="3"/>
-      <c r="P921" s="6"/>
+      <c r="P921" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="17.25">
       <c r="A922" s="3"/>
@@ -17286,7 +17280,7 @@
       <c r="M922" s="3"/>
       <c r="N922" s="3"/>
       <c r="O922" s="3"/>
-      <c r="P922" s="6"/>
+      <c r="P922" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="17.25">
       <c r="A923" s="3"/>
@@ -17304,7 +17298,7 @@
       <c r="M923" s="3"/>
       <c r="N923" s="3"/>
       <c r="O923" s="3"/>
-      <c r="P923" s="6"/>
+      <c r="P923" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="17.25">
       <c r="A924" s="3"/>
@@ -17322,7 +17316,7 @@
       <c r="M924" s="3"/>
       <c r="N924" s="3"/>
       <c r="O924" s="3"/>
-      <c r="P924" s="6"/>
+      <c r="P924" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="17.25">
       <c r="A925" s="3"/>
@@ -17340,7 +17334,7 @@
       <c r="M925" s="3"/>
       <c r="N925" s="3"/>
       <c r="O925" s="3"/>
-      <c r="P925" s="6"/>
+      <c r="P925" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="17.25">
       <c r="A926" s="3"/>
@@ -17358,7 +17352,7 @@
       <c r="M926" s="3"/>
       <c r="N926" s="3"/>
       <c r="O926" s="3"/>
-      <c r="P926" s="6"/>
+      <c r="P926" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="17.25">
       <c r="A927" s="3"/>
@@ -17376,7 +17370,7 @@
       <c r="M927" s="3"/>
       <c r="N927" s="3"/>
       <c r="O927" s="3"/>
-      <c r="P927" s="6"/>
+      <c r="P927" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="17.25">
       <c r="A928" s="3"/>
@@ -17394,7 +17388,7 @@
       <c r="M928" s="3"/>
       <c r="N928" s="3"/>
       <c r="O928" s="3"/>
-      <c r="P928" s="6"/>
+      <c r="P928" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="17.25">
       <c r="A929" s="3"/>
@@ -17412,7 +17406,7 @@
       <c r="M929" s="3"/>
       <c r="N929" s="3"/>
       <c r="O929" s="3"/>
-      <c r="P929" s="6"/>
+      <c r="P929" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="17.25">
       <c r="A930" s="3"/>
@@ -17430,7 +17424,7 @@
       <c r="M930" s="3"/>
       <c r="N930" s="3"/>
       <c r="O930" s="3"/>
-      <c r="P930" s="6"/>
+      <c r="P930" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="17.25">
       <c r="A931" s="3"/>
@@ -17448,7 +17442,7 @@
       <c r="M931" s="3"/>
       <c r="N931" s="3"/>
       <c r="O931" s="3"/>
-      <c r="P931" s="6"/>
+      <c r="P931" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="17.25">
       <c r="A932" s="3"/>
@@ -17466,7 +17460,7 @@
       <c r="M932" s="3"/>
       <c r="N932" s="3"/>
       <c r="O932" s="3"/>
-      <c r="P932" s="6"/>
+      <c r="P932" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="17.25">
       <c r="A933" s="3"/>
@@ -17484,7 +17478,7 @@
       <c r="M933" s="3"/>
       <c r="N933" s="3"/>
       <c r="O933" s="3"/>
-      <c r="P933" s="6"/>
+      <c r="P933" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="17.25">
       <c r="A934" s="3"/>
@@ -17502,7 +17496,7 @@
       <c r="M934" s="3"/>
       <c r="N934" s="3"/>
       <c r="O934" s="3"/>
-      <c r="P934" s="6"/>
+      <c r="P934" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="17.25">
       <c r="A935" s="3"/>
@@ -17520,7 +17514,7 @@
       <c r="M935" s="3"/>
       <c r="N935" s="3"/>
       <c r="O935" s="3"/>
-      <c r="P935" s="6"/>
+      <c r="P935" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="17.25">
       <c r="A936" s="3"/>
@@ -17538,7 +17532,7 @@
       <c r="M936" s="3"/>
       <c r="N936" s="3"/>
       <c r="O936" s="3"/>
-      <c r="P936" s="6"/>
+      <c r="P936" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="17.25">
       <c r="A937" s="3"/>
@@ -17556,7 +17550,7 @@
       <c r="M937" s="3"/>
       <c r="N937" s="3"/>
       <c r="O937" s="3"/>
-      <c r="P937" s="6"/>
+      <c r="P937" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="17.25">
       <c r="A938" s="3"/>
@@ -17574,7 +17568,7 @@
       <c r="M938" s="3"/>
       <c r="N938" s="3"/>
       <c r="O938" s="3"/>
-      <c r="P938" s="6"/>
+      <c r="P938" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="17.25">
       <c r="A939" s="3"/>
@@ -17592,7 +17586,7 @@
       <c r="M939" s="3"/>
       <c r="N939" s="3"/>
       <c r="O939" s="3"/>
-      <c r="P939" s="6"/>
+      <c r="P939" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="17.25">
       <c r="A940" s="3"/>
@@ -17610,7 +17604,7 @@
       <c r="M940" s="3"/>
       <c r="N940" s="3"/>
       <c r="O940" s="3"/>
-      <c r="P940" s="6"/>
+      <c r="P940" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="17.25">
       <c r="A941" s="3"/>
@@ -17628,7 +17622,7 @@
       <c r="M941" s="3"/>
       <c r="N941" s="3"/>
       <c r="O941" s="3"/>
-      <c r="P941" s="6"/>
+      <c r="P941" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="17.25">
       <c r="A942" s="3"/>
@@ -17646,7 +17640,7 @@
       <c r="M942" s="3"/>
       <c r="N942" s="3"/>
       <c r="O942" s="3"/>
-      <c r="P942" s="6"/>
+      <c r="P942" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="17.25">
       <c r="A943" s="3"/>
@@ -17664,7 +17658,7 @@
       <c r="M943" s="3"/>
       <c r="N943" s="3"/>
       <c r="O943" s="3"/>
-      <c r="P943" s="6"/>
+      <c r="P943" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="17.25">
       <c r="A944" s="3"/>
@@ -17682,7 +17676,7 @@
       <c r="M944" s="3"/>
       <c r="N944" s="3"/>
       <c r="O944" s="3"/>
-      <c r="P944" s="6"/>
+      <c r="P944" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="17.25">
       <c r="A945" s="3"/>
@@ -17700,7 +17694,7 @@
       <c r="M945" s="3"/>
       <c r="N945" s="3"/>
       <c r="O945" s="3"/>
-      <c r="P945" s="6"/>
+      <c r="P945" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="17.25">
       <c r="A946" s="3"/>
@@ -17718,7 +17712,7 @@
       <c r="M946" s="3"/>
       <c r="N946" s="3"/>
       <c r="O946" s="3"/>
-      <c r="P946" s="6"/>
+      <c r="P946" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="17.25">
       <c r="A947" s="3"/>
@@ -17736,7 +17730,7 @@
       <c r="M947" s="3"/>
       <c r="N947" s="3"/>
       <c r="O947" s="3"/>
-      <c r="P947" s="6"/>
+      <c r="P947" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="17.25">
       <c r="A948" s="3"/>
@@ -17754,7 +17748,7 @@
       <c r="M948" s="3"/>
       <c r="N948" s="3"/>
       <c r="O948" s="3"/>
-      <c r="P948" s="6"/>
+      <c r="P948" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="17.25">
       <c r="A949" s="3"/>
@@ -17772,7 +17766,7 @@
       <c r="M949" s="3"/>
       <c r="N949" s="3"/>
       <c r="O949" s="3"/>
-      <c r="P949" s="6"/>
+      <c r="P949" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="17.25">
       <c r="A950" s="3"/>
@@ -17790,7 +17784,7 @@
       <c r="M950" s="3"/>
       <c r="N950" s="3"/>
       <c r="O950" s="3"/>
-      <c r="P950" s="6"/>
+      <c r="P950" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="17.25">
       <c r="A951" s="3"/>
@@ -17808,7 +17802,7 @@
       <c r="M951" s="3"/>
       <c r="N951" s="3"/>
       <c r="O951" s="3"/>
-      <c r="P951" s="6"/>
+      <c r="P951" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="17.25">
       <c r="A952" s="3"/>
@@ -17826,7 +17820,7 @@
       <c r="M952" s="3"/>
       <c r="N952" s="3"/>
       <c r="O952" s="3"/>
-      <c r="P952" s="6"/>
+      <c r="P952" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="17.25">
       <c r="A953" s="3"/>
@@ -17844,7 +17838,7 @@
       <c r="M953" s="3"/>
       <c r="N953" s="3"/>
       <c r="O953" s="3"/>
-      <c r="P953" s="6"/>
+      <c r="P953" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="17.25">
       <c r="A954" s="3"/>
@@ -17862,7 +17856,7 @@
       <c r="M954" s="3"/>
       <c r="N954" s="3"/>
       <c r="O954" s="3"/>
-      <c r="P954" s="6"/>
+      <c r="P954" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="955" customHeight="1" ht="17.25">
       <c r="A955" s="3"/>
@@ -17880,7 +17874,7 @@
       <c r="M955" s="3"/>
       <c r="N955" s="3"/>
       <c r="O955" s="3"/>
-      <c r="P955" s="6"/>
+      <c r="P955" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="956" customHeight="1" ht="17.25">
       <c r="A956" s="3"/>
@@ -17898,7 +17892,7 @@
       <c r="M956" s="3"/>
       <c r="N956" s="3"/>
       <c r="O956" s="3"/>
-      <c r="P956" s="6"/>
+      <c r="P956" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="17.25">
       <c r="A957" s="3"/>
@@ -17916,7 +17910,7 @@
       <c r="M957" s="3"/>
       <c r="N957" s="3"/>
       <c r="O957" s="3"/>
-      <c r="P957" s="6"/>
+      <c r="P957" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="17.25">
       <c r="A958" s="3"/>
@@ -17934,7 +17928,7 @@
       <c r="M958" s="3"/>
       <c r="N958" s="3"/>
       <c r="O958" s="3"/>
-      <c r="P958" s="6"/>
+      <c r="P958" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="17.25">
       <c r="A959" s="3"/>
@@ -17952,7 +17946,7 @@
       <c r="M959" s="3"/>
       <c r="N959" s="3"/>
       <c r="O959" s="3"/>
-      <c r="P959" s="6"/>
+      <c r="P959" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="17.25">
       <c r="A960" s="3"/>
@@ -17970,7 +17964,7 @@
       <c r="M960" s="3"/>
       <c r="N960" s="3"/>
       <c r="O960" s="3"/>
-      <c r="P960" s="6"/>
+      <c r="P960" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="17.25">
       <c r="A961" s="3"/>
@@ -17988,7 +17982,7 @@
       <c r="M961" s="3"/>
       <c r="N961" s="3"/>
       <c r="O961" s="3"/>
-      <c r="P961" s="6"/>
+      <c r="P961" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="17.25">
       <c r="A962" s="3"/>
@@ -18006,7 +18000,7 @@
       <c r="M962" s="3"/>
       <c r="N962" s="3"/>
       <c r="O962" s="3"/>
-      <c r="P962" s="6"/>
+      <c r="P962" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="17.25">
       <c r="A963" s="3"/>
@@ -18024,7 +18018,7 @@
       <c r="M963" s="3"/>
       <c r="N963" s="3"/>
       <c r="O963" s="3"/>
-      <c r="P963" s="6"/>
+      <c r="P963" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="17.25">
       <c r="A964" s="3"/>
@@ -18042,7 +18036,7 @@
       <c r="M964" s="3"/>
       <c r="N964" s="3"/>
       <c r="O964" s="3"/>
-      <c r="P964" s="6"/>
+      <c r="P964" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="17.25">
       <c r="A965" s="3"/>
@@ -18060,7 +18054,7 @@
       <c r="M965" s="3"/>
       <c r="N965" s="3"/>
       <c r="O965" s="3"/>
-      <c r="P965" s="6"/>
+      <c r="P965" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="17.25">
       <c r="A966" s="3"/>
@@ -18078,7 +18072,7 @@
       <c r="M966" s="3"/>
       <c r="N966" s="3"/>
       <c r="O966" s="3"/>
-      <c r="P966" s="6"/>
+      <c r="P966" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="17.25">
       <c r="A967" s="3"/>
@@ -18096,7 +18090,7 @@
       <c r="M967" s="3"/>
       <c r="N967" s="3"/>
       <c r="O967" s="3"/>
-      <c r="P967" s="6"/>
+      <c r="P967" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="17.25">
       <c r="A968" s="3"/>
@@ -18114,7 +18108,7 @@
       <c r="M968" s="3"/>
       <c r="N968" s="3"/>
       <c r="O968" s="3"/>
-      <c r="P968" s="6"/>
+      <c r="P968" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="17.25">
       <c r="A969" s="3"/>
@@ -18132,7 +18126,7 @@
       <c r="M969" s="3"/>
       <c r="N969" s="3"/>
       <c r="O969" s="3"/>
-      <c r="P969" s="6"/>
+      <c r="P969" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="17.25">
       <c r="A970" s="3"/>
@@ -18150,7 +18144,7 @@
       <c r="M970" s="3"/>
       <c r="N970" s="3"/>
       <c r="O970" s="3"/>
-      <c r="P970" s="6"/>
+      <c r="P970" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="17.25">
       <c r="A971" s="3"/>
@@ -18168,7 +18162,7 @@
       <c r="M971" s="3"/>
       <c r="N971" s="3"/>
       <c r="O971" s="3"/>
-      <c r="P971" s="6"/>
+      <c r="P971" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="17.25">
       <c r="A972" s="3"/>
@@ -18186,7 +18180,7 @@
       <c r="M972" s="3"/>
       <c r="N972" s="3"/>
       <c r="O972" s="3"/>
-      <c r="P972" s="6"/>
+      <c r="P972" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="17.25">
       <c r="A973" s="3"/>
@@ -18204,7 +18198,7 @@
       <c r="M973" s="3"/>
       <c r="N973" s="3"/>
       <c r="O973" s="3"/>
-      <c r="P973" s="6"/>
+      <c r="P973" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="17.25">
       <c r="A974" s="3"/>
@@ -18222,7 +18216,7 @@
       <c r="M974" s="3"/>
       <c r="N974" s="3"/>
       <c r="O974" s="3"/>
-      <c r="P974" s="6"/>
+      <c r="P974" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="17.25">
       <c r="A975" s="3"/>
@@ -18240,7 +18234,7 @@
       <c r="M975" s="3"/>
       <c r="N975" s="3"/>
       <c r="O975" s="3"/>
-      <c r="P975" s="6"/>
+      <c r="P975" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="976" customHeight="1" ht="17.25">
       <c r="A976" s="3"/>
@@ -18258,7 +18252,7 @@
       <c r="M976" s="3"/>
       <c r="N976" s="3"/>
       <c r="O976" s="3"/>
-      <c r="P976" s="6"/>
+      <c r="P976" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="17.25">
       <c r="A977" s="3"/>
@@ -18276,7 +18270,7 @@
       <c r="M977" s="3"/>
       <c r="N977" s="3"/>
       <c r="O977" s="3"/>
-      <c r="P977" s="6"/>
+      <c r="P977" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="17.25">
       <c r="A978" s="3"/>
@@ -18294,7 +18288,7 @@
       <c r="M978" s="3"/>
       <c r="N978" s="3"/>
       <c r="O978" s="3"/>
-      <c r="P978" s="6"/>
+      <c r="P978" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="17.25">
       <c r="A979" s="3"/>
@@ -18312,7 +18306,7 @@
       <c r="M979" s="3"/>
       <c r="N979" s="3"/>
       <c r="O979" s="3"/>
-      <c r="P979" s="6"/>
+      <c r="P979" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="980" customHeight="1" ht="17.25">
       <c r="A980" s="3"/>
@@ -18330,7 +18324,7 @@
       <c r="M980" s="3"/>
       <c r="N980" s="3"/>
       <c r="O980" s="3"/>
-      <c r="P980" s="6"/>
+      <c r="P980" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="981" customHeight="1" ht="17.25">
       <c r="A981" s="3"/>
@@ -18348,7 +18342,7 @@
       <c r="M981" s="3"/>
       <c r="N981" s="3"/>
       <c r="O981" s="3"/>
-      <c r="P981" s="6"/>
+      <c r="P981" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="982" customHeight="1" ht="17.25">
       <c r="A982" s="3"/>
@@ -18366,7 +18360,7 @@
       <c r="M982" s="3"/>
       <c r="N982" s="3"/>
       <c r="O982" s="3"/>
-      <c r="P982" s="6"/>
+      <c r="P982" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="983" customHeight="1" ht="17.25">
       <c r="A983" s="3"/>
@@ -18384,7 +18378,7 @@
       <c r="M983" s="3"/>
       <c r="N983" s="3"/>
       <c r="O983" s="3"/>
-      <c r="P983" s="6"/>
+      <c r="P983" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="984" customHeight="1" ht="17.25">
       <c r="A984" s="3"/>
@@ -18402,7 +18396,7 @@
       <c r="M984" s="3"/>
       <c r="N984" s="3"/>
       <c r="O984" s="3"/>
-      <c r="P984" s="6"/>
+      <c r="P984" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="985" customHeight="1" ht="17.25">
       <c r="A985" s="3"/>
@@ -18420,7 +18414,7 @@
       <c r="M985" s="3"/>
       <c r="N985" s="3"/>
       <c r="O985" s="3"/>
-      <c r="P985" s="6"/>
+      <c r="P985" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="986" customHeight="1" ht="17.25">
       <c r="A986" s="3"/>
@@ -18438,7 +18432,7 @@
       <c r="M986" s="3"/>
       <c r="N986" s="3"/>
       <c r="O986" s="3"/>
-      <c r="P986" s="6"/>
+      <c r="P986" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="987" customHeight="1" ht="17.25">
       <c r="A987" s="3"/>
@@ -18456,7 +18450,7 @@
       <c r="M987" s="3"/>
       <c r="N987" s="3"/>
       <c r="O987" s="3"/>
-      <c r="P987" s="6"/>
+      <c r="P987" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="988" customHeight="1" ht="17.25">
       <c r="A988" s="3"/>
@@ -18474,7 +18468,7 @@
       <c r="M988" s="3"/>
       <c r="N988" s="3"/>
       <c r="O988" s="3"/>
-      <c r="P988" s="6"/>
+      <c r="P988" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="989" customHeight="1" ht="17.25">
       <c r="A989" s="3"/>
@@ -18492,7 +18486,7 @@
       <c r="M989" s="3"/>
       <c r="N989" s="3"/>
       <c r="O989" s="3"/>
-      <c r="P989" s="6"/>
+      <c r="P989" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="990" customHeight="1" ht="17.25">
       <c r="A990" s="3"/>
@@ -18510,7 +18504,7 @@
       <c r="M990" s="3"/>
       <c r="N990" s="3"/>
       <c r="O990" s="3"/>
-      <c r="P990" s="6"/>
+      <c r="P990" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="991" customHeight="1" ht="17.25">
       <c r="A991" s="3"/>
@@ -18528,7 +18522,7 @@
       <c r="M991" s="3"/>
       <c r="N991" s="3"/>
       <c r="O991" s="3"/>
-      <c r="P991" s="6"/>
+      <c r="P991" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="992" customHeight="1" ht="17.25">
       <c r="A992" s="3"/>
@@ -18546,7 +18540,7 @@
       <c r="M992" s="3"/>
       <c r="N992" s="3"/>
       <c r="O992" s="3"/>
-      <c r="P992" s="6"/>
+      <c r="P992" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="993" customHeight="1" ht="17.25">
       <c r="A993" s="3"/>
@@ -18564,7 +18558,7 @@
       <c r="M993" s="3"/>
       <c r="N993" s="3"/>
       <c r="O993" s="3"/>
-      <c r="P993" s="6"/>
+      <c r="P993" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="994" customHeight="1" ht="17.25">
       <c r="A994" s="3"/>
@@ -18582,7 +18576,7 @@
       <c r="M994" s="3"/>
       <c r="N994" s="3"/>
       <c r="O994" s="3"/>
-      <c r="P994" s="6"/>
+      <c r="P994" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="995" customHeight="1" ht="17.25">
       <c r="A995" s="3"/>
@@ -18600,7 +18594,7 @@
       <c r="M995" s="3"/>
       <c r="N995" s="3"/>
       <c r="O995" s="3"/>
-      <c r="P995" s="6"/>
+      <c r="P995" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="996" customHeight="1" ht="17.25">
       <c r="A996" s="3"/>
@@ -18618,7 +18612,7 @@
       <c r="M996" s="3"/>
       <c r="N996" s="3"/>
       <c r="O996" s="3"/>
-      <c r="P996" s="6"/>
+      <c r="P996" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="997" customHeight="1" ht="17.25">
       <c r="A997" s="3"/>
@@ -18636,7 +18630,7 @@
       <c r="M997" s="3"/>
       <c r="N997" s="3"/>
       <c r="O997" s="3"/>
-      <c r="P997" s="6"/>
+      <c r="P997" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="998" customHeight="1" ht="17.25">
       <c r="A998" s="3"/>
@@ -18654,7 +18648,7 @@
       <c r="M998" s="3"/>
       <c r="N998" s="3"/>
       <c r="O998" s="3"/>
-      <c r="P998" s="6"/>
+      <c r="P998" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="999" customHeight="1" ht="17.25">
       <c r="A999" s="3"/>
@@ -18672,7 +18666,7 @@
       <c r="M999" s="3"/>
       <c r="N999" s="3"/>
       <c r="O999" s="3"/>
-      <c r="P999" s="6"/>
+      <c r="P999" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1000" customHeight="1" ht="17.25">
       <c r="A1000" s="3"/>
@@ -18690,7 +18684,7 @@
       <c r="M1000" s="3"/>
       <c r="N1000" s="3"/>
       <c r="O1000" s="3"/>
-      <c r="P1000" s="6"/>
+      <c r="P1000" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
